--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/G06Monthreport.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/G06Monthreport.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr showInkAnnotation="0" defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\HSbank_branches20201013\tams-svreport-parent\tams-svreport\src\main\resources\tpl\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20730" windowHeight="9765" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="10395" windowHeight="4995"/>
   </bookViews>
   <sheets>
     <sheet name="G0601" sheetId="1" r:id="rId1"/>
@@ -13,14 +18,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'G0601'!$A$1:$J$52</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'G0602'!$A$1:$E$174</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'G0602'!$A$1:$E$171</definedName>
   </definedNames>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="741">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="732">
   <si>
     <t>G06_I 非保本理财业务月度统计表-产品情况</t>
   </si>
@@ -29,9 +34,6 @@
   </si>
   <si>
     <t>报表日期：${report.termname}</t>
-  </si>
-  <si>
-    <t>单位：万元、只</t>
   </si>
   <si>
     <t>项目</t>
@@ -935,9 +937,6 @@
     </r>
   </si>
   <si>
-    <t>单位：万元</t>
-  </si>
-  <si>
     <t>1.期末理财资金投向情况</t>
   </si>
   <si>
@@ -2133,9 +2132,18 @@
     <t>${AMT1_17_a.bottombalance}</t>
   </si>
   <si>
+    <t xml:space="preserve">     其中：1.17.b 投向市场化债转股相关产品的部分</t>
+  </si>
+  <si>
+    <t>${AMT1_17_b.balance}</t>
+  </si>
+  <si>
     <t>2.期末理财负债情况</t>
   </si>
   <si>
+    <t>负债类别</t>
+  </si>
+  <si>
     <t>2.1同业拆入及卖出回购</t>
   </si>
   <si>
@@ -2259,51 +2267,11 @@
     <t>无数据部分</t>
   </si>
   <si>
-    <t>${AMT1_17_b.balance}</t>
+    <t>单位：万元</t>
     <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">     其中：1.17.b 投向市场化债转股相关产品的部分</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">     其中：1.17.d 商业银行永续债</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">     其中：1.17.e 商业银行优先股</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t>负债类别</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t>${AMT1_17_c.balance}</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t>${AMT1_17_d.balance}</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t>${AMT1_17_e.balance}</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t>${AMT1_17_c.bottombalance}</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t>${AMT1_17_d.bottombalance}</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t>${AMT1_17_e.bottombalance}</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">     其中：1.17.c 商业银行二级资本债</t>
+    <t>单位：万元、只</t>
     <phoneticPr fontId="16" type="noConversion"/>
   </si>
 </sst>
@@ -3047,6 +3015,37 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3061,30 +3060,6 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3100,53 +3075,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
@@ -3173,11 +3108,53 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="17" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="6" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3201,15 +3178,6 @@
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="17" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -3224,6 +3192,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -3283,7 +3254,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -3325,7 +3296,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3360,7 +3331,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3588,886 +3559,886 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="34.5" customHeight="1">
-      <c r="A1" s="102" t="s">
+      <c r="A1" s="112" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="102"/>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
+      <c r="B1" s="112"/>
+      <c r="C1" s="112"/>
+      <c r="D1" s="112"/>
+      <c r="E1" s="112"/>
+      <c r="F1" s="112"/>
+      <c r="G1" s="112"/>
+      <c r="H1" s="112"/>
+      <c r="I1" s="112"/>
+      <c r="J1" s="112"/>
     </row>
     <row r="2" spans="1:10" s="58" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A2" s="103" t="s">
+      <c r="A2" s="113" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="103"/>
-      <c r="E2" s="104" t="s">
+      <c r="B2" s="113"/>
+      <c r="E2" s="114" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="105"/>
+      <c r="F2" s="115"/>
       <c r="G2" s="60"/>
       <c r="H2" s="61"/>
       <c r="J2" s="87" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="59" customFormat="1" ht="23.1" customHeight="1">
+      <c r="A3" s="116" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" s="59" customFormat="1" ht="23.1" customHeight="1">
-      <c r="A3" s="114" t="s">
+      <c r="B3" s="117"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="62" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="115"/>
-      <c r="C3" s="116"/>
-      <c r="D3" s="62" t="s">
+      <c r="E3" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="62" t="s">
+      <c r="F3" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="62" t="s">
+      <c r="G3" s="63" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="63" t="s">
+      <c r="H3" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="64" t="s">
+      <c r="I3" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="63" t="s">
+      <c r="J3" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="88" t="s">
+    </row>
+    <row r="4" spans="1:10" s="59" customFormat="1" ht="24" customHeight="1">
+      <c r="A4" s="119"/>
+      <c r="B4" s="120"/>
+      <c r="C4" s="120"/>
+      <c r="D4" s="65" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" s="59" customFormat="1" ht="24" customHeight="1">
-      <c r="A4" s="117"/>
-      <c r="B4" s="118"/>
-      <c r="C4" s="118"/>
-      <c r="D4" s="65" t="s">
+      <c r="E4" s="65" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="65" t="s">
+      <c r="F4" s="65" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="65" t="s">
+      <c r="G4" s="65" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="65" t="s">
+      <c r="H4" s="66" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="66" t="s">
+      <c r="I4" s="65" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="65" t="s">
+      <c r="J4" s="89" t="s">
         <v>17</v>
       </c>
-      <c r="J4" s="89" t="s">
+    </row>
+    <row r="5" spans="1:10" s="59" customFormat="1" ht="18.95" customHeight="1">
+      <c r="A5" s="103" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" s="59" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A5" s="111" t="s">
+      <c r="B5" s="106" t="s">
         <v>19</v>
-      </c>
-      <c r="B5" s="106" t="s">
-        <v>20</v>
       </c>
       <c r="C5" s="106"/>
       <c r="D5" s="67" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="67" t="s">
+      <c r="F5" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="67" t="s">
+      <c r="G5" s="67" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="67" t="s">
+      <c r="H5" s="68" t="s">
         <v>24</v>
       </c>
-      <c r="H5" s="68" t="s">
+      <c r="I5" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="68" t="s">
+      <c r="J5" s="90" t="s">
         <v>26</v>
       </c>
-      <c r="J5" s="90" t="s">
+    </row>
+    <row r="6" spans="1:10" s="59" customFormat="1" ht="18.95" customHeight="1">
+      <c r="A6" s="103"/>
+      <c r="B6" s="106" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" s="59" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A6" s="111"/>
-      <c r="B6" s="106" t="s">
-        <v>28</v>
       </c>
       <c r="C6" s="106"/>
       <c r="D6" s="67" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="67" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="67" t="s">
+      <c r="F6" s="67" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="67" t="s">
+      <c r="G6" s="67" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="67" t="s">
+      <c r="H6" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="H6" s="68" t="s">
+      <c r="I6" s="68" t="s">
         <v>33</v>
       </c>
-      <c r="I6" s="68" t="s">
+      <c r="J6" s="90" t="s">
         <v>34</v>
       </c>
-      <c r="J6" s="90" t="s">
+    </row>
+    <row r="7" spans="1:10" s="59" customFormat="1" ht="18.95" customHeight="1">
+      <c r="A7" s="103"/>
+      <c r="B7" s="105" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" s="59" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A7" s="111"/>
-      <c r="B7" s="107" t="s">
+      <c r="C7" s="105"/>
+      <c r="D7" s="69" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="107"/>
-      <c r="D7" s="69" t="s">
+      <c r="E7" s="69" t="s">
         <v>37</v>
       </c>
-      <c r="E7" s="69" t="s">
+      <c r="F7" s="69" t="s">
         <v>38</v>
       </c>
-      <c r="F7" s="69" t="s">
+      <c r="G7" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="G7" s="69" t="s">
+      <c r="H7" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="H7" s="69" t="s">
+      <c r="I7" s="69" t="s">
         <v>41</v>
       </c>
-      <c r="I7" s="69" t="s">
+      <c r="J7" s="91" t="s">
         <v>42</v>
       </c>
-      <c r="J7" s="91" t="s">
+    </row>
+    <row r="8" spans="1:10" s="59" customFormat="1" ht="18.95" customHeight="1">
+      <c r="A8" s="103" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" s="59" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A8" s="111" t="s">
+      <c r="B8" s="106" t="s">
         <v>44</v>
-      </c>
-      <c r="B8" s="106" t="s">
-        <v>45</v>
       </c>
       <c r="C8" s="106"/>
       <c r="D8" s="67" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="E8" s="67" t="s">
+      <c r="F8" s="67" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="67" t="s">
+      <c r="G8" s="67" t="s">
         <v>48</v>
       </c>
-      <c r="G8" s="67" t="s">
+      <c r="H8" s="67" t="s">
         <v>49</v>
       </c>
-      <c r="H8" s="67" t="s">
+      <c r="I8" s="67" t="s">
         <v>50</v>
       </c>
-      <c r="I8" s="67" t="s">
+      <c r="J8" s="92" t="s">
         <v>51</v>
       </c>
-      <c r="J8" s="92" t="s">
+    </row>
+    <row r="9" spans="1:10" s="59" customFormat="1" ht="18.95" customHeight="1">
+      <c r="A9" s="103"/>
+      <c r="B9" s="106" t="s">
         <v>52</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" s="59" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A9" s="111"/>
-      <c r="B9" s="106" t="s">
-        <v>53</v>
       </c>
       <c r="C9" s="106"/>
       <c r="D9" s="67" t="s">
+        <v>53</v>
+      </c>
+      <c r="E9" s="67" t="s">
         <v>54</v>
       </c>
-      <c r="E9" s="67" t="s">
+      <c r="F9" s="67" t="s">
         <v>55</v>
       </c>
-      <c r="F9" s="67" t="s">
+      <c r="G9" s="67" t="s">
         <v>56</v>
       </c>
-      <c r="G9" s="67" t="s">
+      <c r="H9" s="67" t="s">
         <v>57</v>
       </c>
-      <c r="H9" s="67" t="s">
+      <c r="I9" s="67" t="s">
         <v>58</v>
       </c>
-      <c r="I9" s="67" t="s">
+      <c r="J9" s="92" t="s">
         <v>59</v>
       </c>
-      <c r="J9" s="92" t="s">
+    </row>
+    <row r="10" spans="1:10" s="59" customFormat="1" ht="18.95" customHeight="1">
+      <c r="A10" s="103"/>
+      <c r="B10" s="106" t="s">
         <v>60</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" s="59" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A10" s="111"/>
-      <c r="B10" s="106" t="s">
-        <v>61</v>
       </c>
       <c r="C10" s="106"/>
       <c r="D10" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="E10" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="E10" s="67" t="s">
+      <c r="F10" s="67" t="s">
         <v>63</v>
       </c>
-      <c r="F10" s="67" t="s">
+      <c r="G10" s="67" t="s">
         <v>64</v>
       </c>
-      <c r="G10" s="67" t="s">
+      <c r="H10" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="H10" s="67" t="s">
+      <c r="I10" s="67" t="s">
         <v>66</v>
       </c>
-      <c r="I10" s="67" t="s">
+      <c r="J10" s="92" t="s">
         <v>67</v>
       </c>
-      <c r="J10" s="92" t="s">
+    </row>
+    <row r="11" spans="1:10" s="59" customFormat="1" ht="18.95" customHeight="1">
+      <c r="A11" s="103"/>
+      <c r="B11" s="106" t="s">
         <v>68</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" s="59" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A11" s="111"/>
-      <c r="B11" s="106" t="s">
-        <v>69</v>
       </c>
       <c r="C11" s="106"/>
       <c r="D11" s="67" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" s="67" t="s">
         <v>70</v>
       </c>
-      <c r="E11" s="67" t="s">
+      <c r="F11" s="67" t="s">
         <v>71</v>
       </c>
-      <c r="F11" s="67" t="s">
+      <c r="G11" s="67" t="s">
         <v>72</v>
       </c>
-      <c r="G11" s="67" t="s">
+      <c r="H11" s="67" t="s">
         <v>73</v>
       </c>
-      <c r="H11" s="67" t="s">
+      <c r="I11" s="67" t="s">
         <v>74</v>
       </c>
-      <c r="I11" s="67" t="s">
+      <c r="J11" s="92" t="s">
         <v>75</v>
       </c>
-      <c r="J11" s="92" t="s">
+    </row>
+    <row r="12" spans="1:10" s="59" customFormat="1" ht="18.95" customHeight="1">
+      <c r="A12" s="103"/>
+      <c r="B12" s="105" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" s="59" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A12" s="111"/>
-      <c r="B12" s="107" t="s">
+      <c r="C12" s="105"/>
+      <c r="D12" s="69" t="s">
         <v>77</v>
       </c>
-      <c r="C12" s="107"/>
-      <c r="D12" s="69" t="s">
+      <c r="E12" s="69" t="s">
         <v>78</v>
       </c>
-      <c r="E12" s="69" t="s">
+      <c r="F12" s="69" t="s">
         <v>79</v>
       </c>
-      <c r="F12" s="69" t="s">
+      <c r="G12" s="69" t="s">
         <v>80</v>
       </c>
-      <c r="G12" s="69" t="s">
+      <c r="H12" s="69" t="s">
         <v>81</v>
       </c>
-      <c r="H12" s="69" t="s">
+      <c r="I12" s="69" t="s">
         <v>82</v>
       </c>
-      <c r="I12" s="69" t="s">
+      <c r="J12" s="91" t="s">
         <v>83</v>
       </c>
-      <c r="J12" s="91" t="s">
+    </row>
+    <row r="13" spans="1:10" s="59" customFormat="1" ht="18.95" customHeight="1">
+      <c r="A13" s="103" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" s="59" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A13" s="111" t="s">
+      <c r="B13" s="109" t="s">
         <v>85</v>
       </c>
-      <c r="B13" s="109" t="s">
+      <c r="C13" s="71" t="s">
         <v>86</v>
       </c>
-      <c r="C13" s="71" t="s">
+      <c r="D13" s="67" t="s">
         <v>87</v>
       </c>
-      <c r="D13" s="67" t="s">
+      <c r="E13" s="67" t="s">
         <v>88</v>
       </c>
-      <c r="E13" s="67" t="s">
+      <c r="F13" s="67" t="s">
         <v>89</v>
       </c>
-      <c r="F13" s="67" t="s">
+      <c r="G13" s="67" t="s">
         <v>90</v>
       </c>
-      <c r="G13" s="67" t="s">
+      <c r="H13" s="68" t="s">
         <v>91</v>
-      </c>
-      <c r="H13" s="68" t="s">
-        <v>92</v>
       </c>
       <c r="I13" s="93"/>
       <c r="J13" s="94"/>
     </row>
     <row r="14" spans="1:10" s="59" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A14" s="111"/>
+      <c r="A14" s="103"/>
       <c r="B14" s="109"/>
       <c r="C14" s="71" t="s">
+        <v>92</v>
+      </c>
+      <c r="D14" s="67" t="s">
         <v>93</v>
       </c>
-      <c r="D14" s="67" t="s">
+      <c r="E14" s="67" t="s">
         <v>94</v>
       </c>
-      <c r="E14" s="67" t="s">
+      <c r="F14" s="67" t="s">
         <v>95</v>
       </c>
-      <c r="F14" s="67" t="s">
+      <c r="G14" s="67" t="s">
         <v>96</v>
       </c>
-      <c r="G14" s="67" t="s">
+      <c r="H14" s="68" t="s">
         <v>97</v>
-      </c>
-      <c r="H14" s="68" t="s">
-        <v>98</v>
       </c>
       <c r="I14" s="93"/>
       <c r="J14" s="94"/>
     </row>
     <row r="15" spans="1:10" s="59" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A15" s="111"/>
+      <c r="A15" s="103"/>
       <c r="B15" s="109"/>
       <c r="C15" s="71" t="s">
+        <v>98</v>
+      </c>
+      <c r="D15" s="67" t="s">
         <v>99</v>
       </c>
-      <c r="D15" s="67" t="s">
+      <c r="E15" s="67" t="s">
         <v>100</v>
       </c>
-      <c r="E15" s="67" t="s">
+      <c r="F15" s="67" t="s">
         <v>101</v>
       </c>
-      <c r="F15" s="67" t="s">
+      <c r="G15" s="67" t="s">
         <v>102</v>
       </c>
-      <c r="G15" s="67" t="s">
+      <c r="H15" s="68" t="s">
         <v>103</v>
-      </c>
-      <c r="H15" s="68" t="s">
-        <v>104</v>
       </c>
       <c r="I15" s="93"/>
       <c r="J15" s="94"/>
     </row>
     <row r="16" spans="1:10" s="59" customFormat="1" ht="32.1" customHeight="1">
-      <c r="A16" s="111"/>
+      <c r="A16" s="103"/>
       <c r="B16" s="109"/>
       <c r="C16" s="71" t="s">
+        <v>104</v>
+      </c>
+      <c r="D16" s="67" t="s">
         <v>105</v>
       </c>
-      <c r="D16" s="67" t="s">
+      <c r="E16" s="67" t="s">
         <v>106</v>
       </c>
-      <c r="E16" s="67" t="s">
+      <c r="F16" s="67" t="s">
         <v>107</v>
       </c>
-      <c r="F16" s="67" t="s">
+      <c r="G16" s="67" t="s">
         <v>108</v>
       </c>
-      <c r="G16" s="67" t="s">
+      <c r="H16" s="68" t="s">
         <v>109</v>
-      </c>
-      <c r="H16" s="68" t="s">
-        <v>110</v>
       </c>
       <c r="I16" s="93"/>
       <c r="J16" s="94"/>
     </row>
     <row r="17" spans="1:10" s="59" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A17" s="111"/>
+      <c r="A17" s="103"/>
       <c r="B17" s="109" t="s">
+        <v>110</v>
+      </c>
+      <c r="C17" s="71" t="s">
         <v>111</v>
       </c>
-      <c r="C17" s="71" t="s">
+      <c r="D17" s="67" t="s">
         <v>112</v>
       </c>
-      <c r="D17" s="67" t="s">
+      <c r="E17" s="67" t="s">
         <v>113</v>
       </c>
-      <c r="E17" s="67" t="s">
+      <c r="F17" s="67" t="s">
         <v>114</v>
       </c>
-      <c r="F17" s="67" t="s">
+      <c r="G17" s="67" t="s">
         <v>115</v>
       </c>
-      <c r="G17" s="67" t="s">
+      <c r="H17" s="68" t="s">
         <v>116</v>
-      </c>
-      <c r="H17" s="68" t="s">
-        <v>117</v>
       </c>
       <c r="I17" s="93"/>
       <c r="J17" s="94"/>
     </row>
     <row r="18" spans="1:10" s="59" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A18" s="111"/>
+      <c r="A18" s="103"/>
       <c r="B18" s="109"/>
       <c r="C18" s="71" t="s">
+        <v>117</v>
+      </c>
+      <c r="D18" s="67" t="s">
         <v>118</v>
       </c>
-      <c r="D18" s="67" t="s">
+      <c r="E18" s="67" t="s">
         <v>119</v>
       </c>
-      <c r="E18" s="67" t="s">
+      <c r="F18" s="67" t="s">
         <v>120</v>
       </c>
-      <c r="F18" s="67" t="s">
+      <c r="G18" s="67" t="s">
         <v>121</v>
       </c>
-      <c r="G18" s="67" t="s">
+      <c r="H18" s="68" t="s">
         <v>122</v>
-      </c>
-      <c r="H18" s="68" t="s">
-        <v>123</v>
       </c>
       <c r="I18" s="93"/>
       <c r="J18" s="94"/>
     </row>
     <row r="19" spans="1:10" s="59" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A19" s="111"/>
+      <c r="A19" s="103"/>
       <c r="B19" s="108" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C19" s="108"/>
       <c r="D19" s="72" t="s">
+        <v>124</v>
+      </c>
+      <c r="E19" s="72" t="s">
         <v>125</v>
       </c>
-      <c r="E19" s="72" t="s">
+      <c r="F19" s="72" t="s">
         <v>126</v>
       </c>
-      <c r="F19" s="72" t="s">
+      <c r="G19" s="72" t="s">
         <v>127</v>
       </c>
-      <c r="G19" s="72" t="s">
+      <c r="H19" s="72" t="s">
         <v>128</v>
-      </c>
-      <c r="H19" s="72" t="s">
-        <v>129</v>
       </c>
       <c r="I19" s="93"/>
       <c r="J19" s="94"/>
     </row>
     <row r="20" spans="1:10" s="59" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A20" s="111" t="s">
+      <c r="A20" s="103" t="s">
+        <v>129</v>
+      </c>
+      <c r="B20" s="109" t="s">
         <v>130</v>
       </c>
-      <c r="B20" s="109" t="s">
+      <c r="C20" s="73" t="s">
         <v>131</v>
       </c>
-      <c r="C20" s="73" t="s">
+      <c r="D20" s="67" t="s">
         <v>132</v>
       </c>
-      <c r="D20" s="67" t="s">
+      <c r="E20" s="67" t="s">
         <v>133</v>
       </c>
-      <c r="E20" s="67" t="s">
+      <c r="F20" s="67" t="s">
         <v>134</v>
       </c>
-      <c r="F20" s="67" t="s">
+      <c r="G20" s="67" t="s">
         <v>135</v>
       </c>
-      <c r="G20" s="67" t="s">
+      <c r="H20" s="74" t="s">
         <v>136</v>
-      </c>
-      <c r="H20" s="74" t="s">
-        <v>137</v>
       </c>
       <c r="I20" s="93"/>
       <c r="J20" s="94"/>
     </row>
     <row r="21" spans="1:10" s="59" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A21" s="111"/>
+      <c r="A21" s="103"/>
       <c r="B21" s="109"/>
       <c r="C21" s="73" t="s">
+        <v>137</v>
+      </c>
+      <c r="D21" s="67" t="s">
         <v>138</v>
       </c>
-      <c r="D21" s="67" t="s">
+      <c r="E21" s="67" t="s">
         <v>139</v>
       </c>
-      <c r="E21" s="67" t="s">
+      <c r="F21" s="67" t="s">
         <v>140</v>
       </c>
-      <c r="F21" s="67" t="s">
+      <c r="G21" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="G21" s="67" t="s">
+      <c r="H21" s="74" t="s">
         <v>142</v>
-      </c>
-      <c r="H21" s="74" t="s">
-        <v>143</v>
       </c>
       <c r="I21" s="93"/>
       <c r="J21" s="94"/>
     </row>
     <row r="22" spans="1:10" s="59" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A22" s="111"/>
+      <c r="A22" s="103"/>
       <c r="B22" s="109"/>
       <c r="C22" s="73" t="s">
+        <v>143</v>
+      </c>
+      <c r="D22" s="67" t="s">
         <v>144</v>
       </c>
-      <c r="D22" s="67" t="s">
+      <c r="E22" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="E22" s="67" t="s">
+      <c r="F22" s="67" t="s">
         <v>146</v>
       </c>
-      <c r="F22" s="67" t="s">
+      <c r="G22" s="67" t="s">
         <v>147</v>
       </c>
-      <c r="G22" s="67" t="s">
+      <c r="H22" s="74" t="s">
         <v>148</v>
-      </c>
-      <c r="H22" s="74" t="s">
-        <v>149</v>
       </c>
       <c r="I22" s="93"/>
       <c r="J22" s="94"/>
     </row>
     <row r="23" spans="1:10" s="59" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A23" s="111"/>
+      <c r="A23" s="103"/>
       <c r="B23" s="109"/>
       <c r="C23" s="73" t="s">
+        <v>149</v>
+      </c>
+      <c r="D23" s="67" t="s">
         <v>150</v>
       </c>
-      <c r="D23" s="67" t="s">
+      <c r="E23" s="67" t="s">
         <v>151</v>
       </c>
-      <c r="E23" s="67" t="s">
+      <c r="F23" s="67" t="s">
         <v>152</v>
       </c>
-      <c r="F23" s="67" t="s">
+      <c r="G23" s="67" t="s">
         <v>153</v>
       </c>
-      <c r="G23" s="67" t="s">
+      <c r="H23" s="74" t="s">
         <v>154</v>
-      </c>
-      <c r="H23" s="74" t="s">
-        <v>155</v>
       </c>
       <c r="I23" s="93"/>
       <c r="J23" s="94"/>
     </row>
     <row r="24" spans="1:10" s="59" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A24" s="111"/>
+      <c r="A24" s="103"/>
       <c r="B24" s="109"/>
       <c r="C24" s="73" t="s">
+        <v>155</v>
+      </c>
+      <c r="D24" s="67" t="s">
         <v>156</v>
       </c>
-      <c r="D24" s="67" t="s">
+      <c r="E24" s="67" t="s">
         <v>157</v>
       </c>
-      <c r="E24" s="67" t="s">
+      <c r="F24" s="67" t="s">
         <v>158</v>
       </c>
-      <c r="F24" s="67" t="s">
+      <c r="G24" s="67" t="s">
         <v>159</v>
       </c>
-      <c r="G24" s="67" t="s">
+      <c r="H24" s="74" t="s">
         <v>160</v>
-      </c>
-      <c r="H24" s="74" t="s">
-        <v>161</v>
       </c>
       <c r="I24" s="93"/>
       <c r="J24" s="94"/>
     </row>
     <row r="25" spans="1:10" s="59" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A25" s="111"/>
+      <c r="A25" s="103"/>
       <c r="B25" s="109"/>
       <c r="C25" s="70" t="s">
+        <v>161</v>
+      </c>
+      <c r="D25" s="69" t="s">
         <v>162</v>
       </c>
-      <c r="D25" s="69" t="s">
+      <c r="E25" s="69" t="s">
         <v>163</v>
       </c>
-      <c r="E25" s="69" t="s">
+      <c r="F25" s="69" t="s">
         <v>164</v>
       </c>
-      <c r="F25" s="69" t="s">
+      <c r="G25" s="69" t="s">
         <v>165</v>
       </c>
-      <c r="G25" s="69" t="s">
+      <c r="H25" s="69" t="s">
         <v>166</v>
-      </c>
-      <c r="H25" s="69" t="s">
-        <v>167</v>
       </c>
       <c r="I25" s="93"/>
       <c r="J25" s="94"/>
     </row>
     <row r="26" spans="1:10" s="59" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A26" s="111"/>
+      <c r="A26" s="103"/>
       <c r="B26" s="109" t="s">
+        <v>167</v>
+      </c>
+      <c r="C26" s="73" t="s">
         <v>168</v>
       </c>
-      <c r="C26" s="73" t="s">
+      <c r="D26" s="67" t="s">
         <v>169</v>
       </c>
-      <c r="D26" s="67" t="s">
+      <c r="E26" s="67" t="s">
         <v>170</v>
       </c>
-      <c r="E26" s="67" t="s">
+      <c r="F26" s="67" t="s">
         <v>171</v>
       </c>
-      <c r="F26" s="67" t="s">
+      <c r="G26" s="67" t="s">
         <v>172</v>
       </c>
-      <c r="G26" s="67" t="s">
+      <c r="H26" s="74" t="s">
         <v>173</v>
-      </c>
-      <c r="H26" s="74" t="s">
-        <v>174</v>
       </c>
       <c r="I26" s="93"/>
       <c r="J26" s="94"/>
     </row>
     <row r="27" spans="1:10" s="59" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A27" s="111"/>
-      <c r="B27" s="113"/>
+      <c r="A27" s="103"/>
+      <c r="B27" s="111"/>
       <c r="C27" s="73" t="s">
+        <v>174</v>
+      </c>
+      <c r="D27" s="67" t="s">
         <v>175</v>
       </c>
-      <c r="D27" s="67" t="s">
+      <c r="E27" s="67" t="s">
         <v>176</v>
       </c>
-      <c r="E27" s="67" t="s">
+      <c r="F27" s="67" t="s">
         <v>177</v>
       </c>
-      <c r="F27" s="67" t="s">
+      <c r="G27" s="67" t="s">
         <v>178</v>
       </c>
-      <c r="G27" s="67" t="s">
+      <c r="H27" s="74" t="s">
         <v>179</v>
-      </c>
-      <c r="H27" s="74" t="s">
-        <v>180</v>
       </c>
       <c r="I27" s="93"/>
       <c r="J27" s="94"/>
     </row>
     <row r="28" spans="1:10" s="59" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A28" s="111"/>
-      <c r="B28" s="113"/>
+      <c r="A28" s="103"/>
+      <c r="B28" s="111"/>
       <c r="C28" s="73" t="s">
+        <v>180</v>
+      </c>
+      <c r="D28" s="67" t="s">
         <v>181</v>
       </c>
-      <c r="D28" s="67" t="s">
+      <c r="E28" s="67" t="s">
         <v>182</v>
       </c>
-      <c r="E28" s="67" t="s">
+      <c r="F28" s="67" t="s">
         <v>183</v>
       </c>
-      <c r="F28" s="67" t="s">
+      <c r="G28" s="67" t="s">
         <v>184</v>
       </c>
-      <c r="G28" s="67" t="s">
+      <c r="H28" s="74" t="s">
         <v>185</v>
-      </c>
-      <c r="H28" s="74" t="s">
-        <v>186</v>
       </c>
       <c r="I28" s="93"/>
       <c r="J28" s="94"/>
     </row>
     <row r="29" spans="1:10" s="59" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A29" s="111"/>
-      <c r="B29" s="113"/>
+      <c r="A29" s="103"/>
+      <c r="B29" s="111"/>
       <c r="C29" s="73" t="s">
+        <v>186</v>
+      </c>
+      <c r="D29" s="67" t="s">
         <v>187</v>
       </c>
-      <c r="D29" s="67" t="s">
+      <c r="E29" s="67" t="s">
         <v>188</v>
       </c>
-      <c r="E29" s="67" t="s">
+      <c r="F29" s="67" t="s">
         <v>189</v>
       </c>
-      <c r="F29" s="67" t="s">
+      <c r="G29" s="67" t="s">
         <v>190</v>
       </c>
-      <c r="G29" s="67" t="s">
+      <c r="H29" s="74" t="s">
         <v>191</v>
-      </c>
-      <c r="H29" s="74" t="s">
-        <v>192</v>
       </c>
       <c r="I29" s="93"/>
       <c r="J29" s="94"/>
     </row>
     <row r="30" spans="1:10" s="59" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A30" s="111"/>
-      <c r="B30" s="113"/>
+      <c r="A30" s="103"/>
+      <c r="B30" s="111"/>
       <c r="C30" s="73" t="s">
+        <v>192</v>
+      </c>
+      <c r="D30" s="67" t="s">
         <v>193</v>
       </c>
-      <c r="D30" s="67" t="s">
+      <c r="E30" s="67" t="s">
         <v>194</v>
       </c>
-      <c r="E30" s="67" t="s">
+      <c r="F30" s="67" t="s">
         <v>195</v>
       </c>
-      <c r="F30" s="67" t="s">
+      <c r="G30" s="67" t="s">
         <v>196</v>
       </c>
-      <c r="G30" s="67" t="s">
+      <c r="H30" s="74" t="s">
         <v>197</v>
-      </c>
-      <c r="H30" s="74" t="s">
-        <v>198</v>
       </c>
       <c r="I30" s="93"/>
       <c r="J30" s="94"/>
     </row>
     <row r="31" spans="1:10" s="59" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A31" s="111"/>
-      <c r="B31" s="113"/>
+      <c r="A31" s="103"/>
+      <c r="B31" s="111"/>
       <c r="C31" s="73" t="s">
+        <v>198</v>
+      </c>
+      <c r="D31" s="67" t="s">
         <v>199</v>
       </c>
-      <c r="D31" s="67" t="s">
+      <c r="E31" s="67" t="s">
         <v>200</v>
       </c>
-      <c r="E31" s="67" t="s">
+      <c r="F31" s="67" t="s">
         <v>201</v>
       </c>
-      <c r="F31" s="67" t="s">
+      <c r="G31" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="G31" s="67" t="s">
+      <c r="H31" s="74" t="s">
         <v>203</v>
-      </c>
-      <c r="H31" s="74" t="s">
-        <v>204</v>
       </c>
       <c r="I31" s="93"/>
       <c r="J31" s="94"/>
     </row>
     <row r="32" spans="1:10" s="59" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A32" s="111"/>
-      <c r="B32" s="113"/>
+      <c r="A32" s="103"/>
+      <c r="B32" s="111"/>
       <c r="C32" s="73" t="s">
+        <v>204</v>
+      </c>
+      <c r="D32" s="67" t="s">
         <v>205</v>
       </c>
-      <c r="D32" s="67" t="s">
+      <c r="E32" s="67" t="s">
         <v>206</v>
       </c>
-      <c r="E32" s="67" t="s">
+      <c r="F32" s="67" t="s">
         <v>207</v>
       </c>
-      <c r="F32" s="67" t="s">
+      <c r="G32" s="67" t="s">
         <v>208</v>
       </c>
-      <c r="G32" s="67" t="s">
+      <c r="H32" s="74" t="s">
         <v>209</v>
-      </c>
-      <c r="H32" s="74" t="s">
-        <v>210</v>
       </c>
       <c r="I32" s="93"/>
       <c r="J32" s="94"/>
     </row>
     <row r="33" spans="1:10" s="59" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A33" s="111"/>
-      <c r="B33" s="113"/>
+      <c r="A33" s="103"/>
+      <c r="B33" s="111"/>
       <c r="C33" s="73" t="s">
+        <v>210</v>
+      </c>
+      <c r="D33" s="67" t="s">
         <v>211</v>
       </c>
-      <c r="D33" s="67" t="s">
+      <c r="E33" s="67" t="s">
         <v>212</v>
       </c>
-      <c r="E33" s="67" t="s">
+      <c r="F33" s="67" t="s">
         <v>213</v>
       </c>
-      <c r="F33" s="67" t="s">
+      <c r="G33" s="67" t="s">
         <v>214</v>
       </c>
-      <c r="G33" s="67" t="s">
+      <c r="H33" s="74" t="s">
         <v>215</v>
-      </c>
-      <c r="H33" s="74" t="s">
-        <v>216</v>
       </c>
       <c r="I33" s="93"/>
       <c r="J33" s="94"/>
     </row>
     <row r="34" spans="1:10" s="59" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A34" s="111"/>
-      <c r="B34" s="113"/>
+      <c r="A34" s="103"/>
+      <c r="B34" s="111"/>
       <c r="C34" s="70" t="s">
+        <v>216</v>
+      </c>
+      <c r="D34" s="69" t="s">
         <v>217</v>
       </c>
-      <c r="D34" s="69" t="s">
+      <c r="E34" s="69" t="s">
         <v>218</v>
       </c>
-      <c r="E34" s="69" t="s">
+      <c r="F34" s="69" t="s">
         <v>219</v>
       </c>
-      <c r="F34" s="69" t="s">
+      <c r="G34" s="69" t="s">
         <v>220</v>
       </c>
-      <c r="G34" s="69" t="s">
+      <c r="H34" s="69" t="s">
         <v>221</v>
-      </c>
-      <c r="H34" s="69" t="s">
-        <v>222</v>
       </c>
       <c r="I34" s="93"/>
       <c r="J34" s="94"/>
     </row>
     <row r="35" spans="1:10" s="59" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A35" s="111"/>
+      <c r="A35" s="103"/>
       <c r="B35" s="110" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C35" s="110"/>
       <c r="D35" s="69" t="s">
+        <v>223</v>
+      </c>
+      <c r="E35" s="69" t="s">
         <v>224</v>
       </c>
-      <c r="E35" s="69" t="s">
+      <c r="F35" s="69" t="s">
         <v>225</v>
       </c>
-      <c r="F35" s="69" t="s">
+      <c r="G35" s="69" t="s">
         <v>226</v>
       </c>
-      <c r="G35" s="69" t="s">
+      <c r="H35" s="69" t="s">
         <v>227</v>
-      </c>
-      <c r="H35" s="69" t="s">
-        <v>228</v>
       </c>
       <c r="I35" s="95"/>
       <c r="J35" s="94"/>
     </row>
     <row r="36" spans="1:10" s="59" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A36" s="111" t="s">
+      <c r="A36" s="103" t="s">
+        <v>228</v>
+      </c>
+      <c r="B36" s="106" t="s">
         <v>229</v>
-      </c>
-      <c r="B36" s="106" t="s">
-        <v>230</v>
       </c>
       <c r="C36" s="106"/>
       <c r="D36" s="75"/>
@@ -4475,15 +4446,15 @@
       <c r="F36" s="75"/>
       <c r="G36" s="75"/>
       <c r="H36" s="67" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I36" s="75"/>
       <c r="J36" s="96"/>
     </row>
     <row r="37" spans="1:10" s="59" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A37" s="111"/>
+      <c r="A37" s="103"/>
       <c r="B37" s="106" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C37" s="106"/>
       <c r="D37" s="75"/>
@@ -4491,15 +4462,15 @@
       <c r="F37" s="75"/>
       <c r="G37" s="75"/>
       <c r="H37" s="69" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I37" s="75"/>
       <c r="J37" s="96"/>
     </row>
     <row r="38" spans="1:10" s="59" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A38" s="111"/>
+      <c r="A38" s="103"/>
       <c r="B38" s="106" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C38" s="106"/>
       <c r="D38" s="75"/>
@@ -4507,15 +4478,15 @@
       <c r="F38" s="75"/>
       <c r="G38" s="75"/>
       <c r="H38" s="67" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I38" s="75"/>
       <c r="J38" s="96"/>
     </row>
     <row r="39" spans="1:10" s="59" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A39" s="111"/>
+      <c r="A39" s="103"/>
       <c r="B39" s="106" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C39" s="106"/>
       <c r="D39" s="75"/>
@@ -4523,15 +4494,15 @@
       <c r="F39" s="75"/>
       <c r="G39" s="75"/>
       <c r="H39" s="67" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I39" s="75"/>
       <c r="J39" s="96"/>
     </row>
     <row r="40" spans="1:10" s="59" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A40" s="111"/>
+      <c r="A40" s="103"/>
       <c r="B40" s="106" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C40" s="106"/>
       <c r="D40" s="75"/>
@@ -4539,221 +4510,221 @@
       <c r="F40" s="75"/>
       <c r="G40" s="75"/>
       <c r="H40" s="67" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I40" s="75"/>
       <c r="J40" s="96"/>
     </row>
     <row r="41" spans="1:10" s="59" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A41" s="111"/>
-      <c r="B41" s="107" t="s">
-        <v>240</v>
-      </c>
-      <c r="C41" s="107"/>
+      <c r="A41" s="103"/>
+      <c r="B41" s="105" t="s">
+        <v>239</v>
+      </c>
+      <c r="C41" s="105"/>
       <c r="D41" s="75"/>
       <c r="E41" s="75"/>
       <c r="F41" s="75"/>
       <c r="G41" s="75"/>
       <c r="H41" s="69" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I41" s="75"/>
       <c r="J41" s="96"/>
     </row>
     <row r="42" spans="1:10" s="59" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A42" s="111" t="s">
+      <c r="A42" s="103" t="s">
+        <v>241</v>
+      </c>
+      <c r="B42" s="106" t="s">
         <v>242</v>
-      </c>
-      <c r="B42" s="106" t="s">
-        <v>243</v>
       </c>
       <c r="C42" s="106"/>
       <c r="D42" s="67" t="s">
+        <v>243</v>
+      </c>
+      <c r="E42" s="67" t="s">
         <v>244</v>
       </c>
-      <c r="E42" s="67" t="s">
+      <c r="F42" s="67" t="s">
         <v>245</v>
       </c>
-      <c r="F42" s="67" t="s">
+      <c r="G42" s="67" t="s">
         <v>246</v>
       </c>
-      <c r="G42" s="67" t="s">
+      <c r="H42" s="68" t="s">
         <v>247</v>
-      </c>
-      <c r="H42" s="68" t="s">
-        <v>248</v>
       </c>
       <c r="I42" s="95"/>
       <c r="J42" s="97"/>
     </row>
     <row r="43" spans="1:10" s="59" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A43" s="111"/>
+      <c r="A43" s="103"/>
       <c r="B43" s="106" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C43" s="106"/>
       <c r="D43" s="67" t="s">
+        <v>249</v>
+      </c>
+      <c r="E43" s="67" t="s">
         <v>250</v>
       </c>
-      <c r="E43" s="67" t="s">
+      <c r="F43" s="67" t="s">
         <v>251</v>
       </c>
-      <c r="F43" s="67" t="s">
+      <c r="G43" s="67" t="s">
         <v>252</v>
       </c>
-      <c r="G43" s="67" t="s">
+      <c r="H43" s="68" t="s">
         <v>253</v>
-      </c>
-      <c r="H43" s="68" t="s">
-        <v>254</v>
       </c>
       <c r="I43" s="95"/>
       <c r="J43" s="97"/>
     </row>
     <row r="44" spans="1:10" s="59" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A44" s="111"/>
+      <c r="A44" s="103"/>
       <c r="B44" s="106" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C44" s="106"/>
       <c r="D44" s="67" t="s">
+        <v>255</v>
+      </c>
+      <c r="E44" s="67" t="s">
         <v>256</v>
       </c>
-      <c r="E44" s="67" t="s">
+      <c r="F44" s="67" t="s">
         <v>257</v>
       </c>
-      <c r="F44" s="67" t="s">
+      <c r="G44" s="67" t="s">
         <v>258</v>
       </c>
-      <c r="G44" s="67" t="s">
+      <c r="H44" s="68" t="s">
         <v>259</v>
-      </c>
-      <c r="H44" s="68" t="s">
-        <v>260</v>
       </c>
       <c r="I44" s="95"/>
       <c r="J44" s="97"/>
     </row>
     <row r="45" spans="1:10" s="59" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A45" s="111"/>
+      <c r="A45" s="103"/>
       <c r="B45" s="106" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C45" s="106"/>
       <c r="D45" s="67" t="s">
+        <v>261</v>
+      </c>
+      <c r="E45" s="67" t="s">
         <v>262</v>
       </c>
-      <c r="E45" s="67" t="s">
+      <c r="F45" s="67" t="s">
         <v>263</v>
       </c>
-      <c r="F45" s="67" t="s">
+      <c r="G45" s="67" t="s">
         <v>264</v>
       </c>
-      <c r="G45" s="67" t="s">
+      <c r="H45" s="68" t="s">
         <v>265</v>
-      </c>
-      <c r="H45" s="68" t="s">
-        <v>266</v>
       </c>
       <c r="I45" s="95"/>
       <c r="J45" s="97"/>
     </row>
     <row r="46" spans="1:10" s="59" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A46" s="111"/>
-      <c r="B46" s="107" t="s">
+      <c r="A46" s="103"/>
+      <c r="B46" s="105" t="s">
+        <v>266</v>
+      </c>
+      <c r="C46" s="105"/>
+      <c r="D46" s="69" t="s">
         <v>267</v>
       </c>
-      <c r="C46" s="107"/>
-      <c r="D46" s="69" t="s">
+      <c r="E46" s="69" t="s">
         <v>268</v>
       </c>
-      <c r="E46" s="69" t="s">
+      <c r="F46" s="69" t="s">
         <v>269</v>
       </c>
-      <c r="F46" s="69" t="s">
+      <c r="G46" s="69" t="s">
         <v>270</v>
       </c>
-      <c r="G46" s="69" t="s">
+      <c r="H46" s="69" t="s">
         <v>271</v>
-      </c>
-      <c r="H46" s="69" t="s">
-        <v>272</v>
       </c>
       <c r="I46" s="95"/>
       <c r="J46" s="97"/>
     </row>
     <row r="47" spans="1:10" s="59" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A47" s="111" t="s">
+      <c r="A47" s="103" t="s">
+        <v>272</v>
+      </c>
+      <c r="B47" s="105" t="s">
         <v>273</v>
       </c>
-      <c r="B47" s="107" t="s">
+      <c r="C47" s="105"/>
+      <c r="D47" s="67" t="s">
         <v>274</v>
       </c>
-      <c r="C47" s="107"/>
-      <c r="D47" s="67" t="s">
+      <c r="E47" s="67" t="s">
         <v>275</v>
       </c>
-      <c r="E47" s="67" t="s">
+      <c r="F47" s="67" t="s">
         <v>276</v>
       </c>
-      <c r="F47" s="67" t="s">
+      <c r="G47" s="67" t="s">
         <v>277</v>
       </c>
-      <c r="G47" s="67" t="s">
+      <c r="H47" s="67" t="s">
         <v>278</v>
-      </c>
-      <c r="H47" s="67" t="s">
-        <v>279</v>
       </c>
       <c r="I47" s="95"/>
       <c r="J47" s="97"/>
     </row>
     <row r="48" spans="1:10" s="59" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A48" s="112"/>
-      <c r="B48" s="119" t="s">
+      <c r="A48" s="104"/>
+      <c r="B48" s="107" t="s">
+        <v>279</v>
+      </c>
+      <c r="C48" s="107"/>
+      <c r="D48" s="76" t="s">
         <v>280</v>
       </c>
-      <c r="C48" s="119"/>
-      <c r="D48" s="76" t="s">
+      <c r="E48" s="76" t="s">
         <v>281</v>
       </c>
-      <c r="E48" s="76" t="s">
+      <c r="F48" s="76" t="s">
         <v>282</v>
       </c>
-      <c r="F48" s="76" t="s">
+      <c r="G48" s="76" t="s">
         <v>283</v>
       </c>
-      <c r="G48" s="76" t="s">
+      <c r="H48" s="76" t="s">
         <v>284</v>
-      </c>
-      <c r="H48" s="76" t="s">
-        <v>285</v>
       </c>
       <c r="I48" s="98"/>
       <c r="J48" s="99"/>
     </row>
     <row r="49" spans="1:10">
-      <c r="A49" s="120" t="s">
-        <v>286</v>
-      </c>
-      <c r="B49" s="120"/>
+      <c r="A49" s="102" t="s">
+        <v>285</v>
+      </c>
+      <c r="B49" s="102"/>
       <c r="C49" s="77"/>
       <c r="D49" s="78"/>
       <c r="E49" s="79" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F49" s="78"/>
       <c r="G49" s="80"/>
       <c r="H49" s="78"/>
       <c r="I49" s="100" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J49" s="101"/>
     </row>
     <row r="50" spans="1:10">
       <c r="A50" s="77"/>
       <c r="B50" s="81" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C50" s="82"/>
       <c r="F50" s="83"/>
@@ -4765,7 +4736,7 @@
     <row r="51" spans="1:10">
       <c r="A51" s="50"/>
       <c r="B51" s="82" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C51" s="82"/>
       <c r="D51" s="84"/>
@@ -4779,11 +4750,34 @@
     <row r="52" spans="1:10">
       <c r="A52" s="86"/>
       <c r="B52" s="83" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="39">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="A3:C4"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B13:B16"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B20:B25"/>
+    <mergeCell ref="B26:B34"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B40:C40"/>
     <mergeCell ref="A49:B49"/>
     <mergeCell ref="A5:A7"/>
     <mergeCell ref="A8:A12"/>
@@ -4800,29 +4794,6 @@
     <mergeCell ref="B46:C46"/>
     <mergeCell ref="B47:C47"/>
     <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B13:B16"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B20:B25"/>
-    <mergeCell ref="B26:B34"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="A3:C4"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <dataValidations count="3">
@@ -4845,7 +4816,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E176"/>
+  <dimension ref="A1:E173"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="10.375" style="4" customWidth="1"/>
@@ -4857,2184 +4828,2129 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30.95" customHeight="1">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="144" t="s">
+        <v>291</v>
+      </c>
+      <c r="B1" s="144"/>
+      <c r="C1" s="144"/>
+      <c r="D1" s="145"/>
+      <c r="E1" s="145"/>
+    </row>
+    <row r="2" spans="1:5" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A2" s="146" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="146"/>
+      <c r="C2" s="6" t="s">
         <v>292</v>
-      </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="122"/>
-      <c r="E1" s="122"/>
-    </row>
-    <row r="2" spans="1:5" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A2" s="123" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="123"/>
-      <c r="C2" s="6" t="s">
-        <v>293</v>
       </c>
       <c r="D2" s="7"/>
       <c r="E2" s="8" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" s="2" customFormat="1" ht="13.5">
+      <c r="A3" s="152" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="153"/>
+      <c r="C3" s="153"/>
+      <c r="D3" s="148" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="150" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" s="2" customFormat="1" ht="13.5">
+      <c r="A4" s="154"/>
+      <c r="B4" s="155"/>
+      <c r="C4" s="155"/>
+      <c r="D4" s="149"/>
+      <c r="E4" s="151"/>
+    </row>
+    <row r="5" spans="1:5" s="2" customFormat="1" ht="17.25" customHeight="1">
+      <c r="A5" s="125" t="s">
+        <v>293</v>
+      </c>
+      <c r="B5" s="121" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" s="2" customFormat="1" ht="13.5">
-      <c r="A3" s="149" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="150"/>
-      <c r="C3" s="150"/>
-      <c r="D3" s="145" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="147" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" s="2" customFormat="1" ht="13.5">
-      <c r="A4" s="151"/>
-      <c r="B4" s="152"/>
-      <c r="C4" s="152"/>
-      <c r="D4" s="146"/>
-      <c r="E4" s="148"/>
-    </row>
-    <row r="5" spans="1:5" s="2" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A5" s="136" t="s">
+      <c r="C5" s="147"/>
+      <c r="D5" s="10" t="s">
         <v>295</v>
       </c>
-      <c r="B5" s="124" t="s">
+      <c r="E5" s="11" t="s">
         <v>296</v>
       </c>
-      <c r="C5" s="125"/>
-      <c r="D5" s="10" t="s">
+    </row>
+    <row r="6" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A6" s="126"/>
+      <c r="B6" s="123" t="s">
         <v>297</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="C6" s="12" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A6" s="137"/>
-      <c r="B6" s="126" t="s">
+      <c r="D6" s="13" t="s">
         <v>299</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="E6" s="14" t="s">
         <v>300</v>
       </c>
-      <c r="D6" s="13" t="s">
+    </row>
+    <row r="7" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A7" s="126"/>
+      <c r="B7" s="123"/>
+      <c r="C7" s="12" t="s">
         <v>301</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="D7" s="13" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A7" s="137"/>
-      <c r="B7" s="126"/>
-      <c r="C7" s="12" t="s">
+      <c r="E7" s="14" t="s">
         <v>303</v>
       </c>
-      <c r="D7" s="13" t="s">
+    </row>
+    <row r="8" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A8" s="126"/>
+      <c r="B8" s="123"/>
+      <c r="C8" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="D8" s="13" t="s">
         <v>305</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A8" s="137"/>
-      <c r="B8" s="126"/>
-      <c r="C8" s="12" t="s">
+      <c r="E8" s="14" t="s">
         <v>306</v>
       </c>
-      <c r="D8" s="13" t="s">
+    </row>
+    <row r="9" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A9" s="126"/>
+      <c r="B9" s="123"/>
+      <c r="C9" s="12" t="s">
         <v>307</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="D9" s="13" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A9" s="137"/>
-      <c r="B9" s="126"/>
-      <c r="C9" s="12" t="s">
+      <c r="E9" s="14" t="s">
         <v>309</v>
       </c>
-      <c r="D9" s="13" t="s">
+    </row>
+    <row r="10" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A10" s="126"/>
+      <c r="B10" s="123"/>
+      <c r="C10" s="12" t="s">
         <v>310</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="D10" s="13" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A10" s="137"/>
-      <c r="B10" s="126"/>
-      <c r="C10" s="12" t="s">
+      <c r="E10" s="14" t="s">
         <v>312</v>
       </c>
-      <c r="D10" s="13" t="s">
+    </row>
+    <row r="11" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A11" s="126"/>
+      <c r="B11" s="123"/>
+      <c r="C11" s="9" t="s">
         <v>313</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="D11" s="15" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A11" s="137"/>
-      <c r="B11" s="126"/>
-      <c r="C11" s="9" t="s">
+      <c r="E11" s="16" t="s">
         <v>315</v>
       </c>
-      <c r="D11" s="15" t="s">
+    </row>
+    <row r="12" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A12" s="126"/>
+      <c r="B12" s="123" t="s">
         <v>316</v>
       </c>
-      <c r="E11" s="16" t="s">
+      <c r="C12" s="12" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A12" s="137"/>
-      <c r="B12" s="126" t="s">
+      <c r="D12" s="13" t="s">
         <v>318</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="E12" s="14" t="s">
         <v>319</v>
       </c>
-      <c r="D12" s="13" t="s">
+    </row>
+    <row r="13" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A13" s="126"/>
+      <c r="B13" s="123"/>
+      <c r="C13" s="12" t="s">
         <v>320</v>
       </c>
-      <c r="E12" s="14" t="s">
+      <c r="D13" s="13" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A13" s="137"/>
-      <c r="B13" s="126"/>
-      <c r="C13" s="12" t="s">
+      <c r="E13" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="D13" s="13" t="s">
+    </row>
+    <row r="14" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A14" s="126"/>
+      <c r="B14" s="123"/>
+      <c r="C14" s="9" t="s">
         <v>323</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="D14" s="17" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A14" s="137"/>
-      <c r="B14" s="126"/>
-      <c r="C14" s="9" t="s">
+      <c r="E14" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="D14" s="17" t="s">
+    </row>
+    <row r="15" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A15" s="126"/>
+      <c r="B15" s="123" t="s">
         <v>326</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="C15" s="12" t="s">
         <v>327</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A15" s="137"/>
-      <c r="B15" s="126" t="s">
+      <c r="D15" s="13" t="s">
         <v>328</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="E15" s="14" t="s">
         <v>329</v>
       </c>
-      <c r="D15" s="13" t="s">
+    </row>
+    <row r="16" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A16" s="126"/>
+      <c r="B16" s="123"/>
+      <c r="C16" s="12" t="s">
         <v>330</v>
       </c>
-      <c r="E15" s="14" t="s">
+      <c r="D16" s="13" t="s">
         <v>331</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A16" s="137"/>
-      <c r="B16" s="126"/>
-      <c r="C16" s="12" t="s">
+      <c r="E16" s="14" t="s">
         <v>332</v>
       </c>
-      <c r="D16" s="13" t="s">
+    </row>
+    <row r="17" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A17" s="126"/>
+      <c r="B17" s="123"/>
+      <c r="C17" s="9" t="s">
         <v>333</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="D17" s="17" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A17" s="137"/>
-      <c r="B17" s="126"/>
-      <c r="C17" s="9" t="s">
+      <c r="E17" s="18" t="s">
         <v>335</v>
       </c>
-      <c r="D17" s="17" t="s">
+    </row>
+    <row r="18" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A18" s="126"/>
+      <c r="B18" s="132" t="s">
         <v>336</v>
       </c>
-      <c r="E17" s="18" t="s">
+      <c r="C18" s="12" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A18" s="137"/>
-      <c r="B18" s="131" t="s">
+      <c r="D18" s="13" t="s">
         <v>338</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="E18" s="14" t="s">
         <v>339</v>
       </c>
-      <c r="D18" s="13" t="s">
+    </row>
+    <row r="19" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A19" s="126"/>
+      <c r="B19" s="132"/>
+      <c r="C19" s="12" t="s">
         <v>340</v>
       </c>
-      <c r="E18" s="14" t="s">
+      <c r="D19" s="13" t="s">
         <v>341</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A19" s="137"/>
-      <c r="B19" s="131"/>
-      <c r="C19" s="12" t="s">
+      <c r="E19" s="14" t="s">
         <v>342</v>
       </c>
-      <c r="D19" s="13" t="s">
+    </row>
+    <row r="20" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A20" s="126"/>
+      <c r="B20" s="132"/>
+      <c r="C20" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="E19" s="14" t="s">
+      <c r="D20" s="13" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A20" s="137"/>
-      <c r="B20" s="131"/>
-      <c r="C20" s="12" t="s">
+      <c r="E20" s="14" t="s">
         <v>345</v>
       </c>
-      <c r="D20" s="13" t="s">
+    </row>
+    <row r="21" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A21" s="126"/>
+      <c r="B21" s="132"/>
+      <c r="C21" s="12" t="s">
         <v>346</v>
       </c>
-      <c r="E20" s="14" t="s">
+      <c r="D21" s="13" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A21" s="137"/>
-      <c r="B21" s="131"/>
-      <c r="C21" s="12" t="s">
+      <c r="E21" s="14" t="s">
         <v>348</v>
       </c>
-      <c r="D21" s="13" t="s">
+    </row>
+    <row r="22" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A22" s="126"/>
+      <c r="B22" s="132"/>
+      <c r="C22" s="12" t="s">
         <v>349</v>
       </c>
-      <c r="E21" s="14" t="s">
+      <c r="D22" s="13" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A22" s="137"/>
-      <c r="B22" s="131"/>
-      <c r="C22" s="12" t="s">
+      <c r="E22" s="14" t="s">
         <v>351</v>
       </c>
-      <c r="D22" s="13" t="s">
+    </row>
+    <row r="23" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A23" s="126"/>
+      <c r="B23" s="132"/>
+      <c r="C23" s="12" t="s">
         <v>352</v>
       </c>
-      <c r="E22" s="14" t="s">
+      <c r="D23" s="13" t="s">
         <v>353</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A23" s="137"/>
-      <c r="B23" s="131"/>
-      <c r="C23" s="12" t="s">
+      <c r="E23" s="14" t="s">
         <v>354</v>
       </c>
-      <c r="D23" s="13" t="s">
+    </row>
+    <row r="24" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A24" s="126"/>
+      <c r="B24" s="132"/>
+      <c r="C24" s="12" t="s">
         <v>355</v>
       </c>
-      <c r="E23" s="14" t="s">
+      <c r="D24" s="13" t="s">
         <v>356</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A24" s="137"/>
-      <c r="B24" s="131"/>
-      <c r="C24" s="12" t="s">
+      <c r="E24" s="14" t="s">
         <v>357</v>
       </c>
-      <c r="D24" s="13" t="s">
+    </row>
+    <row r="25" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A25" s="126"/>
+      <c r="B25" s="132"/>
+      <c r="C25" s="12" t="s">
         <v>358</v>
       </c>
-      <c r="E24" s="14" t="s">
+      <c r="D25" s="13" t="s">
         <v>359</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A25" s="137"/>
-      <c r="B25" s="131"/>
-      <c r="C25" s="12" t="s">
+      <c r="E25" s="14" t="s">
         <v>360</v>
       </c>
-      <c r="D25" s="13" t="s">
+    </row>
+    <row r="26" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A26" s="126"/>
+      <c r="B26" s="132"/>
+      <c r="C26" s="12" t="s">
         <v>361</v>
       </c>
-      <c r="E25" s="14" t="s">
+      <c r="D26" s="13" t="s">
         <v>362</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A26" s="137"/>
-      <c r="B26" s="131"/>
-      <c r="C26" s="12" t="s">
+      <c r="E26" s="14" t="s">
         <v>363</v>
       </c>
-      <c r="D26" s="13" t="s">
+    </row>
+    <row r="27" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A27" s="126"/>
+      <c r="B27" s="132"/>
+      <c r="C27" s="12" t="s">
         <v>364</v>
       </c>
-      <c r="E26" s="14" t="s">
+      <c r="D27" s="13" t="s">
         <v>365</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A27" s="137"/>
-      <c r="B27" s="131"/>
-      <c r="C27" s="12" t="s">
+      <c r="E27" s="14" t="s">
         <v>366</v>
       </c>
-      <c r="D27" s="13" t="s">
+    </row>
+    <row r="28" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A28" s="126"/>
+      <c r="B28" s="132"/>
+      <c r="C28" s="12" t="s">
         <v>367</v>
       </c>
-      <c r="E27" s="14" t="s">
+      <c r="D28" s="13" t="s">
         <v>368</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A28" s="137"/>
-      <c r="B28" s="131"/>
-      <c r="C28" s="12" t="s">
+      <c r="E28" s="14" t="s">
         <v>369</v>
       </c>
-      <c r="D28" s="13" t="s">
+    </row>
+    <row r="29" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A29" s="126"/>
+      <c r="B29" s="132"/>
+      <c r="C29" s="20" t="s">
         <v>370</v>
-      </c>
-      <c r="E28" s="14" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A29" s="137"/>
-      <c r="B29" s="131"/>
-      <c r="C29" s="20" t="s">
-        <v>372</v>
       </c>
       <c r="D29" s="21"/>
       <c r="E29" s="22"/>
     </row>
     <row r="30" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A30" s="137"/>
-      <c r="B30" s="131"/>
+      <c r="A30" s="126"/>
+      <c r="B30" s="132"/>
       <c r="C30" s="9" t="s">
+        <v>371</v>
+      </c>
+      <c r="D30" s="17" t="s">
+        <v>372</v>
+      </c>
+      <c r="E30" s="18" t="s">
         <v>373</v>
       </c>
-      <c r="D30" s="17" t="s">
+    </row>
+    <row r="31" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A31" s="126"/>
+      <c r="B31" s="132"/>
+      <c r="C31" s="12" t="s">
         <v>374</v>
       </c>
-      <c r="E30" s="18" t="s">
+      <c r="D31" s="13" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A31" s="137"/>
-      <c r="B31" s="131"/>
-      <c r="C31" s="12" t="s">
+      <c r="E31" s="14" t="s">
         <v>376</v>
       </c>
-      <c r="D31" s="13" t="s">
+    </row>
+    <row r="32" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A32" s="126"/>
+      <c r="B32" s="132"/>
+      <c r="C32" s="12" t="s">
         <v>377</v>
       </c>
-      <c r="E31" s="14" t="s">
+      <c r="D32" s="13" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A32" s="137"/>
-      <c r="B32" s="131"/>
-      <c r="C32" s="12" t="s">
+      <c r="E32" s="14" t="s">
         <v>379</v>
       </c>
-      <c r="D32" s="13" t="s">
+    </row>
+    <row r="33" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A33" s="126"/>
+      <c r="B33" s="132"/>
+      <c r="C33" s="12" t="s">
         <v>380</v>
       </c>
-      <c r="E32" s="14" t="s">
+      <c r="D33" s="13" t="s">
         <v>381</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A33" s="137"/>
-      <c r="B33" s="131"/>
-      <c r="C33" s="12" t="s">
+      <c r="E33" s="14" t="s">
         <v>382</v>
       </c>
-      <c r="D33" s="13" t="s">
+    </row>
+    <row r="34" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A34" s="126"/>
+      <c r="B34" s="123" t="s">
         <v>383</v>
       </c>
-      <c r="E33" s="14" t="s">
+      <c r="C34" s="12" t="s">
         <v>384</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A34" s="137"/>
-      <c r="B34" s="126" t="s">
+      <c r="D34" s="13" t="s">
         <v>385</v>
       </c>
-      <c r="C34" s="12" t="s">
+      <c r="E34" s="14" t="s">
         <v>386</v>
       </c>
-      <c r="D34" s="13" t="s">
+    </row>
+    <row r="35" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A35" s="126"/>
+      <c r="B35" s="123"/>
+      <c r="C35" s="20" t="s">
         <v>387</v>
-      </c>
-      <c r="E34" s="14" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A35" s="137"/>
-      <c r="B35" s="126"/>
-      <c r="C35" s="20" t="s">
-        <v>389</v>
       </c>
       <c r="D35" s="21"/>
       <c r="E35" s="22"/>
     </row>
     <row r="36" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A36" s="137"/>
-      <c r="B36" s="126"/>
+      <c r="A36" s="126"/>
+      <c r="B36" s="123"/>
       <c r="C36" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="D36" s="17" t="s">
+        <v>389</v>
+      </c>
+      <c r="E36" s="18" t="s">
         <v>390</v>
       </c>
-      <c r="D36" s="17" t="s">
+    </row>
+    <row r="37" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A37" s="126"/>
+      <c r="B37" s="123" t="s">
         <v>391</v>
       </c>
-      <c r="E36" s="18" t="s">
+      <c r="C37" s="12" t="s">
         <v>392</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A37" s="137"/>
-      <c r="B37" s="126" t="s">
+      <c r="D37" s="13" t="s">
         <v>393</v>
       </c>
-      <c r="C37" s="12" t="s">
+      <c r="E37" s="14" t="s">
         <v>394</v>
       </c>
-      <c r="D37" s="13" t="s">
+    </row>
+    <row r="38" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A38" s="126"/>
+      <c r="B38" s="123"/>
+      <c r="C38" s="19" t="s">
         <v>395</v>
       </c>
-      <c r="E37" s="14" t="s">
+      <c r="D38" s="13" t="s">
         <v>396</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A38" s="137"/>
-      <c r="B38" s="126"/>
-      <c r="C38" s="19" t="s">
+      <c r="E38" s="14" t="s">
         <v>397</v>
       </c>
-      <c r="D38" s="13" t="s">
+    </row>
+    <row r="39" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A39" s="126"/>
+      <c r="B39" s="123"/>
+      <c r="C39" s="12" t="s">
         <v>398</v>
       </c>
-      <c r="E38" s="14" t="s">
+      <c r="D39" s="13" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A39" s="137"/>
-      <c r="B39" s="126"/>
-      <c r="C39" s="12" t="s">
+      <c r="E39" s="14" t="s">
         <v>400</v>
       </c>
-      <c r="D39" s="13" t="s">
+    </row>
+    <row r="40" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A40" s="126"/>
+      <c r="B40" s="123"/>
+      <c r="C40" s="9" t="s">
         <v>401</v>
       </c>
-      <c r="E39" s="14" t="s">
+      <c r="D40" s="17" t="s">
         <v>402</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A40" s="137"/>
-      <c r="B40" s="126"/>
-      <c r="C40" s="9" t="s">
+      <c r="E40" s="18" t="s">
         <v>403</v>
       </c>
-      <c r="D40" s="17" t="s">
+    </row>
+    <row r="41" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A41" s="126"/>
+      <c r="B41" s="139" t="s">
         <v>404</v>
       </c>
-      <c r="E40" s="18" t="s">
+      <c r="C41" s="12" t="s">
         <v>405</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A41" s="137"/>
-      <c r="B41" s="129" t="s">
+      <c r="D41" s="13" t="s">
         <v>406</v>
       </c>
-      <c r="C41" s="12" t="s">
+      <c r="E41" s="14" t="s">
         <v>407</v>
       </c>
-      <c r="D41" s="13" t="s">
+    </row>
+    <row r="42" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A42" s="126"/>
+      <c r="B42" s="139"/>
+      <c r="C42" s="12" t="s">
         <v>408</v>
       </c>
-      <c r="E41" s="14" t="s">
+      <c r="D42" s="13" t="s">
         <v>409</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A42" s="137"/>
-      <c r="B42" s="129"/>
-      <c r="C42" s="12" t="s">
+      <c r="E42" s="14" t="s">
         <v>410</v>
       </c>
-      <c r="D42" s="13" t="s">
+    </row>
+    <row r="43" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A43" s="126"/>
+      <c r="B43" s="139"/>
+      <c r="C43" s="12" t="s">
         <v>411</v>
       </c>
-      <c r="E42" s="14" t="s">
+      <c r="D43" s="13" t="s">
         <v>412</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A43" s="137"/>
-      <c r="B43" s="129"/>
-      <c r="C43" s="12" t="s">
+      <c r="E43" s="14" t="s">
         <v>413</v>
       </c>
-      <c r="D43" s="13" t="s">
+    </row>
+    <row r="44" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A44" s="126"/>
+      <c r="B44" s="139"/>
+      <c r="C44" s="12" t="s">
         <v>414</v>
       </c>
-      <c r="E43" s="14" t="s">
+      <c r="D44" s="13" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A44" s="137"/>
-      <c r="B44" s="129"/>
-      <c r="C44" s="12" t="s">
+      <c r="E44" s="14" t="s">
         <v>416</v>
       </c>
-      <c r="D44" s="13" t="s">
+    </row>
+    <row r="45" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A45" s="126"/>
+      <c r="B45" s="139"/>
+      <c r="C45" s="12" t="s">
         <v>417</v>
       </c>
-      <c r="E44" s="14" t="s">
+      <c r="D45" s="13" t="s">
         <v>418</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A45" s="137"/>
-      <c r="B45" s="129"/>
-      <c r="C45" s="12" t="s">
+      <c r="E45" s="14" t="s">
         <v>419</v>
       </c>
-      <c r="D45" s="13" t="s">
+    </row>
+    <row r="46" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A46" s="126"/>
+      <c r="B46" s="139"/>
+      <c r="C46" s="12" t="s">
         <v>420</v>
       </c>
-      <c r="E45" s="14" t="s">
+      <c r="D46" s="13" t="s">
         <v>421</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A46" s="137"/>
-      <c r="B46" s="129"/>
-      <c r="C46" s="12" t="s">
+      <c r="E46" s="14" t="s">
         <v>422</v>
       </c>
-      <c r="D46" s="13" t="s">
+    </row>
+    <row r="47" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A47" s="126"/>
+      <c r="B47" s="139"/>
+      <c r="C47" s="12" t="s">
         <v>423</v>
       </c>
-      <c r="E46" s="14" t="s">
+      <c r="D47" s="13" t="s">
         <v>424</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A47" s="137"/>
-      <c r="B47" s="129"/>
-      <c r="C47" s="12" t="s">
+      <c r="E47" s="14" t="s">
         <v>425</v>
       </c>
-      <c r="D47" s="13" t="s">
+    </row>
+    <row r="48" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A48" s="126"/>
+      <c r="B48" s="139"/>
+      <c r="C48" s="12" t="s">
         <v>426</v>
       </c>
-      <c r="E47" s="14" t="s">
+      <c r="D48" s="13" t="s">
         <v>427</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A48" s="137"/>
-      <c r="B48" s="129"/>
-      <c r="C48" s="12" t="s">
+      <c r="E48" s="14" t="s">
         <v>428</v>
       </c>
-      <c r="D48" s="13" t="s">
+    </row>
+    <row r="49" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A49" s="126"/>
+      <c r="B49" s="139"/>
+      <c r="C49" s="12" t="s">
         <v>429</v>
       </c>
-      <c r="E48" s="14" t="s">
+      <c r="D49" s="13" t="s">
         <v>430</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A49" s="137"/>
-      <c r="B49" s="129"/>
-      <c r="C49" s="12" t="s">
+      <c r="E49" s="14" t="s">
         <v>431</v>
       </c>
-      <c r="D49" s="13" t="s">
+    </row>
+    <row r="50" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A50" s="126"/>
+      <c r="B50" s="139"/>
+      <c r="C50" s="12" t="s">
         <v>432</v>
       </c>
-      <c r="E49" s="14" t="s">
+      <c r="D50" s="13" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A50" s="137"/>
-      <c r="B50" s="129"/>
-      <c r="C50" s="12" t="s">
+      <c r="E50" s="14" t="s">
         <v>434</v>
       </c>
-      <c r="D50" s="13" t="s">
+    </row>
+    <row r="51" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A51" s="126"/>
+      <c r="B51" s="139"/>
+      <c r="C51" s="12" t="s">
         <v>435</v>
       </c>
-      <c r="E50" s="14" t="s">
+      <c r="D51" s="13" t="s">
         <v>436</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A51" s="137"/>
-      <c r="B51" s="129"/>
-      <c r="C51" s="12" t="s">
+      <c r="E51" s="14" t="s">
         <v>437</v>
       </c>
-      <c r="D51" s="13" t="s">
+    </row>
+    <row r="52" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A52" s="126"/>
+      <c r="B52" s="139"/>
+      <c r="C52" s="12" t="s">
         <v>438</v>
       </c>
-      <c r="E51" s="14" t="s">
+      <c r="D52" s="13" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="52" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A52" s="137"/>
-      <c r="B52" s="129"/>
-      <c r="C52" s="12" t="s">
+      <c r="E52" s="14" t="s">
         <v>440</v>
       </c>
-      <c r="D52" s="13" t="s">
+    </row>
+    <row r="53" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A53" s="126"/>
+      <c r="B53" s="139"/>
+      <c r="C53" s="12" t="s">
         <v>441</v>
       </c>
-      <c r="E52" s="14" t="s">
+      <c r="D53" s="13" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="53" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A53" s="137"/>
-      <c r="B53" s="129"/>
-      <c r="C53" s="12" t="s">
+      <c r="E53" s="14" t="s">
         <v>443</v>
       </c>
-      <c r="D53" s="13" t="s">
+    </row>
+    <row r="54" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A54" s="126"/>
+      <c r="B54" s="139"/>
+      <c r="C54" s="23" t="s">
         <v>444</v>
       </c>
-      <c r="E53" s="14" t="s">
+      <c r="D54" s="17" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A54" s="137"/>
-      <c r="B54" s="129"/>
-      <c r="C54" s="23" t="s">
+      <c r="E54" s="18" t="s">
         <v>446</v>
       </c>
-      <c r="D54" s="17" t="s">
+    </row>
+    <row r="55" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A55" s="126"/>
+      <c r="B55" s="140"/>
+      <c r="C55" s="24" t="s">
         <v>447</v>
-      </c>
-      <c r="E54" s="18" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A55" s="137"/>
-      <c r="B55" s="130"/>
-      <c r="C55" s="24" t="s">
-        <v>449</v>
       </c>
       <c r="D55" s="21"/>
       <c r="E55" s="14" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A56" s="126"/>
+      <c r="B56" s="123" t="s">
+        <v>449</v>
+      </c>
+      <c r="C56" s="12" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A56" s="137"/>
-      <c r="B56" s="126" t="s">
+      <c r="D56" s="13" t="s">
         <v>451</v>
       </c>
-      <c r="C56" s="12" t="s">
+      <c r="E56" s="14" t="s">
         <v>452</v>
       </c>
-      <c r="D56" s="13" t="s">
+    </row>
+    <row r="57" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A57" s="126"/>
+      <c r="B57" s="123"/>
+      <c r="C57" s="24" t="s">
         <v>453</v>
       </c>
-      <c r="E56" s="14" t="s">
+      <c r="D57" s="13" t="s">
         <v>454</v>
       </c>
-    </row>
-    <row r="57" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A57" s="137"/>
-      <c r="B57" s="126"/>
-      <c r="C57" s="24" t="s">
+      <c r="E57" s="14" t="s">
         <v>455</v>
       </c>
-      <c r="D57" s="13" t="s">
+    </row>
+    <row r="58" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A58" s="126"/>
+      <c r="B58" s="123"/>
+      <c r="C58" s="12" t="s">
         <v>456</v>
       </c>
-      <c r="E57" s="14" t="s">
+      <c r="D58" s="13" t="s">
         <v>457</v>
       </c>
-    </row>
-    <row r="58" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A58" s="137"/>
-      <c r="B58" s="126"/>
-      <c r="C58" s="12" t="s">
+      <c r="E58" s="14" t="s">
         <v>458</v>
       </c>
-      <c r="D58" s="13" t="s">
+    </row>
+    <row r="59" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A59" s="126"/>
+      <c r="B59" s="123"/>
+      <c r="C59" s="12" t="s">
         <v>459</v>
       </c>
-      <c r="E58" s="14" t="s">
+      <c r="D59" s="13" t="s">
         <v>460</v>
       </c>
-    </row>
-    <row r="59" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A59" s="137"/>
-      <c r="B59" s="126"/>
-      <c r="C59" s="12" t="s">
+      <c r="E59" s="14" t="s">
         <v>461</v>
       </c>
-      <c r="D59" s="13" t="s">
+    </row>
+    <row r="60" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A60" s="126"/>
+      <c r="B60" s="123"/>
+      <c r="C60" s="9" t="s">
         <v>462</v>
       </c>
-      <c r="E59" s="14" t="s">
+      <c r="D60" s="17" t="s">
         <v>463</v>
       </c>
-    </row>
-    <row r="60" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A60" s="137"/>
-      <c r="B60" s="126"/>
-      <c r="C60" s="9" t="s">
+      <c r="E60" s="18" t="s">
         <v>464</v>
       </c>
-      <c r="D60" s="17" t="s">
+    </row>
+    <row r="61" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A61" s="126"/>
+      <c r="B61" s="123" t="s">
         <v>465</v>
       </c>
-      <c r="E60" s="18" t="s">
+      <c r="C61" s="12" t="s">
         <v>466</v>
       </c>
-    </row>
-    <row r="61" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A61" s="137"/>
-      <c r="B61" s="126" t="s">
+      <c r="D61" s="13" t="s">
         <v>467</v>
       </c>
-      <c r="C61" s="12" t="s">
+      <c r="E61" s="14" t="s">
         <v>468</v>
       </c>
-      <c r="D61" s="13" t="s">
+    </row>
+    <row r="62" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A62" s="126"/>
+      <c r="B62" s="123"/>
+      <c r="C62" s="12" t="s">
         <v>469</v>
       </c>
-      <c r="E61" s="14" t="s">
+      <c r="D62" s="13" t="s">
         <v>470</v>
       </c>
-    </row>
-    <row r="62" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A62" s="137"/>
-      <c r="B62" s="126"/>
-      <c r="C62" s="12" t="s">
+      <c r="E62" s="14" t="s">
         <v>471</v>
       </c>
-      <c r="D62" s="13" t="s">
+    </row>
+    <row r="63" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A63" s="126"/>
+      <c r="B63" s="123"/>
+      <c r="C63" s="12" t="s">
         <v>472</v>
       </c>
-      <c r="E62" s="14" t="s">
+      <c r="D63" s="13" t="s">
         <v>473</v>
       </c>
-    </row>
-    <row r="63" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A63" s="137"/>
-      <c r="B63" s="126"/>
-      <c r="C63" s="12" t="s">
+      <c r="E63" s="14" t="s">
         <v>474</v>
       </c>
-      <c r="D63" s="13" t="s">
+    </row>
+    <row r="64" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A64" s="126"/>
+      <c r="B64" s="123"/>
+      <c r="C64" s="12" t="s">
         <v>475</v>
       </c>
-      <c r="E63" s="14" t="s">
+      <c r="D64" s="13" t="s">
         <v>476</v>
       </c>
-    </row>
-    <row r="64" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A64" s="137"/>
-      <c r="B64" s="126"/>
-      <c r="C64" s="12" t="s">
+      <c r="E64" s="14" t="s">
         <v>477</v>
       </c>
-      <c r="D64" s="13" t="s">
+    </row>
+    <row r="65" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A65" s="126"/>
+      <c r="B65" s="123"/>
+      <c r="C65" s="12" t="s">
         <v>478</v>
       </c>
-      <c r="E64" s="14" t="s">
+      <c r="D65" s="13" t="s">
         <v>479</v>
       </c>
-    </row>
-    <row r="65" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A65" s="137"/>
-      <c r="B65" s="126"/>
-      <c r="C65" s="12" t="s">
+      <c r="E65" s="14" t="s">
         <v>480</v>
       </c>
-      <c r="D65" s="13" t="s">
+    </row>
+    <row r="66" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A66" s="126"/>
+      <c r="B66" s="123"/>
+      <c r="C66" s="12" t="s">
         <v>481</v>
       </c>
-      <c r="E65" s="14" t="s">
+      <c r="D66" s="13" t="s">
         <v>482</v>
       </c>
-    </row>
-    <row r="66" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A66" s="137"/>
-      <c r="B66" s="126"/>
-      <c r="C66" s="12" t="s">
+      <c r="E66" s="14" t="s">
         <v>483</v>
       </c>
-      <c r="D66" s="13" t="s">
+    </row>
+    <row r="67" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A67" s="126"/>
+      <c r="B67" s="123"/>
+      <c r="C67" s="12" t="s">
         <v>484</v>
       </c>
-      <c r="E66" s="14" t="s">
+      <c r="D67" s="13" t="s">
         <v>485</v>
       </c>
-    </row>
-    <row r="67" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A67" s="137"/>
-      <c r="B67" s="126"/>
-      <c r="C67" s="12" t="s">
+      <c r="E67" s="14" t="s">
         <v>486</v>
       </c>
-      <c r="D67" s="13" t="s">
+    </row>
+    <row r="68" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A68" s="126"/>
+      <c r="B68" s="123"/>
+      <c r="C68" s="9" t="s">
         <v>487</v>
       </c>
-      <c r="E67" s="14" t="s">
+      <c r="D68" s="17" t="s">
         <v>488</v>
       </c>
-    </row>
-    <row r="68" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A68" s="137"/>
-      <c r="B68" s="126"/>
-      <c r="C68" s="9" t="s">
+      <c r="E68" s="18" t="s">
         <v>489</v>
       </c>
-      <c r="D68" s="17" t="s">
+    </row>
+    <row r="69" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A69" s="126"/>
+      <c r="B69" s="132" t="s">
         <v>490</v>
       </c>
-      <c r="E68" s="18" t="s">
+      <c r="C69" s="12" t="s">
         <v>491</v>
       </c>
-    </row>
-    <row r="69" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A69" s="137"/>
-      <c r="B69" s="131" t="s">
+      <c r="D69" s="13" t="s">
         <v>492</v>
       </c>
-      <c r="C69" s="12" t="s">
+      <c r="E69" s="14" t="s">
         <v>493</v>
       </c>
-      <c r="D69" s="13" t="s">
+    </row>
+    <row r="70" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A70" s="126"/>
+      <c r="B70" s="132"/>
+      <c r="C70" s="12" t="s">
         <v>494</v>
       </c>
-      <c r="E69" s="14" t="s">
+      <c r="D70" s="13" t="s">
         <v>495</v>
       </c>
-    </row>
-    <row r="70" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A70" s="137"/>
-      <c r="B70" s="131"/>
-      <c r="C70" s="12" t="s">
+      <c r="E70" s="14" t="s">
         <v>496</v>
       </c>
-      <c r="D70" s="13" t="s">
+    </row>
+    <row r="71" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A71" s="126"/>
+      <c r="B71" s="132"/>
+      <c r="C71" s="12" t="s">
         <v>497</v>
       </c>
-      <c r="E70" s="14" t="s">
+      <c r="D71" s="13" t="s">
         <v>498</v>
       </c>
-    </row>
-    <row r="71" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A71" s="137"/>
-      <c r="B71" s="131"/>
-      <c r="C71" s="12" t="s">
+      <c r="E71" s="14" t="s">
         <v>499</v>
       </c>
-      <c r="D71" s="13" t="s">
+    </row>
+    <row r="72" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A72" s="126"/>
+      <c r="B72" s="132"/>
+      <c r="C72" s="12" t="s">
         <v>500</v>
       </c>
-      <c r="E71" s="14" t="s">
+      <c r="D72" s="13" t="s">
         <v>501</v>
       </c>
-    </row>
-    <row r="72" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A72" s="137"/>
-      <c r="B72" s="131"/>
-      <c r="C72" s="12" t="s">
+      <c r="E72" s="14" t="s">
         <v>502</v>
       </c>
-      <c r="D72" s="13" t="s">
+    </row>
+    <row r="73" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A73" s="126"/>
+      <c r="B73" s="132"/>
+      <c r="C73" s="12" t="s">
         <v>503</v>
       </c>
-      <c r="E72" s="14" t="s">
+      <c r="D73" s="13" t="s">
         <v>504</v>
       </c>
-    </row>
-    <row r="73" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A73" s="137"/>
-      <c r="B73" s="131"/>
-      <c r="C73" s="12" t="s">
+      <c r="E73" s="14" t="s">
         <v>505</v>
       </c>
-      <c r="D73" s="13" t="s">
+    </row>
+    <row r="74" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A74" s="126"/>
+      <c r="B74" s="132"/>
+      <c r="C74" s="12" t="s">
         <v>506</v>
       </c>
-      <c r="E73" s="14" t="s">
+      <c r="D74" s="13" t="s">
         <v>507</v>
       </c>
-    </row>
-    <row r="74" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A74" s="137"/>
-      <c r="B74" s="131"/>
-      <c r="C74" s="12" t="s">
+      <c r="E74" s="14" t="s">
         <v>508</v>
       </c>
-      <c r="D74" s="13" t="s">
+    </row>
+    <row r="75" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A75" s="126"/>
+      <c r="B75" s="132"/>
+      <c r="C75" s="12" t="s">
         <v>509</v>
       </c>
-      <c r="E74" s="14" t="s">
+      <c r="D75" s="13" t="s">
         <v>510</v>
       </c>
-    </row>
-    <row r="75" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A75" s="137"/>
-      <c r="B75" s="131"/>
-      <c r="C75" s="12" t="s">
+      <c r="E75" s="14" t="s">
         <v>511</v>
       </c>
-      <c r="D75" s="13" t="s">
+    </row>
+    <row r="76" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A76" s="126"/>
+      <c r="B76" s="132"/>
+      <c r="C76" s="12" t="s">
         <v>512</v>
       </c>
-      <c r="E75" s="14" t="s">
+      <c r="D76" s="13" t="s">
         <v>513</v>
       </c>
-    </row>
-    <row r="76" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A76" s="137"/>
-      <c r="B76" s="131"/>
-      <c r="C76" s="12" t="s">
+      <c r="E76" s="14" t="s">
         <v>514</v>
       </c>
-      <c r="D76" s="13" t="s">
+    </row>
+    <row r="77" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A77" s="126"/>
+      <c r="B77" s="132"/>
+      <c r="C77" s="12" t="s">
         <v>515</v>
       </c>
-      <c r="E76" s="14" t="s">
+      <c r="D77" s="13" t="s">
         <v>516</v>
       </c>
-    </row>
-    <row r="77" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A77" s="137"/>
-      <c r="B77" s="131"/>
-      <c r="C77" s="12" t="s">
+      <c r="E77" s="14" t="s">
         <v>517</v>
       </c>
-      <c r="D77" s="13" t="s">
+    </row>
+    <row r="78" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A78" s="126"/>
+      <c r="B78" s="132"/>
+      <c r="C78" s="12" t="s">
         <v>518</v>
       </c>
-      <c r="E77" s="14" t="s">
+      <c r="D78" s="13" t="s">
         <v>519</v>
       </c>
-    </row>
-    <row r="78" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A78" s="137"/>
-      <c r="B78" s="131"/>
-      <c r="C78" s="12" t="s">
+      <c r="E78" s="14" t="s">
         <v>520</v>
       </c>
-      <c r="D78" s="13" t="s">
+    </row>
+    <row r="79" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A79" s="126"/>
+      <c r="B79" s="132"/>
+      <c r="C79" s="9" t="s">
         <v>521</v>
       </c>
-      <c r="E78" s="14" t="s">
+      <c r="D79" s="17" t="s">
         <v>522</v>
       </c>
-    </row>
-    <row r="79" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A79" s="137"/>
-      <c r="B79" s="131"/>
-      <c r="C79" s="9" t="s">
+      <c r="E79" s="18" t="s">
         <v>523</v>
       </c>
-      <c r="D79" s="17" t="s">
+    </row>
+    <row r="80" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A80" s="126"/>
+      <c r="B80" s="123" t="s">
         <v>524</v>
       </c>
-      <c r="E79" s="18" t="s">
+      <c r="C80" s="12" t="s">
         <v>525</v>
       </c>
-    </row>
-    <row r="80" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A80" s="137"/>
-      <c r="B80" s="126" t="s">
+      <c r="D80" s="13" t="s">
         <v>526</v>
       </c>
-      <c r="C80" s="12" t="s">
+      <c r="E80" s="14" t="s">
         <v>527</v>
       </c>
-      <c r="D80" s="13" t="s">
+    </row>
+    <row r="81" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A81" s="126"/>
+      <c r="B81" s="123"/>
+      <c r="C81" s="12" t="s">
         <v>528</v>
       </c>
-      <c r="E80" s="14" t="s">
+      <c r="D81" s="13" t="s">
         <v>529</v>
       </c>
-    </row>
-    <row r="81" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A81" s="137"/>
-      <c r="B81" s="126"/>
-      <c r="C81" s="12" t="s">
+      <c r="E81" s="14" t="s">
         <v>530</v>
       </c>
-      <c r="D81" s="13" t="s">
+    </row>
+    <row r="82" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A82" s="126"/>
+      <c r="B82" s="123"/>
+      <c r="C82" s="12" t="s">
         <v>531</v>
       </c>
-      <c r="E81" s="14" t="s">
+      <c r="D82" s="13" t="s">
         <v>532</v>
       </c>
-    </row>
-    <row r="82" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A82" s="137"/>
-      <c r="B82" s="126"/>
-      <c r="C82" s="12" t="s">
+      <c r="E82" s="14" t="s">
         <v>533</v>
       </c>
-      <c r="D82" s="13" t="s">
+    </row>
+    <row r="83" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A83" s="126"/>
+      <c r="B83" s="123"/>
+      <c r="C83" s="9" t="s">
         <v>534</v>
       </c>
-      <c r="E82" s="14" t="s">
+      <c r="D83" s="17" t="s">
         <v>535</v>
       </c>
-    </row>
-    <row r="83" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A83" s="137"/>
-      <c r="B83" s="126"/>
-      <c r="C83" s="9" t="s">
+      <c r="E83" s="18" t="s">
         <v>536</v>
       </c>
-      <c r="D83" s="17" t="s">
+    </row>
+    <row r="84" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A84" s="126"/>
+      <c r="B84" s="123" t="s">
         <v>537</v>
       </c>
-      <c r="E83" s="18" t="s">
+      <c r="C84" s="12" t="s">
         <v>538</v>
       </c>
-    </row>
-    <row r="84" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A84" s="137"/>
-      <c r="B84" s="126" t="s">
+      <c r="D84" s="13" t="s">
         <v>539</v>
       </c>
-      <c r="C84" s="12" t="s">
+      <c r="E84" s="14" t="s">
         <v>540</v>
       </c>
-      <c r="D84" s="13" t="s">
+    </row>
+    <row r="85" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A85" s="126"/>
+      <c r="B85" s="123"/>
+      <c r="C85" s="12" t="s">
         <v>541</v>
       </c>
-      <c r="E84" s="14" t="s">
+      <c r="D85" s="13" t="s">
         <v>542</v>
       </c>
-    </row>
-    <row r="85" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A85" s="137"/>
-      <c r="B85" s="126"/>
-      <c r="C85" s="12" t="s">
+      <c r="E85" s="14" t="s">
         <v>543</v>
       </c>
-      <c r="D85" s="13" t="s">
+    </row>
+    <row r="86" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A86" s="126"/>
+      <c r="B86" s="123"/>
+      <c r="C86" s="12" t="s">
         <v>544</v>
       </c>
-      <c r="E85" s="14" t="s">
+      <c r="D86" s="13" t="s">
         <v>545</v>
       </c>
-    </row>
-    <row r="86" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A86" s="137"/>
-      <c r="B86" s="126"/>
-      <c r="C86" s="12" t="s">
+      <c r="E86" s="14" t="s">
         <v>546</v>
       </c>
-      <c r="D86" s="13" t="s">
+    </row>
+    <row r="87" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A87" s="126"/>
+      <c r="B87" s="123"/>
+      <c r="C87" s="12" t="s">
         <v>547</v>
       </c>
-      <c r="E86" s="14" t="s">
+      <c r="D87" s="13" t="s">
         <v>548</v>
       </c>
-    </row>
-    <row r="87" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A87" s="137"/>
-      <c r="B87" s="126"/>
-      <c r="C87" s="12" t="s">
+      <c r="E87" s="14" t="s">
         <v>549</v>
       </c>
-      <c r="D87" s="13" t="s">
+    </row>
+    <row r="88" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A88" s="126"/>
+      <c r="B88" s="123"/>
+      <c r="C88" s="12" t="s">
         <v>550</v>
       </c>
-      <c r="E87" s="14" t="s">
+      <c r="D88" s="13" t="s">
         <v>551</v>
       </c>
-    </row>
-    <row r="88" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A88" s="137"/>
-      <c r="B88" s="126"/>
-      <c r="C88" s="12" t="s">
+      <c r="E88" s="14" t="s">
         <v>552</v>
       </c>
-      <c r="D88" s="13" t="s">
+    </row>
+    <row r="89" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A89" s="126"/>
+      <c r="B89" s="123"/>
+      <c r="C89" s="12" t="s">
         <v>553</v>
       </c>
-      <c r="E88" s="14" t="s">
+      <c r="D89" s="13" t="s">
         <v>554</v>
       </c>
-    </row>
-    <row r="89" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A89" s="137"/>
-      <c r="B89" s="126"/>
-      <c r="C89" s="12" t="s">
+      <c r="E89" s="14" t="s">
         <v>555</v>
       </c>
-      <c r="D89" s="13" t="s">
+    </row>
+    <row r="90" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A90" s="126"/>
+      <c r="B90" s="123"/>
+      <c r="C90" s="9" t="s">
         <v>556</v>
       </c>
-      <c r="E89" s="14" t="s">
+      <c r="D90" s="17" t="s">
         <v>557</v>
       </c>
-    </row>
-    <row r="90" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A90" s="137"/>
-      <c r="B90" s="126"/>
-      <c r="C90" s="9" t="s">
+      <c r="E90" s="18" t="s">
         <v>558</v>
       </c>
-      <c r="D90" s="17" t="s">
+    </row>
+    <row r="91" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A91" s="126"/>
+      <c r="B91" s="123" t="s">
         <v>559</v>
       </c>
-      <c r="E90" s="18" t="s">
+      <c r="C91" s="12" t="s">
         <v>560</v>
       </c>
-    </row>
-    <row r="91" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A91" s="137"/>
-      <c r="B91" s="126" t="s">
+      <c r="D91" s="13" t="s">
         <v>561</v>
       </c>
-      <c r="C91" s="12" t="s">
+      <c r="E91" s="14" t="s">
         <v>562</v>
       </c>
-      <c r="D91" s="13" t="s">
+    </row>
+    <row r="92" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A92" s="126"/>
+      <c r="B92" s="123"/>
+      <c r="C92" s="12" t="s">
         <v>563</v>
       </c>
-      <c r="E91" s="14" t="s">
+      <c r="D92" s="13" t="s">
         <v>564</v>
       </c>
-    </row>
-    <row r="92" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A92" s="137"/>
-      <c r="B92" s="126"/>
-      <c r="C92" s="12" t="s">
+      <c r="E92" s="14" t="s">
         <v>565</v>
       </c>
-      <c r="D92" s="13" t="s">
+    </row>
+    <row r="93" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A93" s="126"/>
+      <c r="B93" s="123"/>
+      <c r="C93" s="12" t="s">
         <v>566</v>
       </c>
-      <c r="E92" s="14" t="s">
+      <c r="D93" s="13" t="s">
         <v>567</v>
       </c>
-    </row>
-    <row r="93" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A93" s="137"/>
-      <c r="B93" s="126"/>
-      <c r="C93" s="12" t="s">
+      <c r="E93" s="14" t="s">
         <v>568</v>
       </c>
-      <c r="D93" s="13" t="s">
+    </row>
+    <row r="94" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A94" s="126"/>
+      <c r="B94" s="123"/>
+      <c r="C94" s="12" t="s">
         <v>569</v>
       </c>
-      <c r="E93" s="14" t="s">
+      <c r="D94" s="13" t="s">
         <v>570</v>
       </c>
-    </row>
-    <row r="94" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A94" s="137"/>
-      <c r="B94" s="126"/>
-      <c r="C94" s="12" t="s">
+      <c r="E94" s="14" t="s">
         <v>571</v>
       </c>
-      <c r="D94" s="13" t="s">
+    </row>
+    <row r="95" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A95" s="126"/>
+      <c r="B95" s="123"/>
+      <c r="C95" s="12" t="s">
         <v>572</v>
       </c>
-      <c r="E94" s="14" t="s">
+      <c r="D95" s="13" t="s">
         <v>573</v>
       </c>
-    </row>
-    <row r="95" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A95" s="137"/>
-      <c r="B95" s="126"/>
-      <c r="C95" s="12" t="s">
+      <c r="E95" s="14" t="s">
         <v>574</v>
       </c>
-      <c r="D95" s="13" t="s">
+    </row>
+    <row r="96" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A96" s="126"/>
+      <c r="B96" s="123"/>
+      <c r="C96" s="12" t="s">
         <v>575</v>
       </c>
-      <c r="E95" s="14" t="s">
+      <c r="D96" s="13" t="s">
         <v>576</v>
       </c>
-    </row>
-    <row r="96" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A96" s="137"/>
-      <c r="B96" s="126"/>
-      <c r="C96" s="12" t="s">
+      <c r="E96" s="14" t="s">
         <v>577</v>
       </c>
-      <c r="D96" s="13" t="s">
+    </row>
+    <row r="97" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A97" s="126"/>
+      <c r="B97" s="123"/>
+      <c r="C97" s="23" t="s">
         <v>578</v>
       </c>
-      <c r="E96" s="14" t="s">
+      <c r="D97" s="17" t="s">
         <v>579</v>
       </c>
-    </row>
-    <row r="97" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A97" s="137"/>
-      <c r="B97" s="126"/>
-      <c r="C97" s="23" t="s">
+      <c r="E97" s="18" t="s">
         <v>580</v>
       </c>
-      <c r="D97" s="17" t="s">
+    </row>
+    <row r="98" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A98" s="126"/>
+      <c r="B98" s="141" t="s">
         <v>581</v>
       </c>
-      <c r="E97" s="18" t="s">
+      <c r="C98" s="24" t="s">
         <v>582</v>
       </c>
-    </row>
-    <row r="98" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A98" s="137"/>
-      <c r="B98" s="153" t="s">
+      <c r="D98" s="27" t="s">
         <v>583</v>
       </c>
-      <c r="C98" s="24" t="s">
+      <c r="E98" s="25"/>
+    </row>
+    <row r="99" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A99" s="126"/>
+      <c r="B99" s="142"/>
+      <c r="C99" s="24" t="s">
         <v>584</v>
       </c>
-      <c r="D98" s="27" t="s">
+      <c r="D99" s="26" t="s">
         <v>585</v>
       </c>
-      <c r="E98" s="25"/>
-    </row>
-    <row r="99" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A99" s="137"/>
-      <c r="B99" s="154"/>
-      <c r="C99" s="24" t="s">
+      <c r="E99" s="25"/>
+    </row>
+    <row r="100" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A100" s="126"/>
+      <c r="B100" s="142"/>
+      <c r="C100" s="19" t="s">
         <v>586</v>
       </c>
-      <c r="D99" s="26" t="s">
+      <c r="D100" s="26" t="s">
         <v>587</v>
       </c>
-      <c r="E99" s="25"/>
-    </row>
-    <row r="100" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A100" s="137"/>
-      <c r="B100" s="154"/>
-      <c r="C100" s="19" t="s">
+      <c r="E100" s="25"/>
+    </row>
+    <row r="101" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A101" s="126"/>
+      <c r="B101" s="142"/>
+      <c r="C101" s="19" t="s">
         <v>588</v>
       </c>
-      <c r="D100" s="26" t="s">
+      <c r="D101" s="26" t="s">
         <v>589</v>
       </c>
-      <c r="E100" s="25"/>
-    </row>
-    <row r="101" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A101" s="137"/>
-      <c r="B101" s="154"/>
-      <c r="C101" s="19" t="s">
+      <c r="E101" s="25"/>
+    </row>
+    <row r="102" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A102" s="126"/>
+      <c r="B102" s="142"/>
+      <c r="C102" s="19" t="s">
         <v>590</v>
       </c>
-      <c r="D101" s="26" t="s">
+      <c r="D102" s="26" t="s">
         <v>591</v>
       </c>
-      <c r="E101" s="25"/>
-    </row>
-    <row r="102" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A102" s="137"/>
-      <c r="B102" s="154"/>
-      <c r="C102" s="19" t="s">
+      <c r="E102" s="25"/>
+    </row>
+    <row r="103" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A103" s="126"/>
+      <c r="B103" s="142"/>
+      <c r="C103" s="24" t="s">
         <v>592</v>
       </c>
-      <c r="D102" s="26" t="s">
+      <c r="D103" s="26" t="s">
         <v>593</v>
       </c>
-      <c r="E102" s="25"/>
-    </row>
-    <row r="103" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A103" s="137"/>
-      <c r="B103" s="154"/>
-      <c r="C103" s="24" t="s">
+      <c r="E103" s="25"/>
+    </row>
+    <row r="104" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A104" s="126"/>
+      <c r="B104" s="142"/>
+      <c r="C104" s="24" t="s">
         <v>594</v>
       </c>
-      <c r="D103" s="26" t="s">
+      <c r="D104" s="27" t="s">
         <v>595</v>
       </c>
-      <c r="E103" s="25"/>
-    </row>
-    <row r="104" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A104" s="137"/>
-      <c r="B104" s="154"/>
-      <c r="C104" s="24" t="s">
+      <c r="E104" s="25"/>
+    </row>
+    <row r="105" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A105" s="126"/>
+      <c r="B105" s="142"/>
+      <c r="C105" s="24" t="s">
         <v>596</v>
       </c>
-      <c r="D104" s="27" t="s">
+      <c r="D105" s="26" t="s">
         <v>597</v>
       </c>
-      <c r="E104" s="25"/>
-    </row>
-    <row r="105" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A105" s="137"/>
-      <c r="B105" s="154"/>
-      <c r="C105" s="24" t="s">
+      <c r="E105" s="25"/>
+    </row>
+    <row r="106" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A106" s="126"/>
+      <c r="B106" s="142"/>
+      <c r="C106" s="19" t="s">
         <v>598</v>
       </c>
-      <c r="D105" s="26" t="s">
+      <c r="D106" s="26" t="s">
         <v>599</v>
       </c>
-      <c r="E105" s="25"/>
-    </row>
-    <row r="106" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A106" s="137"/>
-      <c r="B106" s="154"/>
-      <c r="C106" s="19" t="s">
+      <c r="E106" s="25"/>
+    </row>
+    <row r="107" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A107" s="126"/>
+      <c r="B107" s="142"/>
+      <c r="C107" s="19" t="s">
         <v>600</v>
       </c>
-      <c r="D106" s="26" t="s">
+      <c r="D107" s="26" t="s">
         <v>601</v>
       </c>
-      <c r="E106" s="25"/>
-    </row>
-    <row r="107" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A107" s="137"/>
-      <c r="B107" s="154"/>
-      <c r="C107" s="19" t="s">
+      <c r="E107" s="25"/>
+    </row>
+    <row r="108" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A108" s="126"/>
+      <c r="B108" s="142"/>
+      <c r="C108" s="19" t="s">
         <v>602</v>
       </c>
-      <c r="D107" s="26" t="s">
+      <c r="D108" s="26" t="s">
         <v>603</v>
       </c>
-      <c r="E107" s="25"/>
-    </row>
-    <row r="108" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A108" s="137"/>
-      <c r="B108" s="154"/>
-      <c r="C108" s="19" t="s">
+      <c r="E108" s="25"/>
+    </row>
+    <row r="109" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A109" s="126"/>
+      <c r="B109" s="142"/>
+      <c r="C109" s="19" t="s">
         <v>604</v>
       </c>
-      <c r="D108" s="26" t="s">
+      <c r="D109" s="26" t="s">
         <v>605</v>
       </c>
-      <c r="E108" s="25"/>
-    </row>
-    <row r="109" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A109" s="137"/>
-      <c r="B109" s="154"/>
-      <c r="C109" s="19" t="s">
+      <c r="E109" s="25"/>
+    </row>
+    <row r="110" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A110" s="126"/>
+      <c r="B110" s="142"/>
+      <c r="C110" s="24" t="s">
         <v>606</v>
       </c>
-      <c r="D109" s="26" t="s">
+      <c r="D110" s="26" t="s">
         <v>607</v>
       </c>
-      <c r="E109" s="25"/>
-    </row>
-    <row r="110" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A110" s="137"/>
-      <c r="B110" s="154"/>
-      <c r="C110" s="24" t="s">
+      <c r="E110" s="25"/>
+    </row>
+    <row r="111" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A111" s="126"/>
+      <c r="B111" s="142"/>
+      <c r="C111" s="24" t="s">
         <v>608</v>
       </c>
-      <c r="D110" s="26" t="s">
+      <c r="D111" s="13" t="s">
         <v>609</v>
       </c>
-      <c r="E110" s="25"/>
-    </row>
-    <row r="111" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A111" s="137"/>
-      <c r="B111" s="154"/>
-      <c r="C111" s="24" t="s">
+      <c r="E111" s="25"/>
+    </row>
+    <row r="112" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A112" s="126"/>
+      <c r="B112" s="142"/>
+      <c r="C112" s="24" t="s">
         <v>610</v>
       </c>
-      <c r="D111" s="13" t="s">
+      <c r="D112" s="26" t="s">
         <v>611</v>
       </c>
-      <c r="E111" s="25"/>
-    </row>
-    <row r="112" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A112" s="137"/>
-      <c r="B112" s="154"/>
-      <c r="C112" s="24" t="s">
+      <c r="E112" s="25"/>
+    </row>
+    <row r="113" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A113" s="126"/>
+      <c r="B113" s="142"/>
+      <c r="C113" s="24" t="s">
         <v>612</v>
       </c>
-      <c r="D112" s="26" t="s">
+      <c r="D113" s="26" t="s">
         <v>613</v>
       </c>
-      <c r="E112" s="25"/>
-    </row>
-    <row r="113" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A113" s="137"/>
-      <c r="B113" s="154"/>
-      <c r="C113" s="24" t="s">
+      <c r="E113" s="25"/>
+    </row>
+    <row r="114" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A114" s="126"/>
+      <c r="B114" s="142"/>
+      <c r="C114" s="24" t="s">
         <v>614</v>
       </c>
-      <c r="D113" s="26" t="s">
+      <c r="D114" s="26" t="s">
         <v>615</v>
       </c>
-      <c r="E113" s="25"/>
-    </row>
-    <row r="114" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A114" s="137"/>
-      <c r="B114" s="154"/>
-      <c r="C114" s="24" t="s">
+      <c r="E114" s="25"/>
+    </row>
+    <row r="115" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A115" s="126"/>
+      <c r="B115" s="142"/>
+      <c r="C115" s="24" t="s">
         <v>616</v>
       </c>
-      <c r="D114" s="26" t="s">
+      <c r="D115" s="26" t="s">
         <v>617</v>
       </c>
-      <c r="E114" s="25"/>
-    </row>
-    <row r="115" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A115" s="137"/>
-      <c r="B115" s="154"/>
-      <c r="C115" s="24" t="s">
+      <c r="E115" s="25"/>
+    </row>
+    <row r="116" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A116" s="126"/>
+      <c r="B116" s="142"/>
+      <c r="C116" s="23" t="s">
         <v>618</v>
       </c>
-      <c r="D115" s="26" t="s">
+      <c r="D116" s="17" t="s">
         <v>619</v>
       </c>
-      <c r="E115" s="25"/>
-    </row>
-    <row r="116" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A116" s="137"/>
-      <c r="B116" s="154"/>
-      <c r="C116" s="23" t="s">
+      <c r="E116" s="25"/>
+    </row>
+    <row r="117" spans="1:5" s="2" customFormat="1" ht="27" customHeight="1">
+      <c r="A117" s="126"/>
+      <c r="B117" s="143"/>
+      <c r="C117" s="28" t="s">
         <v>620</v>
       </c>
-      <c r="D116" s="17" t="s">
+      <c r="D117" s="29" t="s">
         <v>621</v>
       </c>
-      <c r="E116" s="25"/>
-    </row>
-    <row r="117" spans="1:5" s="2" customFormat="1" ht="27" customHeight="1">
-      <c r="A117" s="137"/>
-      <c r="B117" s="155"/>
-      <c r="C117" s="28" t="s">
+      <c r="E117" s="25"/>
+    </row>
+    <row r="118" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A118" s="126"/>
+      <c r="B118" s="141" t="s">
         <v>622</v>
       </c>
-      <c r="D117" s="29" t="s">
+      <c r="C118" s="19" t="s">
         <v>623</v>
       </c>
-      <c r="E117" s="25"/>
-    </row>
-    <row r="118" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A118" s="137"/>
-      <c r="B118" s="153" t="s">
+      <c r="D118" s="27" t="s">
         <v>624</v>
       </c>
-      <c r="C118" s="19" t="s">
+      <c r="E118" s="25"/>
+    </row>
+    <row r="119" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A119" s="126"/>
+      <c r="B119" s="142"/>
+      <c r="C119" s="19" t="s">
         <v>625</v>
       </c>
-      <c r="D118" s="27" t="s">
+      <c r="D119" s="13" t="s">
         <v>626</v>
       </c>
-      <c r="E118" s="25"/>
-    </row>
-    <row r="119" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A119" s="137"/>
-      <c r="B119" s="154"/>
-      <c r="C119" s="19" t="s">
+      <c r="E119" s="25"/>
+    </row>
+    <row r="120" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A120" s="126"/>
+      <c r="B120" s="142"/>
+      <c r="C120" s="19" t="s">
         <v>627</v>
       </c>
-      <c r="D119" s="13" t="s">
+      <c r="D120" s="13" t="s">
         <v>628</v>
       </c>
-      <c r="E119" s="25"/>
-    </row>
-    <row r="120" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A120" s="137"/>
-      <c r="B120" s="154"/>
-      <c r="C120" s="19" t="s">
+      <c r="E120" s="25"/>
+    </row>
+    <row r="121" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A121" s="126"/>
+      <c r="B121" s="142"/>
+      <c r="C121" s="19" t="s">
         <v>629</v>
       </c>
-      <c r="D120" s="13" t="s">
+      <c r="D121" s="27" t="s">
         <v>630</v>
       </c>
-      <c r="E120" s="25"/>
-    </row>
-    <row r="121" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A121" s="137"/>
-      <c r="B121" s="154"/>
-      <c r="C121" s="19" t="s">
+      <c r="E121" s="25"/>
+    </row>
+    <row r="122" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A122" s="126"/>
+      <c r="B122" s="142"/>
+      <c r="C122" s="19" t="s">
         <v>631</v>
       </c>
-      <c r="D121" s="27" t="s">
+      <c r="D122" s="13" t="s">
         <v>632</v>
       </c>
-      <c r="E121" s="25"/>
-    </row>
-    <row r="122" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A122" s="137"/>
-      <c r="B122" s="154"/>
-      <c r="C122" s="19" t="s">
+      <c r="E122" s="25"/>
+    </row>
+    <row r="123" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A123" s="126"/>
+      <c r="B123" s="142"/>
+      <c r="C123" s="19" t="s">
         <v>633</v>
       </c>
-      <c r="D122" s="13" t="s">
+      <c r="D123" s="13" t="s">
         <v>634</v>
       </c>
-      <c r="E122" s="25"/>
-    </row>
-    <row r="123" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A123" s="137"/>
-      <c r="B123" s="154"/>
-      <c r="C123" s="19" t="s">
+      <c r="E123" s="25"/>
+    </row>
+    <row r="124" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A124" s="126"/>
+      <c r="B124" s="142"/>
+      <c r="C124" s="19" t="s">
         <v>635</v>
       </c>
-      <c r="D123" s="13" t="s">
+      <c r="D124" s="27" t="s">
         <v>636</v>
       </c>
-      <c r="E123" s="25"/>
-    </row>
-    <row r="124" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A124" s="137"/>
-      <c r="B124" s="154"/>
-      <c r="C124" s="19" t="s">
+      <c r="E124" s="25"/>
+    </row>
+    <row r="125" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A125" s="126"/>
+      <c r="B125" s="142"/>
+      <c r="C125" s="19" t="s">
         <v>637</v>
       </c>
-      <c r="D124" s="27" t="s">
+      <c r="D125" s="13" t="s">
         <v>638</v>
       </c>
-      <c r="E124" s="25"/>
-    </row>
-    <row r="125" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A125" s="137"/>
-      <c r="B125" s="154"/>
-      <c r="C125" s="19" t="s">
+      <c r="E125" s="25"/>
+    </row>
+    <row r="126" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A126" s="126"/>
+      <c r="B126" s="142"/>
+      <c r="C126" s="19" t="s">
         <v>639</v>
       </c>
-      <c r="D125" s="13" t="s">
+      <c r="D126" s="13" t="s">
         <v>640</v>
       </c>
-      <c r="E125" s="25"/>
-    </row>
-    <row r="126" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A126" s="137"/>
-      <c r="B126" s="154"/>
-      <c r="C126" s="19" t="s">
+      <c r="E126" s="25"/>
+    </row>
+    <row r="127" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A127" s="126"/>
+      <c r="B127" s="142"/>
+      <c r="C127" s="19" t="s">
         <v>641</v>
       </c>
-      <c r="D126" s="13" t="s">
+      <c r="D127" s="27" t="s">
         <v>642</v>
       </c>
-      <c r="E126" s="25"/>
-    </row>
-    <row r="127" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A127" s="137"/>
-      <c r="B127" s="154"/>
-      <c r="C127" s="19" t="s">
+      <c r="E127" s="25"/>
+    </row>
+    <row r="128" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A128" s="126"/>
+      <c r="B128" s="142"/>
+      <c r="C128" s="19" t="s">
         <v>643</v>
       </c>
-      <c r="D127" s="27" t="s">
+      <c r="D128" s="13" t="s">
         <v>644</v>
       </c>
-      <c r="E127" s="25"/>
-    </row>
-    <row r="128" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A128" s="137"/>
-      <c r="B128" s="154"/>
-      <c r="C128" s="19" t="s">
+      <c r="E128" s="25"/>
+    </row>
+    <row r="129" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A129" s="126"/>
+      <c r="B129" s="142"/>
+      <c r="C129" s="19" t="s">
         <v>645</v>
       </c>
-      <c r="D128" s="13" t="s">
+      <c r="D129" s="13" t="s">
         <v>646</v>
       </c>
-      <c r="E128" s="25"/>
-    </row>
-    <row r="129" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A129" s="137"/>
-      <c r="B129" s="154"/>
-      <c r="C129" s="19" t="s">
+      <c r="E129" s="25"/>
+    </row>
+    <row r="130" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A130" s="126"/>
+      <c r="B130" s="142"/>
+      <c r="C130" s="19" t="s">
         <v>647</v>
       </c>
-      <c r="D129" s="13" t="s">
+      <c r="D130" s="27" t="s">
         <v>648</v>
       </c>
-      <c r="E129" s="25"/>
-    </row>
-    <row r="130" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A130" s="137"/>
-      <c r="B130" s="154"/>
-      <c r="C130" s="19" t="s">
+      <c r="E130" s="25"/>
+    </row>
+    <row r="131" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A131" s="126"/>
+      <c r="B131" s="142"/>
+      <c r="C131" s="19" t="s">
         <v>649</v>
       </c>
-      <c r="D130" s="27" t="s">
+      <c r="D131" s="13" t="s">
         <v>650</v>
       </c>
-      <c r="E130" s="25"/>
-    </row>
-    <row r="131" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A131" s="137"/>
-      <c r="B131" s="154"/>
-      <c r="C131" s="19" t="s">
+      <c r="E131" s="25"/>
+    </row>
+    <row r="132" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A132" s="126"/>
+      <c r="B132" s="142"/>
+      <c r="C132" s="19" t="s">
         <v>651</v>
       </c>
-      <c r="D131" s="13" t="s">
+      <c r="D132" s="13" t="s">
         <v>652</v>
       </c>
-      <c r="E131" s="25"/>
-    </row>
-    <row r="132" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A132" s="137"/>
-      <c r="B132" s="154"/>
-      <c r="C132" s="19" t="s">
+      <c r="E132" s="25"/>
+    </row>
+    <row r="133" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A133" s="126"/>
+      <c r="B133" s="142"/>
+      <c r="C133" s="19" t="s">
         <v>653</v>
       </c>
-      <c r="D132" s="13" t="s">
+      <c r="D133" s="27" t="s">
         <v>654</v>
       </c>
-      <c r="E132" s="25"/>
-    </row>
-    <row r="133" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A133" s="137"/>
-      <c r="B133" s="154"/>
-      <c r="C133" s="19" t="s">
+      <c r="E133" s="25"/>
+    </row>
+    <row r="134" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A134" s="126"/>
+      <c r="B134" s="142"/>
+      <c r="C134" s="19" t="s">
         <v>655</v>
       </c>
-      <c r="D133" s="27" t="s">
+      <c r="D134" s="13" t="s">
         <v>656</v>
       </c>
-      <c r="E133" s="25"/>
-    </row>
-    <row r="134" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A134" s="137"/>
-      <c r="B134" s="154"/>
-      <c r="C134" s="19" t="s">
+      <c r="E134" s="25"/>
+    </row>
+    <row r="135" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A135" s="126"/>
+      <c r="B135" s="142"/>
+      <c r="C135" s="19" t="s">
         <v>657</v>
       </c>
-      <c r="D134" s="13" t="s">
+      <c r="D135" s="13" t="s">
         <v>658</v>
       </c>
-      <c r="E134" s="25"/>
-    </row>
-    <row r="135" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A135" s="137"/>
-      <c r="B135" s="154"/>
-      <c r="C135" s="19" t="s">
+      <c r="E135" s="25"/>
+    </row>
+    <row r="136" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A136" s="126"/>
+      <c r="B136" s="142"/>
+      <c r="C136" s="30" t="s">
         <v>659</v>
       </c>
-      <c r="D135" s="13" t="s">
+      <c r="D136" s="17" t="s">
         <v>660</v>
       </c>
-      <c r="E135" s="25"/>
-    </row>
-    <row r="136" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A136" s="137"/>
-      <c r="B136" s="154"/>
-      <c r="C136" s="30" t="s">
+      <c r="E136" s="25"/>
+    </row>
+    <row r="137" spans="1:5" s="2" customFormat="1" ht="37.5" customHeight="1">
+      <c r="A137" s="126"/>
+      <c r="B137" s="143"/>
+      <c r="C137" s="30" t="s">
         <v>661</v>
       </c>
-      <c r="D136" s="17" t="s">
+      <c r="D137" s="29" t="s">
         <v>662</v>
       </c>
-      <c r="E136" s="25"/>
-    </row>
-    <row r="137" spans="1:5" s="2" customFormat="1" ht="37.5" customHeight="1">
-      <c r="A137" s="137"/>
-      <c r="B137" s="155"/>
-      <c r="C137" s="30" t="s">
+      <c r="E137" s="25"/>
+    </row>
+    <row r="138" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A138" s="126"/>
+      <c r="B138" s="132" t="s">
         <v>663</v>
       </c>
-      <c r="D137" s="29" t="s">
+      <c r="C138" s="19" t="s">
         <v>664</v>
       </c>
-      <c r="E137" s="25"/>
-    </row>
-    <row r="138" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A138" s="137"/>
-      <c r="B138" s="131" t="s">
+      <c r="D138" s="13" t="s">
         <v>665</v>
       </c>
-      <c r="C138" s="19" t="s">
+      <c r="E138" s="25"/>
+    </row>
+    <row r="139" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A139" s="126"/>
+      <c r="B139" s="132"/>
+      <c r="C139" s="19" t="s">
         <v>666</v>
       </c>
-      <c r="D138" s="13" t="s">
+      <c r="D139" s="13" t="s">
         <v>667</v>
       </c>
-      <c r="E138" s="25"/>
-    </row>
-    <row r="139" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A139" s="137"/>
-      <c r="B139" s="131"/>
-      <c r="C139" s="19" t="s">
+      <c r="E139" s="25"/>
+    </row>
+    <row r="140" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A140" s="126"/>
+      <c r="B140" s="132"/>
+      <c r="C140" s="19" t="s">
         <v>668</v>
       </c>
-      <c r="D139" s="13" t="s">
+      <c r="D140" s="13" t="s">
         <v>669</v>
       </c>
-      <c r="E139" s="25"/>
-    </row>
-    <row r="140" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A140" s="137"/>
-      <c r="B140" s="131"/>
-      <c r="C140" s="19" t="s">
+      <c r="E140" s="25"/>
+    </row>
+    <row r="141" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A141" s="126"/>
+      <c r="B141" s="132"/>
+      <c r="C141" s="19" t="s">
         <v>670</v>
       </c>
-      <c r="D140" s="13" t="s">
+      <c r="D141" s="13" t="s">
         <v>671</v>
       </c>
-      <c r="E140" s="25"/>
-    </row>
-    <row r="141" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A141" s="137"/>
-      <c r="B141" s="131"/>
-      <c r="C141" s="19" t="s">
+      <c r="E141" s="25"/>
+    </row>
+    <row r="142" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A142" s="126"/>
+      <c r="B142" s="132"/>
+      <c r="C142" s="19" t="s">
         <v>672</v>
       </c>
-      <c r="D141" s="13" t="s">
+      <c r="D142" s="13" t="s">
         <v>673</v>
       </c>
-      <c r="E141" s="25"/>
-    </row>
-    <row r="142" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A142" s="137"/>
-      <c r="B142" s="131"/>
-      <c r="C142" s="19" t="s">
+      <c r="E142" s="25"/>
+    </row>
+    <row r="143" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A143" s="126"/>
+      <c r="B143" s="132"/>
+      <c r="C143" s="19" t="s">
         <v>674</v>
       </c>
-      <c r="D142" s="13" t="s">
+      <c r="D143" s="13" t="s">
         <v>675</v>
       </c>
-      <c r="E142" s="25"/>
-    </row>
-    <row r="143" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A143" s="137"/>
-      <c r="B143" s="131"/>
-      <c r="C143" s="19" t="s">
+      <c r="E143" s="25"/>
+    </row>
+    <row r="144" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A144" s="126"/>
+      <c r="B144" s="132"/>
+      <c r="C144" s="19" t="s">
         <v>676</v>
       </c>
-      <c r="D143" s="13" t="s">
+      <c r="D144" s="13" t="s">
         <v>677</v>
       </c>
-      <c r="E143" s="25"/>
-    </row>
-    <row r="144" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A144" s="137"/>
-      <c r="B144" s="131"/>
-      <c r="C144" s="19" t="s">
+      <c r="E144" s="25"/>
+    </row>
+    <row r="145" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A145" s="126"/>
+      <c r="B145" s="132"/>
+      <c r="C145" s="30" t="s">
         <v>678</v>
       </c>
-      <c r="D144" s="13" t="s">
+      <c r="D145" s="17" t="s">
         <v>679</v>
       </c>
-      <c r="E144" s="25"/>
-    </row>
-    <row r="145" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A145" s="137"/>
-      <c r="B145" s="131"/>
-      <c r="C145" s="30" t="s">
+      <c r="E145" s="25"/>
+    </row>
+    <row r="146" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A146" s="126"/>
+      <c r="B146" s="121" t="s">
         <v>680</v>
       </c>
-      <c r="D145" s="17" t="s">
+      <c r="C146" s="121"/>
+      <c r="D146" s="17" t="s">
         <v>681</v>
       </c>
-      <c r="E145" s="25"/>
-    </row>
-    <row r="146" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A146" s="137"/>
-      <c r="B146" s="124" t="s">
+      <c r="E146" s="18" t="s">
         <v>682</v>
       </c>
-      <c r="C146" s="124"/>
-      <c r="D146" s="17" t="s">
+    </row>
+    <row r="147" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A147" s="126"/>
+      <c r="B147" s="123" t="s">
         <v>683</v>
       </c>
-      <c r="E146" s="18" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A147" s="137"/>
-      <c r="B147" s="126" t="s">
-        <v>685</v>
-      </c>
-      <c r="C147" s="126"/>
+      <c r="C147" s="123"/>
       <c r="D147" s="21"/>
       <c r="E147" s="31" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A148" s="127"/>
+      <c r="B148" s="137" t="s">
+        <v>685</v>
+      </c>
+      <c r="C148" s="138"/>
+      <c r="D148" s="13" t="s">
         <v>686</v>
       </c>
-    </row>
-    <row r="148" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A148" s="137"/>
-      <c r="B148" s="127" t="s">
-        <v>730</v>
-      </c>
-      <c r="C148" s="128"/>
-      <c r="D148" s="13" t="s">
-        <v>729</v>
-      </c>
       <c r="E148" s="22"/>
     </row>
-    <row r="149" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A149" s="137"/>
-      <c r="B149" s="127" t="s">
-        <v>740</v>
-      </c>
-      <c r="C149" s="128"/>
-      <c r="D149" s="13" t="s">
-        <v>734</v>
-      </c>
-      <c r="E149" s="31" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A150" s="137"/>
-      <c r="B150" s="127" t="s">
-        <v>731</v>
-      </c>
-      <c r="C150" s="128"/>
-      <c r="D150" s="13" t="s">
-        <v>735</v>
-      </c>
-      <c r="E150" s="31" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A151" s="138"/>
-      <c r="B151" s="127" t="s">
-        <v>732</v>
-      </c>
-      <c r="C151" s="128"/>
-      <c r="D151" s="13" t="s">
-        <v>736</v>
-      </c>
-      <c r="E151" s="31" t="s">
-        <v>739</v>
+    <row r="149" spans="1:5" s="2" customFormat="1" ht="22.5" customHeight="1">
+      <c r="A149" s="128" t="s">
+        <v>687</v>
+      </c>
+      <c r="B149" s="121" t="s">
+        <v>688</v>
+      </c>
+      <c r="C149" s="135"/>
+      <c r="D149" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="E149" s="11" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" s="2" customFormat="1" ht="22.5" customHeight="1">
+      <c r="A150" s="129"/>
+      <c r="B150" s="123" t="s">
+        <v>689</v>
+      </c>
+      <c r="C150" s="12" t="s">
+        <v>690</v>
+      </c>
+      <c r="D150" s="26" t="s">
+        <v>691</v>
+      </c>
+      <c r="E150" s="32" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" s="2" customFormat="1" ht="22.5" customHeight="1">
+      <c r="A151" s="129"/>
+      <c r="B151" s="123"/>
+      <c r="C151" s="12" t="s">
+        <v>693</v>
+      </c>
+      <c r="D151" s="26" t="s">
+        <v>694</v>
+      </c>
+      <c r="E151" s="32" t="s">
+        <v>695</v>
       </c>
     </row>
     <row r="152" spans="1:5" s="2" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A152" s="139" t="s">
-        <v>687</v>
-      </c>
-      <c r="B152" s="124" t="s">
-        <v>733</v>
-      </c>
-      <c r="C152" s="132"/>
-      <c r="D152" s="10" t="s">
-        <v>297</v>
-      </c>
-      <c r="E152" s="11" t="s">
-        <v>298</v>
+      <c r="A152" s="129"/>
+      <c r="B152" s="123"/>
+      <c r="C152" s="12" t="s">
+        <v>696</v>
+      </c>
+      <c r="D152" s="27" t="s">
+        <v>697</v>
+      </c>
+      <c r="E152" s="33" t="s">
+        <v>698</v>
       </c>
     </row>
     <row r="153" spans="1:5" s="2" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A153" s="140"/>
-      <c r="B153" s="126" t="s">
-        <v>688</v>
-      </c>
-      <c r="C153" s="12" t="s">
-        <v>689</v>
-      </c>
+      <c r="A153" s="129"/>
+      <c r="B153" s="123" t="s">
+        <v>699</v>
+      </c>
+      <c r="C153" s="135"/>
       <c r="D153" s="26" t="s">
-        <v>690</v>
+        <v>700</v>
       </c>
       <c r="E153" s="32" t="s">
-        <v>691</v>
+        <v>701</v>
       </c>
     </row>
     <row r="154" spans="1:5" s="2" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A154" s="140"/>
-      <c r="B154" s="126"/>
-      <c r="C154" s="12" t="s">
-        <v>692</v>
-      </c>
-      <c r="D154" s="26" t="s">
-        <v>693</v>
-      </c>
-      <c r="E154" s="32" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="155" spans="1:5" s="2" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A155" s="140"/>
-      <c r="B155" s="126"/>
-      <c r="C155" s="12" t="s">
-        <v>695</v>
-      </c>
-      <c r="D155" s="27" t="s">
-        <v>696</v>
-      </c>
-      <c r="E155" s="33" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="156" spans="1:5" s="2" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A156" s="140"/>
-      <c r="B156" s="126" t="s">
-        <v>698</v>
-      </c>
-      <c r="C156" s="132"/>
-      <c r="D156" s="26" t="s">
-        <v>699</v>
-      </c>
-      <c r="E156" s="32" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="157" spans="1:5" s="2" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A157" s="140"/>
-      <c r="B157" s="124" t="s">
-        <v>701</v>
-      </c>
-      <c r="C157" s="133"/>
-      <c r="D157" s="17" t="s">
+      <c r="A154" s="129"/>
+      <c r="B154" s="121" t="s">
         <v>702</v>
       </c>
-      <c r="E157" s="34" t="s">
+      <c r="C154" s="136"/>
+      <c r="D154" s="17" t="s">
         <v>703</v>
       </c>
+      <c r="E154" s="34" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" s="2" customFormat="1" ht="23.25" customHeight="1">
+      <c r="A155" s="130" t="s">
+        <v>705</v>
+      </c>
+      <c r="B155" s="121" t="s">
+        <v>706</v>
+      </c>
+      <c r="C155" s="122"/>
+      <c r="D155" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E155" s="35"/>
+    </row>
+    <row r="156" spans="1:5" s="2" customFormat="1" ht="23.25" customHeight="1">
+      <c r="A156" s="130"/>
+      <c r="B156" s="123" t="s">
+        <v>707</v>
+      </c>
+      <c r="C156" s="123"/>
+      <c r="D156" s="13" t="s">
+        <v>708</v>
+      </c>
+      <c r="E156" s="36"/>
+    </row>
+    <row r="157" spans="1:5" s="2" customFormat="1" ht="23.25" customHeight="1">
+      <c r="A157" s="130"/>
+      <c r="B157" s="121" t="s">
+        <v>709</v>
+      </c>
+      <c r="C157" s="122"/>
+      <c r="D157" s="37"/>
+      <c r="E157" s="11" t="s">
+        <v>296</v>
+      </c>
     </row>
     <row r="158" spans="1:5" s="2" customFormat="1" ht="23.25" customHeight="1">
-      <c r="A158" s="141" t="s">
-        <v>704</v>
-      </c>
-      <c r="B158" s="124" t="s">
-        <v>705</v>
-      </c>
-      <c r="C158" s="134"/>
-      <c r="D158" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="E158" s="35"/>
+      <c r="A158" s="130"/>
+      <c r="B158" s="133" t="s">
+        <v>710</v>
+      </c>
+      <c r="C158" s="38" t="s">
+        <v>711</v>
+      </c>
+      <c r="D158" s="39"/>
+      <c r="E158" s="14" t="s">
+        <v>712</v>
+      </c>
     </row>
     <row r="159" spans="1:5" s="2" customFormat="1" ht="23.25" customHeight="1">
-      <c r="A159" s="141"/>
-      <c r="B159" s="126" t="s">
-        <v>706</v>
-      </c>
-      <c r="C159" s="126"/>
-      <c r="D159" s="13" t="s">
-        <v>707</v>
-      </c>
-      <c r="E159" s="36"/>
+      <c r="A159" s="130"/>
+      <c r="B159" s="133"/>
+      <c r="C159" s="38" t="s">
+        <v>713</v>
+      </c>
+      <c r="D159" s="39"/>
+      <c r="E159" s="14" t="s">
+        <v>714</v>
+      </c>
     </row>
     <row r="160" spans="1:5" s="2" customFormat="1" ht="23.25" customHeight="1">
-      <c r="A160" s="141"/>
-      <c r="B160" s="124" t="s">
-        <v>708</v>
-      </c>
-      <c r="C160" s="134"/>
-      <c r="D160" s="37"/>
-      <c r="E160" s="11" t="s">
-        <v>298</v>
+      <c r="A160" s="130"/>
+      <c r="B160" s="133"/>
+      <c r="C160" s="38" t="s">
+        <v>715</v>
+      </c>
+      <c r="D160" s="39"/>
+      <c r="E160" s="14" t="s">
+        <v>716</v>
       </c>
     </row>
     <row r="161" spans="1:5" s="2" customFormat="1" ht="23.25" customHeight="1">
-      <c r="A161" s="141"/>
-      <c r="B161" s="143" t="s">
-        <v>709</v>
-      </c>
+      <c r="A161" s="130"/>
+      <c r="B161" s="133"/>
       <c r="C161" s="38" t="s">
-        <v>710</v>
+        <v>717</v>
       </c>
       <c r="D161" s="39"/>
       <c r="E161" s="14" t="s">
-        <v>711</v>
+        <v>718</v>
       </c>
     </row>
     <row r="162" spans="1:5" s="2" customFormat="1" ht="23.25" customHeight="1">
-      <c r="A162" s="141"/>
-      <c r="B162" s="143"/>
+      <c r="A162" s="130"/>
+      <c r="B162" s="133"/>
       <c r="C162" s="38" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="D162" s="39"/>
       <c r="E162" s="14" t="s">
-        <v>713</v>
+        <v>720</v>
       </c>
     </row>
     <row r="163" spans="1:5" s="2" customFormat="1" ht="23.25" customHeight="1">
-      <c r="A163" s="141"/>
-      <c r="B163" s="143"/>
+      <c r="A163" s="130"/>
+      <c r="B163" s="133"/>
       <c r="C163" s="38" t="s">
-        <v>714</v>
+        <v>721</v>
       </c>
       <c r="D163" s="39"/>
       <c r="E163" s="14" t="s">
-        <v>715</v>
+        <v>722</v>
       </c>
     </row>
     <row r="164" spans="1:5" s="2" customFormat="1" ht="23.25" customHeight="1">
-      <c r="A164" s="141"/>
-      <c r="B164" s="143"/>
+      <c r="A164" s="130"/>
+      <c r="B164" s="133"/>
       <c r="C164" s="38" t="s">
-        <v>716</v>
+        <v>723</v>
       </c>
       <c r="D164" s="39"/>
       <c r="E164" s="14" t="s">
-        <v>717</v>
+        <v>724</v>
       </c>
     </row>
     <row r="165" spans="1:5" s="2" customFormat="1" ht="23.25" customHeight="1">
-      <c r="A165" s="141"/>
-      <c r="B165" s="143"/>
+      <c r="A165" s="130"/>
+      <c r="B165" s="133"/>
       <c r="C165" s="38" t="s">
-        <v>718</v>
+        <v>725</v>
       </c>
       <c r="D165" s="39"/>
       <c r="E165" s="14" t="s">
-        <v>719</v>
+        <v>726</v>
       </c>
     </row>
     <row r="166" spans="1:5" s="2" customFormat="1" ht="23.25" customHeight="1">
-      <c r="A166" s="141"/>
-      <c r="B166" s="143"/>
-      <c r="C166" s="38" t="s">
-        <v>720</v>
-      </c>
-      <c r="D166" s="39"/>
-      <c r="E166" s="14" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="167" spans="1:5" s="2" customFormat="1" ht="23.25" customHeight="1">
-      <c r="A167" s="141"/>
-      <c r="B167" s="143"/>
-      <c r="C167" s="38" t="s">
-        <v>722</v>
-      </c>
-      <c r="D167" s="39"/>
-      <c r="E167" s="14" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="168" spans="1:5" s="2" customFormat="1" ht="23.25" customHeight="1">
-      <c r="A168" s="141"/>
-      <c r="B168" s="143"/>
-      <c r="C168" s="38" t="s">
-        <v>724</v>
-      </c>
-      <c r="D168" s="39"/>
-      <c r="E168" s="14" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="169" spans="1:5" s="2" customFormat="1" ht="23.25" customHeight="1">
-      <c r="A169" s="142"/>
-      <c r="B169" s="144"/>
-      <c r="C169" s="40" t="s">
-        <v>726</v>
-      </c>
-      <c r="D169" s="41"/>
-      <c r="E169" s="42" t="s">
+      <c r="A166" s="131"/>
+      <c r="B166" s="134"/>
+      <c r="C166" s="40" t="s">
         <v>727</v>
       </c>
-    </row>
-    <row r="170" spans="1:5" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="A170" s="135" t="s">
+      <c r="D166" s="41"/>
+      <c r="E166" s="42" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="A167" s="124" t="s">
+        <v>285</v>
+      </c>
+      <c r="B167" s="124"/>
+      <c r="C167" s="44" t="s">
         <v>286</v>
       </c>
-      <c r="B170" s="135"/>
-      <c r="C170" s="44" t="s">
+      <c r="D167" s="45" t="s">
         <v>287</v>
       </c>
-      <c r="D170" s="45" t="s">
+      <c r="E167" s="46"/>
+    </row>
+    <row r="168" spans="1:5" s="3" customFormat="1" ht="17.25" customHeight="1">
+      <c r="A168" s="43"/>
+      <c r="B168" s="47" t="s">
         <v>288</v>
       </c>
-      <c r="E170" s="46"/>
-    </row>
-    <row r="171" spans="1:5" s="3" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A171" s="43"/>
-      <c r="B171" s="47" t="s">
+      <c r="C168" s="48"/>
+      <c r="D168" s="49"/>
+      <c r="E168" s="49"/>
+    </row>
+    <row r="169" spans="1:5" s="3" customFormat="1" ht="17.25" customHeight="1">
+      <c r="A169" s="50"/>
+      <c r="B169" s="48" t="s">
         <v>289</v>
       </c>
-      <c r="C171" s="48"/>
-      <c r="D171" s="49"/>
-      <c r="E171" s="49"/>
-    </row>
-    <row r="172" spans="1:5" s="3" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A172" s="50"/>
-      <c r="B172" s="48" t="s">
-        <v>290</v>
-      </c>
-      <c r="C172" s="48"/>
-      <c r="D172" s="51"/>
-      <c r="E172" s="52"/>
-    </row>
-    <row r="173" spans="1:5" s="3" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A173" s="53"/>
-      <c r="B173" s="54" t="s">
-        <v>728</v>
-      </c>
-      <c r="C173" s="55"/>
-      <c r="D173" s="49"/>
-      <c r="E173" s="49"/>
-    </row>
-    <row r="174" spans="1:5" s="2" customFormat="1" ht="13.5">
-      <c r="D174" s="56"/>
-      <c r="E174" s="56"/>
-    </row>
-    <row r="175" spans="1:5" s="2" customFormat="1">
-      <c r="A175" s="4"/>
-      <c r="B175" s="57"/>
-      <c r="C175" s="4"/>
-      <c r="D175" s="5"/>
-      <c r="E175" s="5"/>
-    </row>
-    <row r="176" spans="1:5" s="2" customFormat="1">
-      <c r="A176" s="4"/>
-      <c r="B176" s="4"/>
-      <c r="C176" s="4"/>
-      <c r="D176" s="5"/>
-      <c r="E176" s="5"/>
+      <c r="C169" s="48"/>
+      <c r="D169" s="51"/>
+      <c r="E169" s="52"/>
+    </row>
+    <row r="170" spans="1:5" s="3" customFormat="1" ht="17.25" customHeight="1">
+      <c r="A170" s="53"/>
+      <c r="B170" s="54" t="s">
+        <v>729</v>
+      </c>
+      <c r="C170" s="55"/>
+      <c r="D170" s="49"/>
+      <c r="E170" s="49"/>
+    </row>
+    <row r="171" spans="1:5" s="2" customFormat="1" ht="13.5">
+      <c r="D171" s="56"/>
+      <c r="E171" s="56"/>
+    </row>
+    <row r="172" spans="1:5" s="2" customFormat="1">
+      <c r="A172" s="4"/>
+      <c r="B172" s="57"/>
+      <c r="C172" s="4"/>
+      <c r="D172" s="5"/>
+      <c r="E172" s="5"/>
+    </row>
+    <row r="173" spans="1:5" s="2" customFormat="1">
+      <c r="A173" s="4"/>
+      <c r="B173" s="4"/>
+      <c r="C173" s="4"/>
+      <c r="D173" s="5"/>
+      <c r="E173" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="40">
-    <mergeCell ref="B149:C149"/>
-    <mergeCell ref="B151:C151"/>
-    <mergeCell ref="B150:C150"/>
-    <mergeCell ref="B160:C160"/>
-    <mergeCell ref="B153:B155"/>
-    <mergeCell ref="A170:B170"/>
-    <mergeCell ref="A5:A151"/>
-    <mergeCell ref="A152:A157"/>
-    <mergeCell ref="A158:A169"/>
-    <mergeCell ref="B6:B11"/>
-    <mergeCell ref="B12:B14"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="B18:B33"/>
-    <mergeCell ref="B34:B36"/>
-    <mergeCell ref="B37:B40"/>
-    <mergeCell ref="B161:B169"/>
-    <mergeCell ref="B80:B83"/>
-    <mergeCell ref="B84:B90"/>
-    <mergeCell ref="B91:B97"/>
-    <mergeCell ref="B152:C152"/>
-    <mergeCell ref="B156:C156"/>
-    <mergeCell ref="B157:C157"/>
-    <mergeCell ref="B158:C158"/>
-    <mergeCell ref="B159:C159"/>
+  <mergeCells count="37">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B146:C146"/>
+    <mergeCell ref="B147:C147"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="A3:C4"/>
     <mergeCell ref="B148:C148"/>
     <mergeCell ref="B41:B55"/>
     <mergeCell ref="B56:B60"/>
@@ -7043,18 +6959,31 @@
     <mergeCell ref="B98:B117"/>
     <mergeCell ref="B118:B137"/>
     <mergeCell ref="B138:B145"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B146:C146"/>
-    <mergeCell ref="B147:C147"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="A3:C4"/>
+    <mergeCell ref="B149:C149"/>
+    <mergeCell ref="B153:C153"/>
+    <mergeCell ref="B154:C154"/>
+    <mergeCell ref="B155:C155"/>
+    <mergeCell ref="B156:C156"/>
+    <mergeCell ref="B157:C157"/>
+    <mergeCell ref="B150:B152"/>
+    <mergeCell ref="A167:B167"/>
+    <mergeCell ref="A5:A148"/>
+    <mergeCell ref="A149:A154"/>
+    <mergeCell ref="A155:A166"/>
+    <mergeCell ref="B6:B11"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="B18:B33"/>
+    <mergeCell ref="B34:B36"/>
+    <mergeCell ref="B37:B40"/>
+    <mergeCell ref="B158:B166"/>
+    <mergeCell ref="B80:B83"/>
+    <mergeCell ref="B84:B90"/>
+    <mergeCell ref="B91:B97"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:E1 D3:E3 D174:E65537 D5:E169"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:E1 D3:E3 D171:E65534 D5:E166"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:B2">
       <formula1>"报送口径：境内汇总数据,报送口径：法人汇总数据(含境外分行),报送口径：合并报表数据(含附属公司)"</formula1>
     </dataValidation>
@@ -7065,7 +6994,7 @@
   <rowBreaks count="3" manualBreakCount="3">
     <brk id="60" max="16383" man="1"/>
     <brk id="117" max="16383" man="1"/>
-    <brk id="175" max="16383" man="1"/>
+    <brk id="172" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/G06Monthreport.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/G06Monthreport.xlsx
@@ -5,11 +5,11 @@
   <workbookPr showInkAnnotation="0" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\新建文件夹\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\项目\主产品\dev\tams-svreport-parent\tams-svreport\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="10392" windowHeight="4992" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="10395" windowHeight="4995"/>
   </bookViews>
   <sheets>
     <sheet name="G0601" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">'G0601'!$A$1:$J$66</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'G0602'!$A$1:$G$182</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" concurrentCalc="0"/>
 </workbook>
 </file>
 
@@ -1655,69 +1655,45 @@
     <t>${GMLCCP.xgdurationprodcounts}</t>
   </si>
   <si>
-    <t>${GMLCCP.xgbottombalance}</t>
-  </si>
-  <si>
     <t>${GMLCCP.prodpayamount}</t>
   </si>
   <si>
     <t>${SMLCCP.xgdurationprodcounts}</t>
   </si>
   <si>
-    <t>${SMLCCP.xgbottombalance}</t>
-  </si>
-  <si>
     <t>${SMLCCP.prodpayamount}</t>
   </si>
   <si>
-    <t>${SUM_MJFS.xgbottombalance}</t>
-  </si>
-  <si>
     <t>${SUM_MJFS.prodpayamount}</t>
   </si>
   <si>
     <t>${GDSYL.xgdurationprodcounts}</t>
   </si>
   <si>
-    <t>${GDSYL.xgbottombalance}</t>
-  </si>
-  <si>
     <t>${GDSYL.prodpayamount}</t>
   </si>
   <si>
     <t>${QYL.xgdurationprodcounts}</t>
   </si>
   <si>
-    <t>${QYL.xgbottombalance}</t>
-  </si>
-  <si>
     <t>${QYL.prodpayamount}</t>
   </si>
   <si>
     <t>${SPJJRYSPL.xgdurationprodcounts}</t>
   </si>
   <si>
-    <t>${SPJJRYSPL.xgbottombalance}</t>
-  </si>
-  <si>
     <t>${SPJJRYSPL.prodpayamount}</t>
   </si>
   <si>
     <t>${HHL.xgdurationprodcounts}</t>
   </si>
   <si>
-    <t>${HHL.xgbottombalance}</t>
-  </si>
-  <si>
     <t>${HHL.prodpayamount}</t>
   </si>
   <si>
     <t>${SUM_TZXZ.xgdurationprodcounts}</t>
   </si>
   <si>
-    <t>${SUM_TZXZ.xgbottombalance}</t>
-  </si>
-  <si>
     <t>${SUM_TZXZ.prodpayamount}</t>
   </si>
   <si>
@@ -1869,9 +1845,6 @@
   </si>
   <si>
     <t>${YLLCCP.balance}</t>
-  </si>
-  <si>
-    <t>${YLLCCP.xgbottombalance}</t>
   </si>
   <si>
     <t>${YLLCCP.prodpayamount}</t>
@@ -4251,6 +4224,42 @@
   </si>
   <si>
     <t>${AMT3_3_9.xgbottombalance}</t>
+  </si>
+  <si>
+    <t>${GMLCCP.xgbalance}</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>${SMLCCP.xgbalance}</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>${SUM_MJFS.xgbalance}</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>${GDSYL.xgbalance}</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>${QYL.xgbalance}</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>${SPJJRYSPL.xgbalance}</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>${HHL.xgbalance}</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>${SUM_TZXZ.xgbalance}</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>${YLLCCP.xgbalance}</t>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -5020,43 +5029,48 @@
     <xf numFmtId="49" fontId="12" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5069,34 +5083,102 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="17" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5120,81 +5202,8 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="17" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -5561,43 +5570,43 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:M66"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="8.5" customWidth="1"/>
-    <col min="2" max="2" width="16.8984375" customWidth="1"/>
+    <col min="2" max="2" width="16.875" customWidth="1"/>
     <col min="3" max="3" width="29.5" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="17.09765625" customWidth="1"/>
-    <col min="6" max="6" width="12.69921875" customWidth="1"/>
-    <col min="7" max="7" width="12.3984375" customWidth="1"/>
-    <col min="8" max="8" width="10.09765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.125" customWidth="1"/>
+    <col min="6" max="6" width="12.75" customWidth="1"/>
+    <col min="7" max="7" width="12.375" customWidth="1"/>
+    <col min="8" max="8" width="10.125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13" customWidth="1"/>
-    <col min="10" max="10" width="13.09765625" customWidth="1"/>
+    <col min="10" max="10" width="13.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="34.5" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="103" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
+      <c r="B1" s="103"/>
+      <c r="C1" s="103"/>
+      <c r="D1" s="103"/>
+      <c r="E1" s="103"/>
+      <c r="F1" s="103"/>
+      <c r="G1" s="103"/>
+      <c r="H1" s="103"/>
+      <c r="I1" s="103"/>
+      <c r="J1" s="103"/>
     </row>
     <row r="2" spans="1:13" s="54" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A2" s="120" t="s">
+      <c r="A2" s="104" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="120"/>
-      <c r="E2" s="121" t="s">
+      <c r="B2" s="104"/>
+      <c r="E2" s="105" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="122"/>
+      <c r="F2" s="106"/>
       <c r="G2" s="55"/>
       <c r="H2" s="56"/>
       <c r="J2" s="79" t="s">
@@ -5677,7 +5686,7 @@
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="103" t="s">
+      <c r="A5" s="114" t="s">
         <v>18</v>
       </c>
       <c r="B5" s="108" t="s">
@@ -5703,10 +5712,10 @@
         <v>24</v>
       </c>
       <c r="J5" s="62" t="s">
+        <v>1121</v>
+      </c>
+      <c r="K5" s="62" t="s">
         <v>523</v>
-      </c>
-      <c r="K5" s="62" t="s">
-        <v>524</v>
       </c>
       <c r="L5" s="62" t="s">
         <v>25</v>
@@ -5716,7 +5725,7 @@
       </c>
     </row>
     <row r="6" spans="1:13">
-      <c r="A6" s="103"/>
+      <c r="A6" s="114"/>
       <c r="B6" s="108" t="s">
         <v>27</v>
       </c>
@@ -5734,16 +5743,16 @@
         <v>31</v>
       </c>
       <c r="H6" s="62" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="I6" s="62" t="s">
         <v>32</v>
       </c>
       <c r="J6" s="62" t="s">
-        <v>526</v>
+        <v>1122</v>
       </c>
       <c r="K6" s="62" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="L6" s="62" t="s">
         <v>33</v>
@@ -5753,11 +5762,11 @@
       </c>
     </row>
     <row r="7" spans="1:13">
-      <c r="A7" s="103"/>
-      <c r="B7" s="106" t="s">
+      <c r="A7" s="114"/>
+      <c r="B7" s="115" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="106"/>
+      <c r="C7" s="115"/>
       <c r="D7" s="63" t="s">
         <v>36</v>
       </c>
@@ -5777,10 +5786,10 @@
         <v>40</v>
       </c>
       <c r="J7" s="63" t="s">
-        <v>528</v>
+        <v>1123</v>
       </c>
       <c r="K7" s="63" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="L7" s="63" t="s">
         <v>41</v>
@@ -5790,7 +5799,7 @@
       </c>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="103" t="s">
+      <c r="A8" s="114" t="s">
         <v>43</v>
       </c>
       <c r="B8" s="108" t="s">
@@ -5810,16 +5819,16 @@
         <v>48</v>
       </c>
       <c r="H8" s="61" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="I8" s="61" t="s">
         <v>49</v>
       </c>
       <c r="J8" s="61" t="s">
-        <v>531</v>
+        <v>1124</v>
       </c>
       <c r="K8" s="61" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="L8" s="61" t="s">
         <v>50</v>
@@ -5829,7 +5838,7 @@
       </c>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="103"/>
+      <c r="A9" s="114"/>
       <c r="B9" s="108" t="s">
         <v>52</v>
       </c>
@@ -5847,16 +5856,16 @@
         <v>56</v>
       </c>
       <c r="H9" s="61" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="I9" s="61" t="s">
         <v>57</v>
       </c>
       <c r="J9" s="61" t="s">
-        <v>534</v>
+        <v>1125</v>
       </c>
       <c r="K9" s="61" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="L9" s="61" t="s">
         <v>58</v>
@@ -5866,7 +5875,7 @@
       </c>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="103"/>
+      <c r="A10" s="114"/>
       <c r="B10" s="108" t="s">
         <v>60</v>
       </c>
@@ -5884,16 +5893,16 @@
         <v>64</v>
       </c>
       <c r="H10" s="61" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="I10" s="61" t="s">
         <v>65</v>
       </c>
       <c r="J10" s="61" t="s">
-        <v>537</v>
+        <v>1126</v>
       </c>
       <c r="K10" s="61" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="L10" s="61" t="s">
         <v>66</v>
@@ -5903,7 +5912,7 @@
       </c>
     </row>
     <row r="11" spans="1:13">
-      <c r="A11" s="103"/>
+      <c r="A11" s="114"/>
       <c r="B11" s="108" t="s">
         <v>68</v>
       </c>
@@ -5921,16 +5930,16 @@
         <v>72</v>
       </c>
       <c r="H11" s="61" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="I11" s="61" t="s">
         <v>73</v>
       </c>
       <c r="J11" s="61" t="s">
-        <v>540</v>
+        <v>1127</v>
       </c>
       <c r="K11" s="61" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="L11" s="61" t="s">
         <v>74</v>
@@ -5940,11 +5949,11 @@
       </c>
     </row>
     <row r="12" spans="1:13">
-      <c r="A12" s="103"/>
-      <c r="B12" s="106" t="s">
+      <c r="A12" s="114"/>
+      <c r="B12" s="115" t="s">
         <v>76</v>
       </c>
-      <c r="C12" s="106"/>
+      <c r="C12" s="115"/>
       <c r="D12" s="63" t="s">
         <v>77</v>
       </c>
@@ -5958,16 +5967,16 @@
         <v>80</v>
       </c>
       <c r="H12" s="63" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="I12" s="63" t="s">
         <v>81</v>
       </c>
       <c r="J12" s="63" t="s">
-        <v>543</v>
+        <v>1128</v>
       </c>
       <c r="K12" s="63" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="L12" s="63" t="s">
         <v>82</v>
@@ -5977,10 +5986,10 @@
       </c>
     </row>
     <row r="13" spans="1:13">
-      <c r="A13" s="103" t="s">
+      <c r="A13" s="114" t="s">
         <v>84</v>
       </c>
-      <c r="B13" s="116" t="s">
+      <c r="B13" s="117" t="s">
         <v>85</v>
       </c>
       <c r="C13" s="64" t="s">
@@ -6008,8 +6017,8 @@
       <c r="M13" s="86"/>
     </row>
     <row r="14" spans="1:13">
-      <c r="A14" s="103"/>
-      <c r="B14" s="116"/>
+      <c r="A14" s="114"/>
+      <c r="B14" s="117"/>
       <c r="C14" s="64" t="s">
         <v>92</v>
       </c>
@@ -6035,8 +6044,8 @@
       <c r="M14" s="86"/>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" s="103"/>
-      <c r="B15" s="116"/>
+      <c r="A15" s="114"/>
+      <c r="B15" s="117"/>
       <c r="C15" s="64" t="s">
         <v>98</v>
       </c>
@@ -6062,8 +6071,8 @@
       <c r="M15" s="86"/>
     </row>
     <row r="16" spans="1:13" ht="24">
-      <c r="A16" s="103"/>
-      <c r="B16" s="116"/>
+      <c r="A16" s="114"/>
+      <c r="B16" s="117"/>
       <c r="C16" s="64" t="s">
         <v>104</v>
       </c>
@@ -6089,8 +6098,8 @@
       <c r="M16" s="86"/>
     </row>
     <row r="17" spans="1:13">
-      <c r="A17" s="103"/>
-      <c r="B17" s="116" t="s">
+      <c r="A17" s="114"/>
+      <c r="B17" s="117" t="s">
         <v>110</v>
       </c>
       <c r="C17" s="64" t="s">
@@ -6118,8 +6127,8 @@
       <c r="M17" s="86"/>
     </row>
     <row r="18" spans="1:13">
-      <c r="A18" s="103"/>
-      <c r="B18" s="116"/>
+      <c r="A18" s="114"/>
+      <c r="B18" s="117"/>
       <c r="C18" s="64" t="s">
         <v>117</v>
       </c>
@@ -6145,11 +6154,11 @@
       <c r="M18" s="86"/>
     </row>
     <row r="19" spans="1:13">
-      <c r="A19" s="103"/>
-      <c r="B19" s="115" t="s">
+      <c r="A19" s="114"/>
+      <c r="B19" s="116" t="s">
         <v>123</v>
       </c>
-      <c r="C19" s="115"/>
+      <c r="C19" s="116"/>
       <c r="D19" s="65" t="s">
         <v>124</v>
       </c>
@@ -6172,10 +6181,10 @@
       <c r="M19" s="86"/>
     </row>
     <row r="20" spans="1:13">
-      <c r="A20" s="103" t="s">
+      <c r="A20" s="114" t="s">
         <v>129</v>
       </c>
-      <c r="B20" s="116" t="s">
+      <c r="B20" s="117" t="s">
         <v>130</v>
       </c>
       <c r="C20" s="95" t="s">
@@ -6203,8 +6212,8 @@
       <c r="M20" s="86"/>
     </row>
     <row r="21" spans="1:13">
-      <c r="A21" s="103"/>
-      <c r="B21" s="116"/>
+      <c r="A21" s="114"/>
+      <c r="B21" s="117"/>
       <c r="C21" s="95" t="s">
         <v>506</v>
       </c>
@@ -6230,8 +6239,8 @@
       <c r="M21" s="86"/>
     </row>
     <row r="22" spans="1:13">
-      <c r="A22" s="103"/>
-      <c r="B22" s="116"/>
+      <c r="A22" s="114"/>
+      <c r="B22" s="117"/>
       <c r="C22" s="95" t="s">
         <v>141</v>
       </c>
@@ -6257,8 +6266,8 @@
       <c r="M22" s="86"/>
     </row>
     <row r="23" spans="1:13">
-      <c r="A23" s="103"/>
-      <c r="B23" s="116"/>
+      <c r="A23" s="114"/>
+      <c r="B23" s="117"/>
       <c r="C23" s="95" t="s">
         <v>147</v>
       </c>
@@ -6284,8 +6293,8 @@
       <c r="M23" s="86"/>
     </row>
     <row r="24" spans="1:13">
-      <c r="A24" s="103"/>
-      <c r="B24" s="116"/>
+      <c r="A24" s="114"/>
+      <c r="B24" s="117"/>
       <c r="C24" s="95" t="s">
         <v>153</v>
       </c>
@@ -6311,8 +6320,8 @@
       <c r="M24" s="86"/>
     </row>
     <row r="25" spans="1:13">
-      <c r="A25" s="103"/>
-      <c r="B25" s="116"/>
+      <c r="A25" s="114"/>
+      <c r="B25" s="117"/>
       <c r="C25" s="94" t="s">
         <v>159</v>
       </c>
@@ -6338,8 +6347,8 @@
       <c r="M25" s="86"/>
     </row>
     <row r="26" spans="1:13">
-      <c r="A26" s="103"/>
-      <c r="B26" s="116" t="s">
+      <c r="A26" s="114"/>
+      <c r="B26" s="117" t="s">
         <v>165</v>
       </c>
       <c r="C26" s="95" t="s">
@@ -6367,8 +6376,8 @@
       <c r="M26" s="86"/>
     </row>
     <row r="27" spans="1:13">
-      <c r="A27" s="103"/>
-      <c r="B27" s="118"/>
+      <c r="A27" s="114"/>
+      <c r="B27" s="119"/>
       <c r="C27" s="95" t="s">
         <v>172</v>
       </c>
@@ -6394,8 +6403,8 @@
       <c r="M27" s="86"/>
     </row>
     <row r="28" spans="1:13">
-      <c r="A28" s="103"/>
-      <c r="B28" s="118"/>
+      <c r="A28" s="114"/>
+      <c r="B28" s="119"/>
       <c r="C28" s="95" t="s">
         <v>178</v>
       </c>
@@ -6421,8 +6430,8 @@
       <c r="M28" s="86"/>
     </row>
     <row r="29" spans="1:13">
-      <c r="A29" s="103"/>
-      <c r="B29" s="118"/>
+      <c r="A29" s="114"/>
+      <c r="B29" s="119"/>
       <c r="C29" s="95" t="s">
         <v>184</v>
       </c>
@@ -6448,8 +6457,8 @@
       <c r="M29" s="86"/>
     </row>
     <row r="30" spans="1:13">
-      <c r="A30" s="103"/>
-      <c r="B30" s="118"/>
+      <c r="A30" s="114"/>
+      <c r="B30" s="119"/>
       <c r="C30" s="95" t="s">
         <v>190</v>
       </c>
@@ -6475,8 +6484,8 @@
       <c r="M30" s="86"/>
     </row>
     <row r="31" spans="1:13">
-      <c r="A31" s="103"/>
-      <c r="B31" s="118"/>
+      <c r="A31" s="114"/>
+      <c r="B31" s="119"/>
       <c r="C31" s="95" t="s">
         <v>196</v>
       </c>
@@ -6502,8 +6511,8 @@
       <c r="M31" s="86"/>
     </row>
     <row r="32" spans="1:13">
-      <c r="A32" s="103"/>
-      <c r="B32" s="118"/>
+      <c r="A32" s="114"/>
+      <c r="B32" s="119"/>
       <c r="C32" s="95" t="s">
         <v>202</v>
       </c>
@@ -6529,8 +6538,8 @@
       <c r="M32" s="86"/>
     </row>
     <row r="33" spans="1:13">
-      <c r="A33" s="103"/>
-      <c r="B33" s="118"/>
+      <c r="A33" s="114"/>
+      <c r="B33" s="119"/>
       <c r="C33" s="95" t="s">
         <v>208</v>
       </c>
@@ -6556,8 +6565,8 @@
       <c r="M33" s="86"/>
     </row>
     <row r="34" spans="1:13">
-      <c r="A34" s="103"/>
-      <c r="B34" s="118"/>
+      <c r="A34" s="114"/>
+      <c r="B34" s="119"/>
       <c r="C34" s="94" t="s">
         <v>214</v>
       </c>
@@ -6583,11 +6592,11 @@
       <c r="M34" s="86"/>
     </row>
     <row r="35" spans="1:13">
-      <c r="A35" s="103"/>
-      <c r="B35" s="117" t="s">
+      <c r="A35" s="114"/>
+      <c r="B35" s="118" t="s">
         <v>220</v>
       </c>
-      <c r="C35" s="117"/>
+      <c r="C35" s="118"/>
       <c r="D35" s="63" t="s">
         <v>221</v>
       </c>
@@ -6610,7 +6619,7 @@
       <c r="M35" s="86"/>
     </row>
     <row r="36" spans="1:13">
-      <c r="A36" s="103" t="s">
+      <c r="A36" s="114" t="s">
         <v>226</v>
       </c>
       <c r="B36" s="108" t="s">
@@ -6631,7 +6640,7 @@
       <c r="M36" s="88"/>
     </row>
     <row r="37" spans="1:13">
-      <c r="A37" s="103"/>
+      <c r="A37" s="114"/>
       <c r="B37" s="108" t="s">
         <v>229</v>
       </c>
@@ -6650,7 +6659,7 @@
       <c r="M37" s="88"/>
     </row>
     <row r="38" spans="1:13">
-      <c r="A38" s="103"/>
+      <c r="A38" s="114"/>
       <c r="B38" s="108" t="s">
         <v>231</v>
       </c>
@@ -6669,7 +6678,7 @@
       <c r="M38" s="88"/>
     </row>
     <row r="39" spans="1:13">
-      <c r="A39" s="103"/>
+      <c r="A39" s="114"/>
       <c r="B39" s="108" t="s">
         <v>233</v>
       </c>
@@ -6688,7 +6697,7 @@
       <c r="M39" s="88"/>
     </row>
     <row r="40" spans="1:13">
-      <c r="A40" s="103"/>
+      <c r="A40" s="114"/>
       <c r="B40" s="108" t="s">
         <v>507</v>
       </c>
@@ -6699,7 +6708,7 @@
       <c r="G40" s="67"/>
       <c r="H40" s="67"/>
       <c r="I40" s="61" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="J40" s="67"/>
       <c r="K40" s="67"/>
@@ -6707,7 +6716,7 @@
       <c r="M40" s="88"/>
     </row>
     <row r="41" spans="1:13">
-      <c r="A41" s="103"/>
+      <c r="A41" s="114"/>
       <c r="B41" s="108" t="s">
         <v>508</v>
       </c>
@@ -6718,7 +6727,7 @@
       <c r="G41" s="67"/>
       <c r="H41" s="67"/>
       <c r="I41" s="61" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="J41" s="67"/>
       <c r="K41" s="67"/>
@@ -6726,7 +6735,7 @@
       <c r="M41" s="88"/>
     </row>
     <row r="42" spans="1:13">
-      <c r="A42" s="103"/>
+      <c r="A42" s="114"/>
       <c r="B42" s="108" t="s">
         <v>509</v>
       </c>
@@ -6737,7 +6746,7 @@
       <c r="G42" s="67"/>
       <c r="H42" s="67"/>
       <c r="I42" s="61" t="s">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="J42" s="67"/>
       <c r="K42" s="67"/>
@@ -6745,7 +6754,7 @@
       <c r="M42" s="88"/>
     </row>
     <row r="43" spans="1:13">
-      <c r="A43" s="103"/>
+      <c r="A43" s="114"/>
       <c r="B43" s="108" t="s">
         <v>510</v>
       </c>
@@ -6756,7 +6765,7 @@
       <c r="G43" s="67"/>
       <c r="H43" s="67"/>
       <c r="I43" s="61" t="s">
-        <v>548</v>
+        <v>540</v>
       </c>
       <c r="J43" s="67"/>
       <c r="K43" s="67"/>
@@ -6764,7 +6773,7 @@
       <c r="M43" s="88"/>
     </row>
     <row r="44" spans="1:13">
-      <c r="A44" s="103"/>
+      <c r="A44" s="114"/>
       <c r="B44" s="108" t="s">
         <v>511</v>
       </c>
@@ -6783,7 +6792,7 @@
       <c r="M44" s="88"/>
     </row>
     <row r="45" spans="1:13">
-      <c r="A45" s="103"/>
+      <c r="A45" s="114"/>
       <c r="B45" s="108" t="s">
         <v>512</v>
       </c>
@@ -6794,7 +6803,7 @@
       <c r="G45" s="67"/>
       <c r="H45" s="67"/>
       <c r="I45" s="61" t="s">
-        <v>549</v>
+        <v>541</v>
       </c>
       <c r="J45" s="67"/>
       <c r="K45" s="67"/>
@@ -6802,11 +6811,11 @@
       <c r="M45" s="88"/>
     </row>
     <row r="46" spans="1:13">
-      <c r="A46" s="103"/>
-      <c r="B46" s="106" t="s">
+      <c r="A46" s="114"/>
+      <c r="B46" s="115" t="s">
         <v>236</v>
       </c>
-      <c r="C46" s="106"/>
+      <c r="C46" s="115"/>
       <c r="D46" s="67"/>
       <c r="E46" s="67"/>
       <c r="F46" s="67"/>
@@ -6821,7 +6830,7 @@
       <c r="M46" s="88"/>
     </row>
     <row r="47" spans="1:13">
-      <c r="A47" s="103" t="s">
+      <c r="A47" s="114" t="s">
         <v>238</v>
       </c>
       <c r="B47" s="108" t="s">
@@ -6850,7 +6859,7 @@
       <c r="M47" s="89"/>
     </row>
     <row r="48" spans="1:13">
-      <c r="A48" s="103"/>
+      <c r="A48" s="114"/>
       <c r="B48" s="108" t="s">
         <v>245</v>
       </c>
@@ -6877,7 +6886,7 @@
       <c r="M48" s="89"/>
     </row>
     <row r="49" spans="1:13">
-      <c r="A49" s="103"/>
+      <c r="A49" s="114"/>
       <c r="B49" s="108" t="s">
         <v>251</v>
       </c>
@@ -6904,7 +6913,7 @@
       <c r="M49" s="89"/>
     </row>
     <row r="50" spans="1:13">
-      <c r="A50" s="103"/>
+      <c r="A50" s="114"/>
       <c r="B50" s="108" t="s">
         <v>257</v>
       </c>
@@ -6931,11 +6940,11 @@
       <c r="M50" s="89"/>
     </row>
     <row r="51" spans="1:13">
-      <c r="A51" s="103"/>
-      <c r="B51" s="106" t="s">
+      <c r="A51" s="114"/>
+      <c r="B51" s="115" t="s">
         <v>263</v>
       </c>
-      <c r="C51" s="106"/>
+      <c r="C51" s="115"/>
       <c r="D51" s="63" t="s">
         <v>264</v>
       </c>
@@ -6958,13 +6967,13 @@
       <c r="M51" s="89"/>
     </row>
     <row r="52" spans="1:13">
-      <c r="A52" s="103" t="s">
+      <c r="A52" s="114" t="s">
         <v>269</v>
       </c>
-      <c r="B52" s="106" t="s">
+      <c r="B52" s="115" t="s">
         <v>270</v>
       </c>
-      <c r="C52" s="106"/>
+      <c r="C52" s="115"/>
       <c r="D52" s="61" t="s">
         <v>271</v>
       </c>
@@ -6986,39 +6995,39 @@
       <c r="L52" s="87"/>
       <c r="M52" s="89"/>
     </row>
-    <row r="53" spans="1:13" ht="16.2" thickBot="1">
-      <c r="A53" s="104"/>
-      <c r="B53" s="106" t="s">
+    <row r="53" spans="1:13" ht="15" thickBot="1">
+      <c r="A53" s="120"/>
+      <c r="B53" s="115" t="s">
         <v>513</v>
       </c>
-      <c r="C53" s="106"/>
+      <c r="C53" s="115"/>
       <c r="D53" s="68" t="s">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="E53" s="68" t="s">
-        <v>551</v>
+        <v>543</v>
       </c>
       <c r="F53" s="68" t="s">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="G53" s="68" t="s">
-        <v>553</v>
+        <v>545</v>
       </c>
       <c r="H53" s="101"/>
       <c r="I53" s="68" t="s">
-        <v>554</v>
+        <v>546</v>
       </c>
       <c r="J53" s="101"/>
       <c r="K53" s="101"/>
       <c r="L53" s="101"/>
       <c r="M53" s="102"/>
     </row>
-    <row r="54" spans="1:13" ht="16.2" thickBot="1">
-      <c r="A54" s="104"/>
-      <c r="B54" s="107" t="s">
+    <row r="54" spans="1:13" ht="15" thickBot="1">
+      <c r="A54" s="120"/>
+      <c r="B54" s="122" t="s">
         <v>276</v>
       </c>
-      <c r="C54" s="107"/>
+      <c r="C54" s="122"/>
       <c r="D54" s="68" t="s">
         <v>277</v>
       </c>
@@ -7040,235 +7049,235 @@
       <c r="L54" s="90"/>
       <c r="M54" s="91"/>
     </row>
-    <row r="55" spans="1:13" ht="16.2" thickBot="1">
-      <c r="A55" s="104"/>
-      <c r="B55" s="107" t="s">
+    <row r="55" spans="1:13" ht="15" thickBot="1">
+      <c r="A55" s="120"/>
+      <c r="B55" s="122" t="s">
         <v>514</v>
       </c>
-      <c r="C55" s="107"/>
+      <c r="C55" s="122"/>
       <c r="D55" s="68" t="s">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="E55" s="68" t="s">
-        <v>556</v>
+        <v>548</v>
       </c>
       <c r="F55" s="68" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
       <c r="G55" s="68" t="s">
-        <v>558</v>
+        <v>550</v>
       </c>
       <c r="H55" s="90"/>
       <c r="I55" s="68" t="s">
-        <v>559</v>
+        <v>551</v>
       </c>
       <c r="J55" s="90"/>
       <c r="K55" s="90"/>
       <c r="L55" s="90"/>
       <c r="M55" s="91"/>
     </row>
-    <row r="56" spans="1:13" ht="16.2" thickBot="1">
-      <c r="A56" s="104"/>
-      <c r="B56" s="107" t="s">
+    <row r="56" spans="1:13" ht="15" thickBot="1">
+      <c r="A56" s="120"/>
+      <c r="B56" s="122" t="s">
         <v>515</v>
       </c>
-      <c r="C56" s="107"/>
+      <c r="C56" s="122"/>
       <c r="D56" s="68" t="s">
-        <v>560</v>
+        <v>552</v>
       </c>
       <c r="E56" s="68" t="s">
-        <v>561</v>
+        <v>553</v>
       </c>
       <c r="F56" s="68" t="s">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="G56" s="68" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="H56" s="90"/>
       <c r="I56" s="68" t="s">
-        <v>564</v>
+        <v>556</v>
       </c>
       <c r="J56" s="90"/>
       <c r="K56" s="90"/>
       <c r="L56" s="90"/>
       <c r="M56" s="91"/>
     </row>
-    <row r="57" spans="1:13" ht="16.2" thickBot="1">
-      <c r="A57" s="104"/>
-      <c r="B57" s="107" t="s">
+    <row r="57" spans="1:13" ht="15" thickBot="1">
+      <c r="A57" s="120"/>
+      <c r="B57" s="122" t="s">
         <v>516</v>
       </c>
-      <c r="C57" s="107"/>
+      <c r="C57" s="122"/>
       <c r="D57" s="68" t="s">
-        <v>565</v>
+        <v>557</v>
       </c>
       <c r="E57" s="68" t="s">
-        <v>566</v>
+        <v>558</v>
       </c>
       <c r="F57" s="68" t="s">
-        <v>567</v>
+        <v>559</v>
       </c>
       <c r="G57" s="68" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="H57" s="90"/>
       <c r="I57" s="68" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="J57" s="90"/>
       <c r="K57" s="90"/>
       <c r="L57" s="90"/>
       <c r="M57" s="91"/>
     </row>
-    <row r="58" spans="1:13" ht="16.2" thickBot="1">
-      <c r="A58" s="104"/>
-      <c r="B58" s="107" t="s">
+    <row r="58" spans="1:13" ht="15" thickBot="1">
+      <c r="A58" s="120"/>
+      <c r="B58" s="122" t="s">
         <v>517</v>
       </c>
-      <c r="C58" s="107"/>
+      <c r="C58" s="122"/>
       <c r="D58" s="68" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
       <c r="E58" s="68" t="s">
-        <v>571</v>
+        <v>563</v>
       </c>
       <c r="F58" s="68" t="s">
-        <v>572</v>
+        <v>564</v>
       </c>
       <c r="G58" s="68" t="s">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="H58" s="90"/>
       <c r="I58" s="68" t="s">
-        <v>574</v>
+        <v>566</v>
       </c>
       <c r="J58" s="90"/>
       <c r="K58" s="90"/>
       <c r="L58" s="90"/>
       <c r="M58" s="91"/>
     </row>
-    <row r="59" spans="1:13" ht="16.2" thickBot="1">
-      <c r="A59" s="104"/>
-      <c r="B59" s="107" t="s">
+    <row r="59" spans="1:13" ht="15" thickBot="1">
+      <c r="A59" s="120"/>
+      <c r="B59" s="122" t="s">
         <v>518</v>
       </c>
-      <c r="C59" s="107"/>
+      <c r="C59" s="122"/>
       <c r="D59" s="68" t="s">
-        <v>575</v>
+        <v>567</v>
       </c>
       <c r="E59" s="68" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="F59" s="68" t="s">
-        <v>577</v>
+        <v>569</v>
       </c>
       <c r="G59" s="68" t="s">
-        <v>578</v>
+        <v>570</v>
       </c>
       <c r="H59" s="90"/>
       <c r="I59" s="68" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="J59" s="90"/>
       <c r="K59" s="90"/>
       <c r="L59" s="90"/>
       <c r="M59" s="91"/>
     </row>
-    <row r="60" spans="1:13" ht="16.2" thickBot="1">
-      <c r="A60" s="104"/>
-      <c r="B60" s="107" t="s">
+    <row r="60" spans="1:13" ht="15" thickBot="1">
+      <c r="A60" s="120"/>
+      <c r="B60" s="122" t="s">
         <v>519</v>
       </c>
-      <c r="C60" s="107"/>
+      <c r="C60" s="122"/>
       <c r="D60" s="68" t="s">
-        <v>580</v>
+        <v>572</v>
       </c>
       <c r="E60" s="68" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="F60" s="68" t="s">
-        <v>582</v>
+        <v>574</v>
       </c>
       <c r="G60" s="68" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
       <c r="H60" s="90"/>
       <c r="I60" s="68" t="s">
-        <v>584</v>
+        <v>576</v>
       </c>
       <c r="J60" s="90"/>
       <c r="K60" s="90"/>
       <c r="L60" s="90"/>
       <c r="M60" s="91"/>
     </row>
-    <row r="61" spans="1:13" ht="16.2" thickBot="1">
-      <c r="A61" s="104"/>
-      <c r="B61" s="107" t="s">
+    <row r="61" spans="1:13" ht="15" thickBot="1">
+      <c r="A61" s="120"/>
+      <c r="B61" s="122" t="s">
         <v>520</v>
       </c>
-      <c r="C61" s="107"/>
+      <c r="C61" s="122"/>
       <c r="D61" s="68" t="s">
-        <v>585</v>
+        <v>577</v>
       </c>
       <c r="E61" s="68" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
       <c r="F61" s="68" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
       <c r="G61" s="68" t="s">
-        <v>588</v>
+        <v>580</v>
       </c>
       <c r="H61" s="90"/>
       <c r="I61" s="68" t="s">
-        <v>589</v>
+        <v>581</v>
       </c>
       <c r="J61" s="90"/>
       <c r="K61" s="90"/>
       <c r="L61" s="90"/>
       <c r="M61" s="91"/>
     </row>
-    <row r="62" spans="1:13" ht="16.2" thickBot="1">
-      <c r="A62" s="105"/>
-      <c r="B62" s="107" t="s">
+    <row r="62" spans="1:13" ht="15" thickBot="1">
+      <c r="A62" s="121"/>
+      <c r="B62" s="122" t="s">
         <v>521</v>
       </c>
-      <c r="C62" s="107"/>
+      <c r="C62" s="122"/>
       <c r="D62" s="68" t="s">
-        <v>590</v>
+        <v>582</v>
       </c>
       <c r="E62" s="68" t="s">
-        <v>591</v>
+        <v>583</v>
       </c>
       <c r="F62" s="68" t="s">
-        <v>592</v>
+        <v>584</v>
       </c>
       <c r="G62" s="68" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
       <c r="H62" s="90"/>
       <c r="I62" s="68" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="J62" s="61" t="s">
-        <v>595</v>
+        <v>1129</v>
       </c>
       <c r="K62" s="61" t="s">
-        <v>596</v>
+        <v>587</v>
       </c>
       <c r="L62" s="61" t="s">
-        <v>597</v>
+        <v>588</v>
       </c>
       <c r="M62" s="84" t="s">
-        <v>598</v>
+        <v>589</v>
       </c>
     </row>
     <row r="63" spans="1:13">
-      <c r="A63" s="114" t="s">
+      <c r="A63" s="107" t="s">
         <v>282</v>
       </c>
-      <c r="B63" s="114"/>
+      <c r="B63" s="107"/>
       <c r="C63" s="69"/>
       <c r="D63" s="70"/>
       <c r="E63" s="71" t="s">
@@ -7308,7 +7317,7 @@
       <c r="I65" s="92"/>
       <c r="J65" s="93"/>
     </row>
-    <row r="66" spans="1:10" ht="24">
+    <row r="66" spans="1:10">
       <c r="A66" s="78"/>
       <c r="B66" s="75" t="s">
         <v>287</v>
@@ -7316,6 +7325,43 @@
     </row>
   </sheetData>
   <mergeCells count="53">
+    <mergeCell ref="A52:A62"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="A47:A51"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="A20:A35"/>
+    <mergeCell ref="A36:A46"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B20:B25"/>
+    <mergeCell ref="B26:B34"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A13:A19"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B13:B16"/>
+    <mergeCell ref="B17:B18"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="E2:F2"/>
@@ -7332,43 +7378,6 @@
     <mergeCell ref="A8:A12"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A13:A19"/>
-    <mergeCell ref="A20:A35"/>
-    <mergeCell ref="A36:A46"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B13:B16"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B20:B25"/>
-    <mergeCell ref="B26:B34"/>
-    <mergeCell ref="A47:A51"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="A52:A62"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <dataValidations count="4">
@@ -7396,32 +7405,32 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G184"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="10.3984375" style="4" customWidth="1"/>
-    <col min="2" max="2" width="26.09765625" style="4" customWidth="1"/>
+    <col min="1" max="1" width="10.375" style="4" customWidth="1"/>
+    <col min="2" max="2" width="26.125" style="4" customWidth="1"/>
     <col min="3" max="3" width="40.5" style="4" customWidth="1"/>
     <col min="4" max="6" width="17.5" style="5" customWidth="1"/>
-    <col min="7" max="7" width="16.3984375" style="5" customWidth="1"/>
+    <col min="7" max="7" width="16.375" style="5" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30.9" customHeight="1">
-      <c r="A1" s="158" t="s">
+    <row r="1" spans="1:7" ht="30.95" customHeight="1">
+      <c r="A1" s="123" t="s">
         <v>288</v>
       </c>
-      <c r="B1" s="158"/>
-      <c r="C1" s="158"/>
-      <c r="D1" s="159"/>
-      <c r="E1" s="159"/>
-      <c r="F1" s="159"/>
-      <c r="G1" s="159"/>
+      <c r="B1" s="123"/>
+      <c r="C1" s="123"/>
+      <c r="D1" s="124"/>
+      <c r="E1" s="124"/>
+      <c r="F1" s="124"/>
+      <c r="G1" s="124"/>
     </row>
     <row r="2" spans="1:7" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A2" s="160" t="s">
+      <c r="A2" s="125" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="160"/>
+      <c r="B2" s="125"/>
       <c r="C2" s="6" t="s">
         <v>289</v>
       </c>
@@ -7432,42 +7441,42 @@
         <v>496</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="2" customFormat="1" ht="14.4">
-      <c r="A3" s="152" t="s">
+    <row r="3" spans="1:7" s="2" customFormat="1" ht="13.5">
+      <c r="A3" s="135" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="153"/>
-      <c r="C3" s="153"/>
-      <c r="D3" s="148" t="s">
+      <c r="B3" s="136"/>
+      <c r="C3" s="136"/>
+      <c r="D3" s="131" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="150" t="s">
+      <c r="E3" s="133" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="148" t="s">
+      <c r="F3" s="131" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="150" t="s">
+      <c r="G3" s="133" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="2" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A4" s="154"/>
-      <c r="B4" s="155"/>
-      <c r="C4" s="155"/>
-      <c r="D4" s="149"/>
-      <c r="E4" s="151"/>
-      <c r="F4" s="149"/>
-      <c r="G4" s="151"/>
+    <row r="4" spans="1:7" s="2" customFormat="1" ht="14.45" customHeight="1">
+      <c r="A4" s="137"/>
+      <c r="B4" s="138"/>
+      <c r="C4" s="138"/>
+      <c r="D4" s="132"/>
+      <c r="E4" s="134"/>
+      <c r="F4" s="132"/>
+      <c r="G4" s="134"/>
     </row>
     <row r="5" spans="1:7" s="2" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A5" s="136" t="s">
+      <c r="A5" s="139" t="s">
         <v>290</v>
       </c>
-      <c r="B5" s="125" t="s">
+      <c r="B5" s="142" t="s">
         <v>291</v>
       </c>
-      <c r="C5" s="139"/>
+      <c r="C5" s="143"/>
       <c r="D5" s="9" t="s">
         <v>292</v>
       </c>
@@ -7475,14 +7484,14 @@
         <v>293</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>599</v>
+        <v>590</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>600</v>
+        <v>591</v>
       </c>
     </row>
     <row r="6" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A6" s="137"/>
+      <c r="A6" s="140"/>
       <c r="B6" s="127" t="s">
         <v>294</v>
       </c>
@@ -7496,14 +7505,14 @@
         <v>297</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>753</v>
+        <v>744</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>754</v>
+        <v>745</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A7" s="137"/>
+      <c r="A7" s="140"/>
       <c r="B7" s="127"/>
       <c r="C7" s="97" t="s">
         <v>298</v>
@@ -7515,14 +7524,14 @@
         <v>300</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>755</v>
+        <v>746</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>756</v>
+        <v>747</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A8" s="137"/>
+      <c r="A8" s="140"/>
       <c r="B8" s="127"/>
       <c r="C8" s="97" t="s">
         <v>301</v>
@@ -7534,14 +7543,14 @@
         <v>303</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>757</v>
+        <v>748</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>758</v>
+        <v>749</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A9" s="137"/>
+      <c r="A9" s="140"/>
       <c r="B9" s="127"/>
       <c r="C9" s="97" t="s">
         <v>304</v>
@@ -7553,14 +7562,14 @@
         <v>306</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>759</v>
+        <v>750</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>760</v>
+        <v>751</v>
       </c>
     </row>
     <row r="10" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A10" s="137"/>
+      <c r="A10" s="140"/>
       <c r="B10" s="127"/>
       <c r="C10" s="97" t="s">
         <v>307</v>
@@ -7572,14 +7581,14 @@
         <v>309</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>761</v>
+        <v>752</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>762</v>
+        <v>753</v>
       </c>
     </row>
     <row r="11" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A11" s="137"/>
+      <c r="A11" s="140"/>
       <c r="B11" s="127"/>
       <c r="C11" s="96" t="s">
         <v>310</v>
@@ -7591,14 +7600,14 @@
         <v>312</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>763</v>
+        <v>754</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>764</v>
+        <v>755</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A12" s="137"/>
+      <c r="A12" s="140"/>
       <c r="B12" s="127" t="s">
         <v>313</v>
       </c>
@@ -7612,14 +7621,14 @@
         <v>316</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>766</v>
+        <v>757</v>
       </c>
     </row>
     <row r="13" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A13" s="137"/>
+      <c r="A13" s="140"/>
       <c r="B13" s="127"/>
       <c r="C13" s="97" t="s">
         <v>317</v>
@@ -7631,14 +7640,14 @@
         <v>319</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>767</v>
+        <v>758</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>768</v>
+        <v>759</v>
       </c>
     </row>
     <row r="14" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A14" s="137"/>
+      <c r="A14" s="140"/>
       <c r="B14" s="127"/>
       <c r="C14" s="96" t="s">
         <v>320</v>
@@ -7650,16 +7659,16 @@
         <v>322</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>769</v>
+        <v>760</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>770</v>
+        <v>761</v>
       </c>
     </row>
     <row r="15" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A15" s="137"/>
+      <c r="A15" s="140"/>
       <c r="B15" s="127" t="s">
-        <v>601</v>
+        <v>592</v>
       </c>
       <c r="C15" s="97" t="s">
         <v>323</v>
@@ -7671,17 +7680,17 @@
         <v>325</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>771</v>
+        <v>762</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>772</v>
+        <v>763</v>
       </c>
     </row>
     <row r="16" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A16" s="137"/>
+      <c r="A16" s="140"/>
       <c r="B16" s="127"/>
       <c r="C16" s="97" t="s">
-        <v>602</v>
+        <v>593</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>326</v>
@@ -7690,14 +7699,14 @@
         <v>327</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>773</v>
+        <v>764</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>774</v>
+        <v>765</v>
       </c>
     </row>
     <row r="17" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A17" s="137"/>
+      <c r="A17" s="140"/>
       <c r="B17" s="127"/>
       <c r="C17" s="96" t="s">
         <v>328</v>
@@ -7709,15 +7718,15 @@
         <v>330</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>775</v>
+        <v>766</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>776</v>
+        <v>767</v>
       </c>
     </row>
     <row r="18" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A18" s="137"/>
-      <c r="B18" s="140" t="s">
+      <c r="A18" s="140"/>
+      <c r="B18" s="144" t="s">
         <v>331</v>
       </c>
       <c r="C18" s="97" t="s">
@@ -7730,15 +7739,15 @@
         <v>334</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>777</v>
+        <v>768</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>778</v>
+        <v>769</v>
       </c>
     </row>
     <row r="19" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A19" s="137"/>
-      <c r="B19" s="140"/>
+      <c r="A19" s="140"/>
+      <c r="B19" s="144"/>
       <c r="C19" s="97" t="s">
         <v>335</v>
       </c>
@@ -7749,34 +7758,34 @@
         <v>337</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>779</v>
+        <v>770</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>780</v>
+        <v>771</v>
       </c>
     </row>
     <row r="20" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A20" s="137"/>
-      <c r="B20" s="140"/>
+      <c r="A20" s="140"/>
+      <c r="B20" s="144"/>
       <c r="C20" s="97" t="s">
-        <v>603</v>
+        <v>594</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>781</v>
+        <v>772</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>782</v>
+        <v>773</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>783</v>
+        <v>774</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>784</v>
+        <v>775</v>
       </c>
     </row>
     <row r="21" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A21" s="137"/>
-      <c r="B21" s="140"/>
+      <c r="A21" s="140"/>
+      <c r="B21" s="144"/>
       <c r="C21" s="97" t="s">
         <v>338</v>
       </c>
@@ -7787,15 +7796,15 @@
         <v>340</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>785</v>
+        <v>776</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>786</v>
+        <v>777</v>
       </c>
     </row>
     <row r="22" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A22" s="137"/>
-      <c r="B22" s="140"/>
+      <c r="A22" s="140"/>
+      <c r="B22" s="144"/>
       <c r="C22" s="97" t="s">
         <v>341</v>
       </c>
@@ -7806,15 +7815,15 @@
         <v>343</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>787</v>
+        <v>778</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>788</v>
+        <v>779</v>
       </c>
     </row>
     <row r="23" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A23" s="137"/>
-      <c r="B23" s="140"/>
+      <c r="A23" s="140"/>
+      <c r="B23" s="144"/>
       <c r="C23" s="97" t="s">
         <v>344</v>
       </c>
@@ -7825,15 +7834,15 @@
         <v>346</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>789</v>
+        <v>780</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>790</v>
+        <v>781</v>
       </c>
     </row>
     <row r="24" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A24" s="137"/>
-      <c r="B24" s="140"/>
+      <c r="A24" s="140"/>
+      <c r="B24" s="144"/>
       <c r="C24" s="97" t="s">
         <v>347</v>
       </c>
@@ -7844,15 +7853,15 @@
         <v>349</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>791</v>
+        <v>782</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>792</v>
+        <v>783</v>
       </c>
     </row>
     <row r="25" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A25" s="137"/>
-      <c r="B25" s="140"/>
+      <c r="A25" s="140"/>
+      <c r="B25" s="144"/>
       <c r="C25" s="97" t="s">
         <v>350</v>
       </c>
@@ -7863,15 +7872,15 @@
         <v>352</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>793</v>
+        <v>784</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>794</v>
+        <v>785</v>
       </c>
     </row>
     <row r="26" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A26" s="137"/>
-      <c r="B26" s="140"/>
+      <c r="A26" s="140"/>
+      <c r="B26" s="144"/>
       <c r="C26" s="97" t="s">
         <v>353</v>
       </c>
@@ -7882,15 +7891,15 @@
         <v>355</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>795</v>
+        <v>786</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>796</v>
+        <v>787</v>
       </c>
     </row>
     <row r="27" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A27" s="137"/>
-      <c r="B27" s="140"/>
+      <c r="A27" s="140"/>
+      <c r="B27" s="144"/>
       <c r="C27" s="97" t="s">
         <v>356</v>
       </c>
@@ -7901,15 +7910,15 @@
         <v>358</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>797</v>
+        <v>788</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>798</v>
+        <v>789</v>
       </c>
     </row>
     <row r="28" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A28" s="137"/>
-      <c r="B28" s="140"/>
+      <c r="A28" s="140"/>
+      <c r="B28" s="144"/>
       <c r="C28" s="97" t="s">
         <v>359</v>
       </c>
@@ -7920,15 +7929,15 @@
         <v>361</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>799</v>
+        <v>790</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>800</v>
+        <v>791</v>
       </c>
     </row>
     <row r="29" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A29" s="137"/>
-      <c r="B29" s="140"/>
+      <c r="A29" s="140"/>
+      <c r="B29" s="144"/>
       <c r="C29" s="97" t="s">
         <v>362</v>
       </c>
@@ -7939,36 +7948,36 @@
         <v>364</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>801</v>
+        <v>792</v>
       </c>
       <c r="G29" s="12" t="s">
-        <v>802</v>
+        <v>793</v>
       </c>
     </row>
     <row r="30" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A30" s="137"/>
-      <c r="B30" s="140"/>
+      <c r="A30" s="140"/>
+      <c r="B30" s="144"/>
       <c r="C30" s="97" t="s">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>803</v>
+        <v>794</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>804</v>
+        <v>795</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>805</v>
+        <v>796</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>806</v>
+        <v>797</v>
       </c>
     </row>
     <row r="31" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A31" s="137"/>
-      <c r="B31" s="140"/>
+      <c r="A31" s="140"/>
+      <c r="B31" s="144"/>
       <c r="C31" s="17" t="s">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="D31" s="18"/>
       <c r="E31" s="19"/>
@@ -7976,27 +7985,27 @@
       <c r="G31" s="19"/>
     </row>
     <row r="32" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A32" s="137"/>
-      <c r="B32" s="140"/>
+      <c r="A32" s="140"/>
+      <c r="B32" s="144"/>
       <c r="C32" s="96" t="s">
-        <v>606</v>
+        <v>597</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>807</v>
+        <v>798</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>808</v>
+        <v>799</v>
       </c>
       <c r="F32" s="15" t="s">
-        <v>809</v>
+        <v>800</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>810</v>
+        <v>801</v>
       </c>
     </row>
     <row r="33" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A33" s="137"/>
-      <c r="B33" s="140"/>
+      <c r="A33" s="140"/>
+      <c r="B33" s="144"/>
       <c r="C33" s="97" t="s">
         <v>365</v>
       </c>
@@ -8007,15 +8016,15 @@
         <v>367</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>811</v>
+        <v>802</v>
       </c>
       <c r="G33" s="12" t="s">
-        <v>812</v>
+        <v>803</v>
       </c>
     </row>
     <row r="34" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A34" s="137"/>
-      <c r="B34" s="140"/>
+      <c r="A34" s="140"/>
+      <c r="B34" s="144"/>
       <c r="C34" s="97" t="s">
         <v>368</v>
       </c>
@@ -8026,15 +8035,15 @@
         <v>370</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="G34" s="12" t="s">
-        <v>814</v>
+        <v>805</v>
       </c>
     </row>
     <row r="35" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A35" s="137"/>
-      <c r="B35" s="140"/>
+      <c r="A35" s="140"/>
+      <c r="B35" s="144"/>
       <c r="C35" s="97" t="s">
         <v>371</v>
       </c>
@@ -8045,19 +8054,19 @@
         <v>373</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>815</v>
+        <v>806</v>
       </c>
       <c r="G35" s="12" t="s">
-        <v>816</v>
+        <v>807</v>
       </c>
     </row>
     <row r="36" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A36" s="137"/>
-      <c r="B36" s="141" t="s">
-        <v>607</v>
+      <c r="A36" s="140"/>
+      <c r="B36" s="145" t="s">
+        <v>598</v>
       </c>
       <c r="C36" s="97" t="s">
-        <v>608</v>
+        <v>599</v>
       </c>
       <c r="D36" s="11" t="s">
         <v>374</v>
@@ -8066,55 +8075,55 @@
         <v>375</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>817</v>
+        <v>808</v>
       </c>
       <c r="G36" s="12" t="s">
-        <v>818</v>
+        <v>809</v>
       </c>
     </row>
     <row r="37" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A37" s="137"/>
-      <c r="B37" s="141"/>
+      <c r="A37" s="140"/>
+      <c r="B37" s="145"/>
       <c r="C37" s="97" t="s">
-        <v>609</v>
+        <v>600</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>819</v>
+        <v>810</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>819</v>
+        <v>810</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>820</v>
+        <v>811</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>819</v>
+        <v>810</v>
       </c>
     </row>
     <row r="38" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A38" s="137"/>
-      <c r="B38" s="141"/>
+      <c r="A38" s="140"/>
+      <c r="B38" s="145"/>
       <c r="C38" s="97" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>821</v>
+        <v>812</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>822</v>
+        <v>813</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>823</v>
+        <v>814</v>
       </c>
       <c r="G38" s="12" t="s">
-        <v>824</v>
+        <v>815</v>
       </c>
     </row>
     <row r="39" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A39" s="137"/>
-      <c r="B39" s="141"/>
+      <c r="A39" s="140"/>
+      <c r="B39" s="145"/>
       <c r="C39" s="97" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
       <c r="D39" s="11" t="s">
         <v>376</v>
@@ -8123,302 +8132,302 @@
         <v>377</v>
       </c>
       <c r="F39" s="11" t="s">
+        <v>816</v>
+      </c>
+      <c r="G39" s="12" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A40" s="140"/>
+      <c r="B40" s="145"/>
+      <c r="C40" s="97" t="s">
+        <v>603</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>818</v>
+      </c>
+      <c r="E40" s="12" t="s">
+        <v>819</v>
+      </c>
+      <c r="F40" s="11" t="s">
+        <v>820</v>
+      </c>
+      <c r="G40" s="12" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A41" s="140"/>
+      <c r="B41" s="145"/>
+      <c r="C41" s="97" t="s">
+        <v>604</v>
+      </c>
+      <c r="D41" s="11" t="s">
+        <v>822</v>
+      </c>
+      <c r="E41" s="12" t="s">
+        <v>823</v>
+      </c>
+      <c r="F41" s="11" t="s">
+        <v>824</v>
+      </c>
+      <c r="G41" s="12" t="s">
         <v>825</v>
       </c>
-      <c r="G39" s="12" t="s">
+    </row>
+    <row r="42" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A42" s="140"/>
+      <c r="B42" s="145"/>
+      <c r="C42" s="97" t="s">
+        <v>605</v>
+      </c>
+      <c r="D42" s="11" t="s">
         <v>826</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A40" s="137"/>
-      <c r="B40" s="141"/>
-      <c r="C40" s="97" t="s">
+      <c r="E42" s="12" t="s">
+        <v>827</v>
+      </c>
+      <c r="F42" s="11" t="s">
+        <v>828</v>
+      </c>
+      <c r="G42" s="12" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A43" s="140"/>
+      <c r="B43" s="145"/>
+      <c r="C43" s="97" t="s">
+        <v>606</v>
+      </c>
+      <c r="D43" s="11" t="s">
+        <v>830</v>
+      </c>
+      <c r="E43" s="12" t="s">
+        <v>831</v>
+      </c>
+      <c r="F43" s="11" t="s">
+        <v>832</v>
+      </c>
+      <c r="G43" s="12" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A44" s="140"/>
+      <c r="B44" s="145"/>
+      <c r="C44" s="97" t="s">
+        <v>607</v>
+      </c>
+      <c r="D44" s="11" t="s">
+        <v>834</v>
+      </c>
+      <c r="E44" s="12" t="s">
+        <v>835</v>
+      </c>
+      <c r="F44" s="11" t="s">
+        <v>836</v>
+      </c>
+      <c r="G44" s="12" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A45" s="140"/>
+      <c r="B45" s="145"/>
+      <c r="C45" s="97" t="s">
+        <v>608</v>
+      </c>
+      <c r="D45" s="11" t="s">
+        <v>838</v>
+      </c>
+      <c r="E45" s="12" t="s">
+        <v>839</v>
+      </c>
+      <c r="F45" s="11" t="s">
+        <v>840</v>
+      </c>
+      <c r="G45" s="12" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A46" s="140"/>
+      <c r="B46" s="145"/>
+      <c r="C46" s="97" t="s">
+        <v>609</v>
+      </c>
+      <c r="D46" s="11" t="s">
+        <v>842</v>
+      </c>
+      <c r="E46" s="12" t="s">
+        <v>843</v>
+      </c>
+      <c r="F46" s="11" t="s">
+        <v>844</v>
+      </c>
+      <c r="G46" s="12" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A47" s="140"/>
+      <c r="B47" s="145"/>
+      <c r="C47" s="97" t="s">
+        <v>610</v>
+      </c>
+      <c r="D47" s="11" t="s">
+        <v>846</v>
+      </c>
+      <c r="E47" s="12" t="s">
+        <v>847</v>
+      </c>
+      <c r="F47" s="11" t="s">
+        <v>848</v>
+      </c>
+      <c r="G47" s="12" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A48" s="140"/>
+      <c r="B48" s="145"/>
+      <c r="C48" s="97" t="s">
+        <v>611</v>
+      </c>
+      <c r="D48" s="11" t="s">
+        <v>850</v>
+      </c>
+      <c r="E48" s="12" t="s">
+        <v>851</v>
+      </c>
+      <c r="F48" s="11" t="s">
+        <v>852</v>
+      </c>
+      <c r="G48" s="12" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A49" s="140"/>
+      <c r="B49" s="145"/>
+      <c r="C49" s="97" t="s">
         <v>612</v>
       </c>
-      <c r="D40" s="11" t="s">
-        <v>827</v>
-      </c>
-      <c r="E40" s="12" t="s">
-        <v>828</v>
-      </c>
-      <c r="F40" s="11" t="s">
-        <v>829</v>
-      </c>
-      <c r="G40" s="12" t="s">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A41" s="137"/>
-      <c r="B41" s="141"/>
-      <c r="C41" s="97" t="s">
+      <c r="D49" s="11" t="s">
+        <v>854</v>
+      </c>
+      <c r="E49" s="12" t="s">
+        <v>855</v>
+      </c>
+      <c r="F49" s="11" t="s">
+        <v>856</v>
+      </c>
+      <c r="G49" s="12" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A50" s="140"/>
+      <c r="B50" s="145"/>
+      <c r="C50" s="97" t="s">
         <v>613</v>
       </c>
-      <c r="D41" s="11" t="s">
-        <v>831</v>
-      </c>
-      <c r="E41" s="12" t="s">
-        <v>832</v>
-      </c>
-      <c r="F41" s="11" t="s">
-        <v>833</v>
-      </c>
-      <c r="G41" s="12" t="s">
-        <v>834</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A42" s="137"/>
-      <c r="B42" s="141"/>
-      <c r="C42" s="97" t="s">
+      <c r="D50" s="11" t="s">
+        <v>858</v>
+      </c>
+      <c r="E50" s="12" t="s">
+        <v>859</v>
+      </c>
+      <c r="F50" s="11" t="s">
+        <v>860</v>
+      </c>
+      <c r="G50" s="12" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A51" s="140"/>
+      <c r="B51" s="145"/>
+      <c r="C51" s="97" t="s">
         <v>614</v>
       </c>
-      <c r="D42" s="11" t="s">
-        <v>835</v>
-      </c>
-      <c r="E42" s="12" t="s">
-        <v>836</v>
-      </c>
-      <c r="F42" s="11" t="s">
-        <v>837</v>
-      </c>
-      <c r="G42" s="12" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A43" s="137"/>
-      <c r="B43" s="141"/>
-      <c r="C43" s="97" t="s">
+      <c r="D51" s="11" t="s">
+        <v>862</v>
+      </c>
+      <c r="E51" s="12" t="s">
+        <v>863</v>
+      </c>
+      <c r="F51" s="11" t="s">
+        <v>864</v>
+      </c>
+      <c r="G51" s="12" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A52" s="140"/>
+      <c r="B52" s="145"/>
+      <c r="C52" s="97" t="s">
         <v>615</v>
       </c>
-      <c r="D43" s="11" t="s">
-        <v>839</v>
-      </c>
-      <c r="E43" s="12" t="s">
-        <v>840</v>
-      </c>
-      <c r="F43" s="11" t="s">
-        <v>841</v>
-      </c>
-      <c r="G43" s="12" t="s">
-        <v>842</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A44" s="137"/>
-      <c r="B44" s="141"/>
-      <c r="C44" s="97" t="s">
+      <c r="D52" s="11" t="s">
+        <v>866</v>
+      </c>
+      <c r="E52" s="12" t="s">
+        <v>867</v>
+      </c>
+      <c r="F52" s="11" t="s">
+        <v>868</v>
+      </c>
+      <c r="G52" s="12" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A53" s="140"/>
+      <c r="B53" s="145"/>
+      <c r="C53" s="97" t="s">
         <v>616</v>
       </c>
-      <c r="D44" s="11" t="s">
-        <v>843</v>
-      </c>
-      <c r="E44" s="12" t="s">
-        <v>844</v>
-      </c>
-      <c r="F44" s="11" t="s">
-        <v>845</v>
-      </c>
-      <c r="G44" s="12" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A45" s="137"/>
-      <c r="B45" s="141"/>
-      <c r="C45" s="97" t="s">
+      <c r="D53" s="11" t="s">
+        <v>870</v>
+      </c>
+      <c r="E53" s="12" t="s">
+        <v>871</v>
+      </c>
+      <c r="F53" s="11" t="s">
+        <v>872</v>
+      </c>
+      <c r="G53" s="12" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A54" s="140"/>
+      <c r="B54" s="145"/>
+      <c r="C54" s="97" t="s">
         <v>617</v>
-      </c>
-      <c r="D45" s="11" t="s">
-        <v>847</v>
-      </c>
-      <c r="E45" s="12" t="s">
-        <v>848</v>
-      </c>
-      <c r="F45" s="11" t="s">
-        <v>849</v>
-      </c>
-      <c r="G45" s="12" t="s">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A46" s="137"/>
-      <c r="B46" s="141"/>
-      <c r="C46" s="97" t="s">
-        <v>618</v>
-      </c>
-      <c r="D46" s="11" t="s">
-        <v>851</v>
-      </c>
-      <c r="E46" s="12" t="s">
-        <v>852</v>
-      </c>
-      <c r="F46" s="11" t="s">
-        <v>853</v>
-      </c>
-      <c r="G46" s="12" t="s">
-        <v>854</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A47" s="137"/>
-      <c r="B47" s="141"/>
-      <c r="C47" s="97" t="s">
-        <v>619</v>
-      </c>
-      <c r="D47" s="11" t="s">
-        <v>855</v>
-      </c>
-      <c r="E47" s="12" t="s">
-        <v>856</v>
-      </c>
-      <c r="F47" s="11" t="s">
-        <v>857</v>
-      </c>
-      <c r="G47" s="12" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A48" s="137"/>
-      <c r="B48" s="141"/>
-      <c r="C48" s="97" t="s">
-        <v>620</v>
-      </c>
-      <c r="D48" s="11" t="s">
-        <v>859</v>
-      </c>
-      <c r="E48" s="12" t="s">
-        <v>860</v>
-      </c>
-      <c r="F48" s="11" t="s">
-        <v>861</v>
-      </c>
-      <c r="G48" s="12" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A49" s="137"/>
-      <c r="B49" s="141"/>
-      <c r="C49" s="97" t="s">
-        <v>621</v>
-      </c>
-      <c r="D49" s="11" t="s">
-        <v>863</v>
-      </c>
-      <c r="E49" s="12" t="s">
-        <v>864</v>
-      </c>
-      <c r="F49" s="11" t="s">
-        <v>865</v>
-      </c>
-      <c r="G49" s="12" t="s">
-        <v>866</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A50" s="137"/>
-      <c r="B50" s="141"/>
-      <c r="C50" s="97" t="s">
-        <v>622</v>
-      </c>
-      <c r="D50" s="11" t="s">
-        <v>867</v>
-      </c>
-      <c r="E50" s="12" t="s">
-        <v>868</v>
-      </c>
-      <c r="F50" s="11" t="s">
-        <v>869</v>
-      </c>
-      <c r="G50" s="12" t="s">
-        <v>870</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A51" s="137"/>
-      <c r="B51" s="141"/>
-      <c r="C51" s="97" t="s">
-        <v>623</v>
-      </c>
-      <c r="D51" s="11" t="s">
-        <v>871</v>
-      </c>
-      <c r="E51" s="12" t="s">
-        <v>872</v>
-      </c>
-      <c r="F51" s="11" t="s">
-        <v>873</v>
-      </c>
-      <c r="G51" s="12" t="s">
-        <v>874</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A52" s="137"/>
-      <c r="B52" s="141"/>
-      <c r="C52" s="97" t="s">
-        <v>624</v>
-      </c>
-      <c r="D52" s="11" t="s">
-        <v>875</v>
-      </c>
-      <c r="E52" s="12" t="s">
-        <v>876</v>
-      </c>
-      <c r="F52" s="11" t="s">
-        <v>877</v>
-      </c>
-      <c r="G52" s="12" t="s">
-        <v>878</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A53" s="137"/>
-      <c r="B53" s="141"/>
-      <c r="C53" s="97" t="s">
-        <v>625</v>
-      </c>
-      <c r="D53" s="11" t="s">
-        <v>879</v>
-      </c>
-      <c r="E53" s="12" t="s">
-        <v>880</v>
-      </c>
-      <c r="F53" s="11" t="s">
-        <v>881</v>
-      </c>
-      <c r="G53" s="12" t="s">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A54" s="137"/>
-      <c r="B54" s="141"/>
-      <c r="C54" s="97" t="s">
-        <v>626</v>
       </c>
       <c r="D54" s="11" t="s">
         <v>402</v>
       </c>
       <c r="E54" s="12" t="s">
-        <v>883</v>
+        <v>874</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>884</v>
+        <v>875</v>
       </c>
       <c r="G54" s="12" t="s">
-        <v>885</v>
+        <v>876</v>
       </c>
     </row>
     <row r="55" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A55" s="137"/>
-      <c r="B55" s="141"/>
+      <c r="A55" s="140"/>
+      <c r="B55" s="145"/>
       <c r="C55" s="20" t="s">
-        <v>627</v>
+        <v>618</v>
       </c>
       <c r="D55" s="15" t="s">
         <v>403</v>
@@ -8427,34 +8436,34 @@
         <v>404</v>
       </c>
       <c r="F55" s="15" t="s">
-        <v>886</v>
+        <v>877</v>
       </c>
       <c r="G55" s="16" t="s">
-        <v>887</v>
+        <v>878</v>
       </c>
     </row>
     <row r="56" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A56" s="137"/>
-      <c r="B56" s="142"/>
+      <c r="A56" s="140"/>
+      <c r="B56" s="146"/>
       <c r="C56" s="21" t="s">
-        <v>628</v>
+        <v>619</v>
       </c>
       <c r="D56" s="18"/>
       <c r="E56" s="12" t="s">
-        <v>888</v>
+        <v>879</v>
       </c>
       <c r="F56" s="18"/>
       <c r="G56" s="12" t="s">
-        <v>889</v>
+        <v>880</v>
       </c>
     </row>
     <row r="57" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A57" s="137"/>
+      <c r="A57" s="140"/>
       <c r="B57" s="127" t="s">
-        <v>629</v>
+        <v>620</v>
       </c>
       <c r="C57" s="97" t="s">
-        <v>630</v>
+        <v>621</v>
       </c>
       <c r="D57" s="11" t="s">
         <v>378</v>
@@ -8463,17 +8472,17 @@
         <v>379</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>890</v>
+        <v>881</v>
       </c>
       <c r="G57" s="12" t="s">
-        <v>891</v>
+        <v>882</v>
       </c>
     </row>
     <row r="58" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A58" s="137"/>
+      <c r="A58" s="140"/>
       <c r="B58" s="127"/>
       <c r="C58" s="21" t="s">
-        <v>631</v>
+        <v>622</v>
       </c>
       <c r="D58" s="11" t="s">
         <v>380</v>
@@ -8482,17 +8491,17 @@
         <v>381</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>892</v>
+        <v>883</v>
       </c>
       <c r="G58" s="12" t="s">
-        <v>893</v>
+        <v>884</v>
       </c>
     </row>
     <row r="59" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A59" s="137"/>
+      <c r="A59" s="140"/>
       <c r="B59" s="127"/>
       <c r="C59" s="97" t="s">
-        <v>632</v>
+        <v>623</v>
       </c>
       <c r="D59" s="11" t="s">
         <v>382</v>
@@ -8501,17 +8510,17 @@
         <v>383</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="G59" s="12" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
     </row>
     <row r="60" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A60" s="137"/>
+      <c r="A60" s="140"/>
       <c r="B60" s="127"/>
       <c r="C60" s="97" t="s">
-        <v>633</v>
+        <v>624</v>
       </c>
       <c r="D60" s="11" t="s">
         <v>384</v>
@@ -8520,38 +8529,38 @@
         <v>385</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>896</v>
+        <v>887</v>
       </c>
       <c r="G60" s="12" t="s">
-        <v>897</v>
+        <v>888</v>
       </c>
     </row>
     <row r="61" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A61" s="137"/>
+      <c r="A61" s="140"/>
       <c r="B61" s="127"/>
       <c r="C61" s="96" t="s">
-        <v>634</v>
+        <v>625</v>
       </c>
       <c r="D61" s="15" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="E61" s="16" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="F61" s="15" t="s">
-        <v>900</v>
+        <v>891</v>
       </c>
       <c r="G61" s="16" t="s">
-        <v>901</v>
+        <v>892</v>
       </c>
     </row>
     <row r="62" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A62" s="137"/>
+      <c r="A62" s="140"/>
       <c r="B62" s="127" t="s">
-        <v>635</v>
+        <v>626</v>
       </c>
       <c r="C62" s="97" t="s">
-        <v>636</v>
+        <v>627</v>
       </c>
       <c r="D62" s="11" t="s">
         <v>386</v>
@@ -8560,17 +8569,17 @@
         <v>387</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>902</v>
+        <v>893</v>
       </c>
       <c r="G62" s="12" t="s">
-        <v>903</v>
+        <v>894</v>
       </c>
     </row>
     <row r="63" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A63" s="137"/>
+      <c r="A63" s="140"/>
       <c r="B63" s="127"/>
       <c r="C63" s="97" t="s">
-        <v>637</v>
+        <v>628</v>
       </c>
       <c r="D63" s="11" t="s">
         <v>388</v>
@@ -8579,17 +8588,17 @@
         <v>389</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>904</v>
+        <v>895</v>
       </c>
       <c r="G63" s="12" t="s">
-        <v>905</v>
+        <v>896</v>
       </c>
     </row>
     <row r="64" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A64" s="137"/>
+      <c r="A64" s="140"/>
       <c r="B64" s="127"/>
       <c r="C64" s="97" t="s">
-        <v>638</v>
+        <v>629</v>
       </c>
       <c r="D64" s="11" t="s">
         <v>390</v>
@@ -8598,17 +8607,17 @@
         <v>391</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>906</v>
+        <v>897</v>
       </c>
       <c r="G64" s="12" t="s">
-        <v>907</v>
+        <v>898</v>
       </c>
     </row>
     <row r="65" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A65" s="137"/>
+      <c r="A65" s="140"/>
       <c r="B65" s="127"/>
       <c r="C65" s="97" t="s">
-        <v>639</v>
+        <v>630</v>
       </c>
       <c r="D65" s="11" t="s">
         <v>392</v>
@@ -8617,17 +8626,17 @@
         <v>393</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>908</v>
+        <v>899</v>
       </c>
       <c r="G65" s="12" t="s">
-        <v>909</v>
+        <v>900</v>
       </c>
     </row>
     <row r="66" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A66" s="137"/>
+      <c r="A66" s="140"/>
       <c r="B66" s="127"/>
       <c r="C66" s="97" t="s">
-        <v>640</v>
+        <v>631</v>
       </c>
       <c r="D66" s="11" t="s">
         <v>394</v>
@@ -8636,17 +8645,17 @@
         <v>395</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>910</v>
+        <v>901</v>
       </c>
       <c r="G66" s="12" t="s">
-        <v>911</v>
+        <v>902</v>
       </c>
     </row>
     <row r="67" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A67" s="137"/>
+      <c r="A67" s="140"/>
       <c r="B67" s="127"/>
       <c r="C67" s="97" t="s">
-        <v>641</v>
+        <v>632</v>
       </c>
       <c r="D67" s="11" t="s">
         <v>396</v>
@@ -8655,17 +8664,17 @@
         <v>397</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>912</v>
+        <v>903</v>
       </c>
       <c r="G67" s="12" t="s">
-        <v>913</v>
+        <v>904</v>
       </c>
     </row>
     <row r="68" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A68" s="137"/>
+      <c r="A68" s="140"/>
       <c r="B68" s="127"/>
       <c r="C68" s="97" t="s">
-        <v>642</v>
+        <v>633</v>
       </c>
       <c r="D68" s="11" t="s">
         <v>398</v>
@@ -8674,17 +8683,17 @@
         <v>399</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>914</v>
+        <v>905</v>
       </c>
       <c r="G68" s="12" t="s">
-        <v>915</v>
+        <v>906</v>
       </c>
     </row>
     <row r="69" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A69" s="137"/>
+      <c r="A69" s="140"/>
       <c r="B69" s="127"/>
       <c r="C69" s="96" t="s">
-        <v>643</v>
+        <v>634</v>
       </c>
       <c r="D69" s="15" t="s">
         <v>400</v>
@@ -8693,19 +8702,19 @@
         <v>401</v>
       </c>
       <c r="F69" s="15" t="s">
-        <v>916</v>
+        <v>907</v>
       </c>
       <c r="G69" s="16" t="s">
-        <v>917</v>
+        <v>908</v>
       </c>
     </row>
     <row r="70" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A70" s="137"/>
-      <c r="B70" s="140" t="s">
-        <v>644</v>
+      <c r="A70" s="140"/>
+      <c r="B70" s="144" t="s">
+        <v>635</v>
       </c>
       <c r="C70" s="97" t="s">
-        <v>645</v>
+        <v>636</v>
       </c>
       <c r="D70" s="11" t="s">
         <v>405</v>
@@ -8714,17 +8723,17 @@
         <v>406</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>918</v>
+        <v>909</v>
       </c>
       <c r="G70" s="12" t="s">
-        <v>919</v>
+        <v>910</v>
       </c>
     </row>
     <row r="71" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A71" s="137"/>
-      <c r="B71" s="140"/>
+      <c r="A71" s="140"/>
+      <c r="B71" s="144"/>
       <c r="C71" s="97" t="s">
-        <v>646</v>
+        <v>637</v>
       </c>
       <c r="D71" s="11" t="s">
         <v>407</v>
@@ -8733,17 +8742,17 @@
         <v>408</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>920</v>
+        <v>911</v>
       </c>
       <c r="G71" s="12" t="s">
-        <v>921</v>
+        <v>912</v>
       </c>
     </row>
     <row r="72" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A72" s="137"/>
-      <c r="B72" s="140"/>
+      <c r="A72" s="140"/>
+      <c r="B72" s="144"/>
       <c r="C72" s="97" t="s">
-        <v>647</v>
+        <v>638</v>
       </c>
       <c r="D72" s="11" t="s">
         <v>409</v>
@@ -8752,17 +8761,17 @@
         <v>410</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>922</v>
+        <v>913</v>
       </c>
       <c r="G72" s="12" t="s">
-        <v>923</v>
+        <v>914</v>
       </c>
     </row>
     <row r="73" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A73" s="137"/>
-      <c r="B73" s="140"/>
+      <c r="A73" s="140"/>
+      <c r="B73" s="144"/>
       <c r="C73" s="97" t="s">
-        <v>648</v>
+        <v>639</v>
       </c>
       <c r="D73" s="11" t="s">
         <v>411</v>
@@ -8771,17 +8780,17 @@
         <v>412</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>924</v>
+        <v>915</v>
       </c>
       <c r="G73" s="12" t="s">
-        <v>925</v>
+        <v>916</v>
       </c>
     </row>
     <row r="74" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A74" s="137"/>
-      <c r="B74" s="140"/>
+      <c r="A74" s="140"/>
+      <c r="B74" s="144"/>
       <c r="C74" s="97" t="s">
-        <v>649</v>
+        <v>640</v>
       </c>
       <c r="D74" s="11" t="s">
         <v>413</v>
@@ -8790,133 +8799,133 @@
         <v>414</v>
       </c>
       <c r="F74" s="11" t="s">
+        <v>917</v>
+      </c>
+      <c r="G74" s="12" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A75" s="140"/>
+      <c r="B75" s="144"/>
+      <c r="C75" s="97" t="s">
+        <v>641</v>
+      </c>
+      <c r="D75" s="11" t="s">
+        <v>919</v>
+      </c>
+      <c r="E75" s="12" t="s">
+        <v>920</v>
+      </c>
+      <c r="F75" s="11" t="s">
+        <v>921</v>
+      </c>
+      <c r="G75" s="12" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A76" s="140"/>
+      <c r="B76" s="144"/>
+      <c r="C76" s="97" t="s">
+        <v>642</v>
+      </c>
+      <c r="D76" s="11" t="s">
+        <v>923</v>
+      </c>
+      <c r="E76" s="12" t="s">
+        <v>924</v>
+      </c>
+      <c r="F76" s="11" t="s">
+        <v>925</v>
+      </c>
+      <c r="G76" s="12" t="s">
         <v>926</v>
       </c>
-      <c r="G74" s="12" t="s">
+    </row>
+    <row r="77" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A77" s="140"/>
+      <c r="B77" s="144"/>
+      <c r="C77" s="97" t="s">
+        <v>643</v>
+      </c>
+      <c r="D77" s="11" t="s">
         <v>927</v>
       </c>
-    </row>
-    <row r="75" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A75" s="137"/>
-      <c r="B75" s="140"/>
-      <c r="C75" s="97" t="s">
-        <v>650</v>
-      </c>
-      <c r="D75" s="11" t="s">
+      <c r="E77" s="12" t="s">
         <v>928</v>
       </c>
-      <c r="E75" s="12" t="s">
+      <c r="F77" s="11" t="s">
         <v>929</v>
       </c>
-      <c r="F75" s="11" t="s">
+      <c r="G77" s="12" t="s">
         <v>930</v>
       </c>
-      <c r="G75" s="12" t="s">
+    </row>
+    <row r="78" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A78" s="140"/>
+      <c r="B78" s="144"/>
+      <c r="C78" s="97" t="s">
+        <v>644</v>
+      </c>
+      <c r="D78" s="11" t="s">
         <v>931</v>
       </c>
-    </row>
-    <row r="76" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A76" s="137"/>
-      <c r="B76" s="140"/>
-      <c r="C76" s="97" t="s">
-        <v>651</v>
-      </c>
-      <c r="D76" s="11" t="s">
+      <c r="E78" s="12" t="s">
         <v>932</v>
       </c>
-      <c r="E76" s="12" t="s">
+      <c r="F78" s="11" t="s">
         <v>933</v>
       </c>
-      <c r="F76" s="11" t="s">
+      <c r="G78" s="12" t="s">
         <v>934</v>
       </c>
-      <c r="G76" s="12" t="s">
+    </row>
+    <row r="79" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A79" s="140"/>
+      <c r="B79" s="144"/>
+      <c r="C79" s="97" t="s">
+        <v>645</v>
+      </c>
+      <c r="D79" s="11" t="s">
         <v>935</v>
       </c>
-    </row>
-    <row r="77" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A77" s="137"/>
-      <c r="B77" s="140"/>
-      <c r="C77" s="97" t="s">
-        <v>652</v>
-      </c>
-      <c r="D77" s="11" t="s">
+      <c r="E79" s="12" t="s">
         <v>936</v>
       </c>
-      <c r="E77" s="12" t="s">
+      <c r="F79" s="11" t="s">
         <v>937</v>
       </c>
-      <c r="F77" s="11" t="s">
+      <c r="G79" s="12" t="s">
         <v>938</v>
       </c>
-      <c r="G77" s="12" t="s">
+    </row>
+    <row r="80" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A80" s="140"/>
+      <c r="B80" s="144"/>
+      <c r="C80" s="96" t="s">
+        <v>646</v>
+      </c>
+      <c r="D80" s="15" t="s">
         <v>939</v>
       </c>
-    </row>
-    <row r="78" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A78" s="137"/>
-      <c r="B78" s="140"/>
-      <c r="C78" s="97" t="s">
-        <v>653</v>
-      </c>
-      <c r="D78" s="11" t="s">
+      <c r="E80" s="16" t="s">
         <v>940</v>
       </c>
-      <c r="E78" s="12" t="s">
+      <c r="F80" s="15" t="s">
         <v>941</v>
       </c>
-      <c r="F78" s="11" t="s">
+      <c r="G80" s="16" t="s">
         <v>942</v>
       </c>
-      <c r="G78" s="12" t="s">
-        <v>943</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A79" s="137"/>
-      <c r="B79" s="140"/>
-      <c r="C79" s="97" t="s">
-        <v>654</v>
-      </c>
-      <c r="D79" s="11" t="s">
-        <v>944</v>
-      </c>
-      <c r="E79" s="12" t="s">
-        <v>945</v>
-      </c>
-      <c r="F79" s="11" t="s">
-        <v>946</v>
-      </c>
-      <c r="G79" s="12" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A80" s="137"/>
-      <c r="B80" s="140"/>
-      <c r="C80" s="96" t="s">
-        <v>655</v>
-      </c>
-      <c r="D80" s="15" t="s">
-        <v>948</v>
-      </c>
-      <c r="E80" s="16" t="s">
-        <v>949</v>
-      </c>
-      <c r="F80" s="15" t="s">
-        <v>950</v>
-      </c>
-      <c r="G80" s="16" t="s">
-        <v>951</v>
-      </c>
     </row>
     <row r="81" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A81" s="137"/>
+      <c r="A81" s="140"/>
       <c r="B81" s="127" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="C81" s="97" t="s">
-        <v>657</v>
+        <v>648</v>
       </c>
       <c r="D81" s="11" t="s">
         <v>415</v>
@@ -8925,17 +8934,17 @@
         <v>416</v>
       </c>
       <c r="F81" s="11" t="s">
-        <v>952</v>
+        <v>943</v>
       </c>
       <c r="G81" s="12" t="s">
-        <v>953</v>
+        <v>944</v>
       </c>
     </row>
     <row r="82" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A82" s="137"/>
+      <c r="A82" s="140"/>
       <c r="B82" s="127"/>
       <c r="C82" s="97" t="s">
-        <v>658</v>
+        <v>649</v>
       </c>
       <c r="D82" s="11" t="s">
         <v>417</v>
@@ -8944,17 +8953,17 @@
         <v>418</v>
       </c>
       <c r="F82" s="11" t="s">
-        <v>954</v>
+        <v>945</v>
       </c>
       <c r="G82" s="12" t="s">
-        <v>955</v>
+        <v>946</v>
       </c>
     </row>
     <row r="83" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A83" s="137"/>
+      <c r="A83" s="140"/>
       <c r="B83" s="127"/>
       <c r="C83" s="97" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="D83" s="11" t="s">
         <v>419</v>
@@ -8963,17 +8972,17 @@
         <v>420</v>
       </c>
       <c r="F83" s="11" t="s">
-        <v>956</v>
+        <v>947</v>
       </c>
       <c r="G83" s="12" t="s">
-        <v>957</v>
+        <v>948</v>
       </c>
     </row>
     <row r="84" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A84" s="137"/>
+      <c r="A84" s="140"/>
       <c r="B84" s="127"/>
       <c r="C84" s="96" t="s">
-        <v>660</v>
+        <v>651</v>
       </c>
       <c r="D84" s="15" t="s">
         <v>421</v>
@@ -8982,19 +8991,19 @@
         <v>422</v>
       </c>
       <c r="F84" s="15" t="s">
-        <v>958</v>
+        <v>949</v>
       </c>
       <c r="G84" s="16" t="s">
-        <v>959</v>
+        <v>950</v>
       </c>
     </row>
     <row r="85" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A85" s="137"/>
+      <c r="A85" s="140"/>
       <c r="B85" s="127" t="s">
-        <v>661</v>
+        <v>652</v>
       </c>
       <c r="C85" s="97" t="s">
-        <v>662</v>
+        <v>653</v>
       </c>
       <c r="D85" s="11" t="s">
         <v>423</v>
@@ -9003,17 +9012,17 @@
         <v>424</v>
       </c>
       <c r="F85" s="11" t="s">
-        <v>960</v>
+        <v>951</v>
       </c>
       <c r="G85" s="12" t="s">
-        <v>961</v>
+        <v>952</v>
       </c>
     </row>
     <row r="86" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A86" s="137"/>
+      <c r="A86" s="140"/>
       <c r="B86" s="127"/>
       <c r="C86" s="97" t="s">
-        <v>663</v>
+        <v>654</v>
       </c>
       <c r="D86" s="11" t="s">
         <v>425</v>
@@ -9022,17 +9031,17 @@
         <v>426</v>
       </c>
       <c r="F86" s="11" t="s">
-        <v>962</v>
+        <v>953</v>
       </c>
       <c r="G86" s="12" t="s">
-        <v>963</v>
+        <v>954</v>
       </c>
     </row>
     <row r="87" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A87" s="137"/>
+      <c r="A87" s="140"/>
       <c r="B87" s="127"/>
       <c r="C87" s="97" t="s">
-        <v>664</v>
+        <v>655</v>
       </c>
       <c r="D87" s="11" t="s">
         <v>427</v>
@@ -9041,17 +9050,17 @@
         <v>428</v>
       </c>
       <c r="F87" s="11" t="s">
-        <v>964</v>
+        <v>955</v>
       </c>
       <c r="G87" s="12" t="s">
-        <v>965</v>
+        <v>956</v>
       </c>
     </row>
     <row r="88" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A88" s="137"/>
+      <c r="A88" s="140"/>
       <c r="B88" s="127"/>
       <c r="C88" s="97" t="s">
-        <v>665</v>
+        <v>656</v>
       </c>
       <c r="D88" s="11" t="s">
         <v>429</v>
@@ -9060,17 +9069,17 @@
         <v>430</v>
       </c>
       <c r="F88" s="11" t="s">
-        <v>966</v>
+        <v>957</v>
       </c>
       <c r="G88" s="12" t="s">
-        <v>967</v>
+        <v>958</v>
       </c>
     </row>
     <row r="89" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A89" s="137"/>
+      <c r="A89" s="140"/>
       <c r="B89" s="127"/>
       <c r="C89" s="97" t="s">
-        <v>666</v>
+        <v>657</v>
       </c>
       <c r="D89" s="11" t="s">
         <v>431</v>
@@ -9079,17 +9088,17 @@
         <v>432</v>
       </c>
       <c r="F89" s="11" t="s">
-        <v>968</v>
+        <v>959</v>
       </c>
       <c r="G89" s="12" t="s">
-        <v>969</v>
+        <v>960</v>
       </c>
     </row>
     <row r="90" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A90" s="137"/>
+      <c r="A90" s="140"/>
       <c r="B90" s="127"/>
       <c r="C90" s="97" t="s">
-        <v>667</v>
+        <v>658</v>
       </c>
       <c r="D90" s="11" t="s">
         <v>433</v>
@@ -9098,17 +9107,17 @@
         <v>434</v>
       </c>
       <c r="F90" s="11" t="s">
-        <v>970</v>
+        <v>961</v>
       </c>
       <c r="G90" s="12" t="s">
-        <v>971</v>
+        <v>962</v>
       </c>
     </row>
     <row r="91" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A91" s="137"/>
+      <c r="A91" s="140"/>
       <c r="B91" s="127"/>
       <c r="C91" s="96" t="s">
-        <v>668</v>
+        <v>659</v>
       </c>
       <c r="D91" s="15" t="s">
         <v>435</v>
@@ -9117,19 +9126,19 @@
         <v>436</v>
       </c>
       <c r="F91" s="15" t="s">
-        <v>972</v>
+        <v>963</v>
       </c>
       <c r="G91" s="16" t="s">
-        <v>973</v>
+        <v>964</v>
       </c>
     </row>
     <row r="92" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A92" s="137"/>
+      <c r="A92" s="140"/>
       <c r="B92" s="127" t="s">
-        <v>669</v>
+        <v>660</v>
       </c>
       <c r="C92" s="97" t="s">
-        <v>670</v>
+        <v>661</v>
       </c>
       <c r="D92" s="11" t="s">
         <v>437</v>
@@ -9138,17 +9147,17 @@
         <v>438</v>
       </c>
       <c r="F92" s="11" t="s">
-        <v>974</v>
+        <v>965</v>
       </c>
       <c r="G92" s="12" t="s">
-        <v>975</v>
+        <v>966</v>
       </c>
     </row>
     <row r="93" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A93" s="137"/>
+      <c r="A93" s="140"/>
       <c r="B93" s="127"/>
       <c r="C93" s="97" t="s">
-        <v>671</v>
+        <v>662</v>
       </c>
       <c r="D93" s="11" t="s">
         <v>439</v>
@@ -9157,17 +9166,17 @@
         <v>440</v>
       </c>
       <c r="F93" s="11" t="s">
-        <v>976</v>
+        <v>967</v>
       </c>
       <c r="G93" s="12" t="s">
-        <v>977</v>
+        <v>968</v>
       </c>
     </row>
     <row r="94" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A94" s="137"/>
+      <c r="A94" s="140"/>
       <c r="B94" s="127"/>
       <c r="C94" s="97" t="s">
-        <v>672</v>
+        <v>663</v>
       </c>
       <c r="D94" s="11" t="s">
         <v>441</v>
@@ -9176,17 +9185,17 @@
         <v>442</v>
       </c>
       <c r="F94" s="11" t="s">
-        <v>978</v>
+        <v>969</v>
       </c>
       <c r="G94" s="12" t="s">
-        <v>979</v>
+        <v>970</v>
       </c>
     </row>
     <row r="95" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A95" s="137"/>
+      <c r="A95" s="140"/>
       <c r="B95" s="127"/>
       <c r="C95" s="97" t="s">
-        <v>673</v>
+        <v>664</v>
       </c>
       <c r="D95" s="11" t="s">
         <v>443</v>
@@ -9195,646 +9204,646 @@
         <v>444</v>
       </c>
       <c r="F95" s="11" t="s">
-        <v>980</v>
+        <v>971</v>
       </c>
       <c r="G95" s="12" t="s">
-        <v>981</v>
+        <v>972</v>
       </c>
     </row>
     <row r="96" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A96" s="137"/>
+      <c r="A96" s="140"/>
       <c r="B96" s="127"/>
       <c r="C96" s="97" t="s">
-        <v>674</v>
+        <v>665</v>
       </c>
       <c r="D96" s="11" t="s">
-        <v>982</v>
+        <v>973</v>
       </c>
       <c r="E96" s="12" t="s">
-        <v>983</v>
+        <v>974</v>
       </c>
       <c r="F96" s="11" t="s">
-        <v>984</v>
+        <v>975</v>
       </c>
       <c r="G96" s="12" t="s">
-        <v>985</v>
+        <v>976</v>
       </c>
     </row>
     <row r="97" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A97" s="137"/>
+      <c r="A97" s="140"/>
       <c r="B97" s="127"/>
       <c r="C97" s="97" t="s">
-        <v>675</v>
+        <v>666</v>
       </c>
       <c r="D97" s="11" t="s">
-        <v>986</v>
+        <v>977</v>
       </c>
       <c r="E97" s="12" t="s">
-        <v>987</v>
+        <v>978</v>
       </c>
       <c r="F97" s="11" t="s">
-        <v>988</v>
+        <v>979</v>
       </c>
       <c r="G97" s="12" t="s">
-        <v>989</v>
+        <v>980</v>
       </c>
     </row>
     <row r="98" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A98" s="137"/>
+      <c r="A98" s="140"/>
       <c r="B98" s="127"/>
       <c r="C98" s="20" t="s">
-        <v>676</v>
+        <v>667</v>
       </c>
       <c r="D98" s="15" t="s">
-        <v>990</v>
+        <v>981</v>
       </c>
       <c r="E98" s="16" t="s">
-        <v>991</v>
+        <v>982</v>
       </c>
       <c r="F98" s="15" t="s">
-        <v>992</v>
+        <v>983</v>
       </c>
       <c r="G98" s="16" t="s">
-        <v>993</v>
+        <v>984</v>
       </c>
     </row>
     <row r="99" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A99" s="137"/>
-      <c r="B99" s="143" t="s">
-        <v>677</v>
+      <c r="A99" s="140"/>
+      <c r="B99" s="147" t="s">
+        <v>668</v>
       </c>
       <c r="C99" s="21" t="s">
-        <v>678</v>
+        <v>669</v>
       </c>
       <c r="D99" s="24" t="s">
         <v>445</v>
       </c>
       <c r="E99" s="22"/>
       <c r="F99" s="24" t="s">
-        <v>994</v>
+        <v>985</v>
       </c>
       <c r="G99" s="22"/>
     </row>
     <row r="100" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A100" s="137"/>
-      <c r="B100" s="144"/>
+      <c r="A100" s="140"/>
+      <c r="B100" s="148"/>
       <c r="C100" s="21" t="s">
-        <v>679</v>
+        <v>670</v>
       </c>
       <c r="D100" s="23" t="s">
-        <v>995</v>
+        <v>986</v>
       </c>
       <c r="E100" s="22"/>
       <c r="F100" s="23" t="s">
-        <v>996</v>
+        <v>987</v>
       </c>
       <c r="G100" s="22"/>
     </row>
     <row r="101" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A101" s="137"/>
-      <c r="B101" s="144"/>
+      <c r="A101" s="140"/>
+      <c r="B101" s="148"/>
       <c r="C101" s="98" t="s">
-        <v>680</v>
+        <v>671</v>
       </c>
       <c r="D101" s="23" t="s">
-        <v>997</v>
+        <v>988</v>
       </c>
       <c r="E101" s="22"/>
       <c r="F101" s="23" t="s">
-        <v>998</v>
+        <v>989</v>
       </c>
       <c r="G101" s="22"/>
     </row>
     <row r="102" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A102" s="137"/>
-      <c r="B102" s="144"/>
+      <c r="A102" s="140"/>
+      <c r="B102" s="148"/>
       <c r="C102" s="98" t="s">
-        <v>681</v>
+        <v>672</v>
       </c>
       <c r="D102" s="23" t="s">
-        <v>999</v>
+        <v>990</v>
       </c>
       <c r="E102" s="22"/>
       <c r="F102" s="23" t="s">
-        <v>1000</v>
+        <v>991</v>
       </c>
       <c r="G102" s="22"/>
     </row>
     <row r="103" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A103" s="137"/>
-      <c r="B103" s="144"/>
+      <c r="A103" s="140"/>
+      <c r="B103" s="148"/>
       <c r="C103" s="98" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="D103" s="23" t="s">
-        <v>1001</v>
+        <v>992</v>
       </c>
       <c r="E103" s="22"/>
       <c r="F103" s="23" t="s">
-        <v>1002</v>
+        <v>993</v>
       </c>
       <c r="G103" s="22"/>
     </row>
     <row r="104" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A104" s="137"/>
-      <c r="B104" s="144"/>
+      <c r="A104" s="140"/>
+      <c r="B104" s="148"/>
       <c r="C104" s="21" t="s">
-        <v>683</v>
+        <v>674</v>
       </c>
       <c r="D104" s="23" t="s">
-        <v>1003</v>
+        <v>994</v>
       </c>
       <c r="E104" s="22"/>
       <c r="F104" s="23" t="s">
-        <v>1004</v>
+        <v>995</v>
       </c>
       <c r="G104" s="22"/>
     </row>
     <row r="105" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A105" s="137"/>
-      <c r="B105" s="144"/>
+      <c r="A105" s="140"/>
+      <c r="B105" s="148"/>
       <c r="C105" s="21" t="s">
-        <v>684</v>
+        <v>675</v>
       </c>
       <c r="D105" s="24" t="s">
         <v>446</v>
       </c>
       <c r="E105" s="22"/>
       <c r="F105" s="24" t="s">
-        <v>1005</v>
+        <v>996</v>
       </c>
       <c r="G105" s="22"/>
     </row>
     <row r="106" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A106" s="137"/>
-      <c r="B106" s="144"/>
+      <c r="A106" s="140"/>
+      <c r="B106" s="148"/>
       <c r="C106" s="21" t="s">
-        <v>685</v>
+        <v>676</v>
       </c>
       <c r="D106" s="23" t="s">
-        <v>1006</v>
+        <v>997</v>
       </c>
       <c r="E106" s="22"/>
       <c r="F106" s="23" t="s">
-        <v>1007</v>
+        <v>998</v>
       </c>
       <c r="G106" s="22"/>
     </row>
     <row r="107" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A107" s="137"/>
-      <c r="B107" s="144"/>
+      <c r="A107" s="140"/>
+      <c r="B107" s="148"/>
       <c r="C107" s="98" t="s">
-        <v>686</v>
+        <v>677</v>
       </c>
       <c r="D107" s="23" t="s">
-        <v>1008</v>
+        <v>999</v>
       </c>
       <c r="E107" s="22"/>
       <c r="F107" s="23" t="s">
-        <v>1009</v>
+        <v>1000</v>
       </c>
       <c r="G107" s="22"/>
     </row>
     <row r="108" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A108" s="137"/>
-      <c r="B108" s="144"/>
+      <c r="A108" s="140"/>
+      <c r="B108" s="148"/>
       <c r="C108" s="98" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="D108" s="23" t="s">
-        <v>1010</v>
+        <v>1001</v>
       </c>
       <c r="E108" s="22"/>
       <c r="F108" s="23" t="s">
-        <v>1011</v>
+        <v>1002</v>
       </c>
       <c r="G108" s="22"/>
     </row>
     <row r="109" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A109" s="137"/>
-      <c r="B109" s="144"/>
+      <c r="A109" s="140"/>
+      <c r="B109" s="148"/>
       <c r="C109" s="98" t="s">
-        <v>688</v>
+        <v>679</v>
       </c>
       <c r="D109" s="23" t="s">
-        <v>1012</v>
+        <v>1003</v>
       </c>
       <c r="E109" s="22"/>
       <c r="F109" s="23" t="s">
-        <v>1013</v>
+        <v>1004</v>
       </c>
       <c r="G109" s="22"/>
     </row>
     <row r="110" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A110" s="137"/>
-      <c r="B110" s="144"/>
+      <c r="A110" s="140"/>
+      <c r="B110" s="148"/>
       <c r="C110" s="98" t="s">
-        <v>689</v>
+        <v>680</v>
       </c>
       <c r="D110" s="23" t="s">
-        <v>1014</v>
+        <v>1005</v>
       </c>
       <c r="E110" s="22"/>
       <c r="F110" s="23" t="s">
-        <v>1015</v>
+        <v>1006</v>
       </c>
       <c r="G110" s="22"/>
     </row>
     <row r="111" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A111" s="137"/>
-      <c r="B111" s="144"/>
+      <c r="A111" s="140"/>
+      <c r="B111" s="148"/>
       <c r="C111" s="21" t="s">
-        <v>690</v>
+        <v>681</v>
       </c>
       <c r="D111" s="23" t="s">
         <v>447</v>
       </c>
       <c r="E111" s="22"/>
       <c r="F111" s="23" t="s">
-        <v>1016</v>
+        <v>1007</v>
       </c>
       <c r="G111" s="22"/>
     </row>
     <row r="112" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A112" s="137"/>
-      <c r="B112" s="144"/>
+      <c r="A112" s="140"/>
+      <c r="B112" s="148"/>
       <c r="C112" s="21" t="s">
-        <v>691</v>
+        <v>682</v>
       </c>
       <c r="D112" s="11" t="s">
         <v>448</v>
       </c>
       <c r="E112" s="22"/>
       <c r="F112" s="11" t="s">
-        <v>1017</v>
+        <v>1008</v>
       </c>
       <c r="G112" s="22"/>
     </row>
     <row r="113" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A113" s="137"/>
-      <c r="B113" s="144"/>
+      <c r="A113" s="140"/>
+      <c r="B113" s="148"/>
       <c r="C113" s="21" t="s">
-        <v>692</v>
+        <v>683</v>
       </c>
       <c r="D113" s="23" t="s">
         <v>449</v>
       </c>
       <c r="E113" s="22"/>
       <c r="F113" s="23" t="s">
-        <v>1018</v>
+        <v>1009</v>
       </c>
       <c r="G113" s="22"/>
     </row>
     <row r="114" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A114" s="137"/>
-      <c r="B114" s="144"/>
+      <c r="A114" s="140"/>
+      <c r="B114" s="148"/>
       <c r="C114" s="21" t="s">
-        <v>693</v>
+        <v>684</v>
       </c>
       <c r="D114" s="23" t="s">
         <v>450</v>
       </c>
       <c r="E114" s="22"/>
       <c r="F114" s="23" t="s">
-        <v>1019</v>
+        <v>1010</v>
       </c>
       <c r="G114" s="22"/>
     </row>
     <row r="115" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A115" s="137"/>
-      <c r="B115" s="144"/>
+      <c r="A115" s="140"/>
+      <c r="B115" s="148"/>
       <c r="C115" s="21" t="s">
-        <v>694</v>
+        <v>685</v>
       </c>
       <c r="D115" s="23" t="s">
         <v>451</v>
       </c>
       <c r="E115" s="22"/>
       <c r="F115" s="23" t="s">
-        <v>1020</v>
+        <v>1011</v>
       </c>
       <c r="G115" s="22"/>
     </row>
     <row r="116" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A116" s="137"/>
-      <c r="B116" s="144"/>
+      <c r="A116" s="140"/>
+      <c r="B116" s="148"/>
       <c r="C116" s="21" t="s">
-        <v>695</v>
+        <v>686</v>
       </c>
       <c r="D116" s="23" t="s">
-        <v>1021</v>
+        <v>1012</v>
       </c>
       <c r="E116" s="22"/>
       <c r="F116" s="23" t="s">
-        <v>1022</v>
+        <v>1013</v>
       </c>
       <c r="G116" s="22"/>
     </row>
     <row r="117" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A117" s="137"/>
-      <c r="B117" s="144"/>
+      <c r="A117" s="140"/>
+      <c r="B117" s="148"/>
       <c r="C117" s="20" t="s">
-        <v>696</v>
+        <v>687</v>
       </c>
       <c r="D117" s="15" t="s">
-        <v>1023</v>
+        <v>1014</v>
       </c>
       <c r="E117" s="22"/>
       <c r="F117" s="15" t="s">
-        <v>1024</v>
+        <v>1015</v>
       </c>
       <c r="G117" s="22"/>
     </row>
     <row r="118" spans="1:7" s="2" customFormat="1" ht="27" customHeight="1">
-      <c r="A118" s="137"/>
-      <c r="B118" s="145"/>
+      <c r="A118" s="140"/>
+      <c r="B118" s="149"/>
       <c r="C118" s="25" t="s">
-        <v>697</v>
+        <v>688</v>
       </c>
       <c r="D118" s="26" t="s">
-        <v>1025</v>
+        <v>1016</v>
       </c>
       <c r="E118" s="22"/>
       <c r="F118" s="26" t="s">
-        <v>1026</v>
+        <v>1017</v>
       </c>
       <c r="G118" s="22"/>
     </row>
     <row r="119" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A119" s="137"/>
-      <c r="B119" s="143" t="s">
-        <v>698</v>
+      <c r="A119" s="140"/>
+      <c r="B119" s="147" t="s">
+        <v>689</v>
       </c>
       <c r="C119" s="98" t="s">
-        <v>699</v>
+        <v>690</v>
       </c>
       <c r="D119" s="24" t="s">
         <v>452</v>
       </c>
       <c r="E119" s="22"/>
       <c r="F119" s="24" t="s">
-        <v>1027</v>
+        <v>1018</v>
       </c>
       <c r="G119" s="22"/>
     </row>
     <row r="120" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A120" s="137"/>
-      <c r="B120" s="144"/>
+      <c r="A120" s="140"/>
+      <c r="B120" s="148"/>
       <c r="C120" s="98" t="s">
-        <v>700</v>
+        <v>691</v>
       </c>
       <c r="D120" s="11" t="s">
-        <v>1028</v>
+        <v>1019</v>
       </c>
       <c r="E120" s="22"/>
       <c r="F120" s="11" t="s">
-        <v>1029</v>
+        <v>1020</v>
       </c>
       <c r="G120" s="22"/>
     </row>
     <row r="121" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A121" s="137"/>
-      <c r="B121" s="144"/>
+      <c r="A121" s="140"/>
+      <c r="B121" s="148"/>
       <c r="C121" s="98" t="s">
-        <v>701</v>
+        <v>692</v>
       </c>
       <c r="D121" s="11" t="s">
-        <v>1030</v>
+        <v>1021</v>
       </c>
       <c r="E121" s="22"/>
       <c r="F121" s="11" t="s">
-        <v>1031</v>
+        <v>1022</v>
       </c>
       <c r="G121" s="22"/>
     </row>
     <row r="122" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A122" s="137"/>
-      <c r="B122" s="144"/>
+      <c r="A122" s="140"/>
+      <c r="B122" s="148"/>
       <c r="C122" s="98" t="s">
-        <v>702</v>
+        <v>693</v>
       </c>
       <c r="D122" s="24" t="s">
         <v>453</v>
       </c>
       <c r="E122" s="22"/>
       <c r="F122" s="24" t="s">
-        <v>1032</v>
+        <v>1023</v>
       </c>
       <c r="G122" s="22"/>
     </row>
     <row r="123" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A123" s="137"/>
-      <c r="B123" s="144"/>
+      <c r="A123" s="140"/>
+      <c r="B123" s="148"/>
       <c r="C123" s="98" t="s">
-        <v>703</v>
+        <v>694</v>
       </c>
       <c r="D123" s="11" t="s">
-        <v>1033</v>
+        <v>1024</v>
       </c>
       <c r="E123" s="22"/>
       <c r="F123" s="11" t="s">
-        <v>1034</v>
+        <v>1025</v>
       </c>
       <c r="G123" s="22"/>
     </row>
     <row r="124" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A124" s="137"/>
-      <c r="B124" s="144"/>
+      <c r="A124" s="140"/>
+      <c r="B124" s="148"/>
       <c r="C124" s="98" t="s">
-        <v>704</v>
+        <v>695</v>
       </c>
       <c r="D124" s="11" t="s">
-        <v>1035</v>
+        <v>1026</v>
       </c>
       <c r="E124" s="22"/>
       <c r="F124" s="11" t="s">
-        <v>1036</v>
+        <v>1027</v>
       </c>
       <c r="G124" s="22"/>
     </row>
     <row r="125" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A125" s="137"/>
-      <c r="B125" s="144"/>
+      <c r="A125" s="140"/>
+      <c r="B125" s="148"/>
       <c r="C125" s="98" t="s">
-        <v>705</v>
+        <v>696</v>
       </c>
       <c r="D125" s="24" t="s">
         <v>454</v>
       </c>
       <c r="E125" s="22"/>
       <c r="F125" s="24" t="s">
-        <v>1037</v>
+        <v>1028</v>
       </c>
       <c r="G125" s="22"/>
     </row>
     <row r="126" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A126" s="137"/>
-      <c r="B126" s="144"/>
+      <c r="A126" s="140"/>
+      <c r="B126" s="148"/>
       <c r="C126" s="98" t="s">
-        <v>706</v>
+        <v>697</v>
       </c>
       <c r="D126" s="11" t="s">
-        <v>1038</v>
+        <v>1029</v>
       </c>
       <c r="E126" s="22"/>
       <c r="F126" s="11" t="s">
-        <v>1039</v>
+        <v>1030</v>
       </c>
       <c r="G126" s="22"/>
     </row>
     <row r="127" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A127" s="137"/>
-      <c r="B127" s="144"/>
+      <c r="A127" s="140"/>
+      <c r="B127" s="148"/>
       <c r="C127" s="98" t="s">
-        <v>707</v>
+        <v>698</v>
       </c>
       <c r="D127" s="11" t="s">
-        <v>1040</v>
+        <v>1031</v>
       </c>
       <c r="E127" s="22"/>
       <c r="F127" s="11" t="s">
-        <v>1041</v>
+        <v>1032</v>
       </c>
       <c r="G127" s="22"/>
     </row>
     <row r="128" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A128" s="137"/>
-      <c r="B128" s="144"/>
+      <c r="A128" s="140"/>
+      <c r="B128" s="148"/>
       <c r="C128" s="98" t="s">
-        <v>708</v>
+        <v>699</v>
       </c>
       <c r="D128" s="24" t="s">
         <v>455</v>
       </c>
       <c r="E128" s="22"/>
       <c r="F128" s="24" t="s">
-        <v>1042</v>
+        <v>1033</v>
       </c>
       <c r="G128" s="22"/>
     </row>
     <row r="129" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A129" s="137"/>
-      <c r="B129" s="144"/>
+      <c r="A129" s="140"/>
+      <c r="B129" s="148"/>
       <c r="C129" s="98" t="s">
-        <v>709</v>
+        <v>700</v>
       </c>
       <c r="D129" s="11" t="s">
-        <v>1043</v>
+        <v>1034</v>
       </c>
       <c r="E129" s="22"/>
       <c r="F129" s="11" t="s">
-        <v>1044</v>
+        <v>1035</v>
       </c>
       <c r="G129" s="22"/>
     </row>
     <row r="130" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A130" s="137"/>
-      <c r="B130" s="144"/>
+      <c r="A130" s="140"/>
+      <c r="B130" s="148"/>
       <c r="C130" s="98" t="s">
-        <v>710</v>
+        <v>701</v>
       </c>
       <c r="D130" s="11" t="s">
-        <v>1045</v>
+        <v>1036</v>
       </c>
       <c r="E130" s="22"/>
       <c r="F130" s="11" t="s">
-        <v>1046</v>
+        <v>1037</v>
       </c>
       <c r="G130" s="22"/>
     </row>
     <row r="131" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A131" s="137"/>
-      <c r="B131" s="144"/>
+      <c r="A131" s="140"/>
+      <c r="B131" s="148"/>
       <c r="C131" s="98" t="s">
-        <v>711</v>
+        <v>702</v>
       </c>
       <c r="D131" s="24" t="s">
         <v>456</v>
       </c>
       <c r="E131" s="22"/>
       <c r="F131" s="24" t="s">
-        <v>1047</v>
+        <v>1038</v>
       </c>
       <c r="G131" s="22"/>
     </row>
     <row r="132" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A132" s="137"/>
-      <c r="B132" s="144"/>
+      <c r="A132" s="140"/>
+      <c r="B132" s="148"/>
       <c r="C132" s="98" t="s">
-        <v>712</v>
+        <v>703</v>
       </c>
       <c r="D132" s="11" t="s">
-        <v>1048</v>
+        <v>1039</v>
       </c>
       <c r="E132" s="22"/>
       <c r="F132" s="11" t="s">
-        <v>1049</v>
+        <v>1040</v>
       </c>
       <c r="G132" s="22"/>
     </row>
     <row r="133" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A133" s="137"/>
-      <c r="B133" s="144"/>
+      <c r="A133" s="140"/>
+      <c r="B133" s="148"/>
       <c r="C133" s="98" t="s">
-        <v>713</v>
+        <v>704</v>
       </c>
       <c r="D133" s="11" t="s">
-        <v>1050</v>
+        <v>1041</v>
       </c>
       <c r="E133" s="22"/>
       <c r="F133" s="11" t="s">
-        <v>1051</v>
+        <v>1042</v>
       </c>
       <c r="G133" s="22"/>
     </row>
     <row r="134" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A134" s="137"/>
-      <c r="B134" s="144"/>
+      <c r="A134" s="140"/>
+      <c r="B134" s="148"/>
       <c r="C134" s="98" t="s">
-        <v>714</v>
+        <v>705</v>
       </c>
       <c r="D134" s="24" t="s">
         <v>457</v>
       </c>
       <c r="E134" s="22"/>
       <c r="F134" s="24" t="s">
-        <v>1052</v>
+        <v>1043</v>
       </c>
       <c r="G134" s="22"/>
     </row>
     <row r="135" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A135" s="137"/>
-      <c r="B135" s="144"/>
+      <c r="A135" s="140"/>
+      <c r="B135" s="148"/>
       <c r="C135" s="98" t="s">
-        <v>715</v>
+        <v>706</v>
       </c>
       <c r="D135" s="11" t="s">
-        <v>1053</v>
+        <v>1044</v>
       </c>
       <c r="E135" s="22"/>
       <c r="F135" s="11" t="s">
-        <v>1054</v>
+        <v>1045</v>
       </c>
       <c r="G135" s="22"/>
     </row>
     <row r="136" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A136" s="137"/>
-      <c r="B136" s="144"/>
+      <c r="A136" s="140"/>
+      <c r="B136" s="148"/>
       <c r="C136" s="98" t="s">
-        <v>716</v>
+        <v>707</v>
       </c>
       <c r="D136" s="11" t="s">
-        <v>1055</v>
+        <v>1046</v>
       </c>
       <c r="E136" s="22"/>
       <c r="F136" s="11" t="s">
-        <v>1056</v>
+        <v>1047</v>
       </c>
       <c r="G136" s="22"/>
     </row>
     <row r="137" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A137" s="137"/>
-      <c r="B137" s="144"/>
+      <c r="A137" s="140"/>
+      <c r="B137" s="148"/>
       <c r="C137" s="27" t="s">
         <v>458</v>
       </c>
@@ -9843,223 +9852,223 @@
       </c>
       <c r="E137" s="22"/>
       <c r="F137" s="15" t="s">
-        <v>1057</v>
+        <v>1048</v>
       </c>
       <c r="G137" s="22"/>
     </row>
     <row r="138" spans="1:7" s="2" customFormat="1" ht="37.5" customHeight="1">
-      <c r="A138" s="137"/>
-      <c r="B138" s="145"/>
+      <c r="A138" s="140"/>
+      <c r="B138" s="149"/>
       <c r="C138" s="27" t="s">
-        <v>717</v>
+        <v>708</v>
       </c>
       <c r="D138" s="26" t="s">
-        <v>1058</v>
+        <v>1049</v>
       </c>
       <c r="E138" s="22"/>
       <c r="F138" s="26" t="s">
-        <v>1059</v>
+        <v>1050</v>
       </c>
       <c r="G138" s="22"/>
     </row>
     <row r="139" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A139" s="137"/>
-      <c r="B139" s="140" t="s">
-        <v>718</v>
+      <c r="A139" s="140"/>
+      <c r="B139" s="144" t="s">
+        <v>709</v>
       </c>
       <c r="C139" s="98" t="s">
-        <v>719</v>
+        <v>710</v>
       </c>
       <c r="D139" s="11" t="s">
         <v>460</v>
       </c>
       <c r="E139" s="22"/>
       <c r="F139" s="11" t="s">
-        <v>1060</v>
+        <v>1051</v>
       </c>
       <c r="G139" s="22"/>
     </row>
     <row r="140" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A140" s="137"/>
-      <c r="B140" s="140"/>
+      <c r="A140" s="140"/>
+      <c r="B140" s="144"/>
       <c r="C140" s="98" t="s">
-        <v>720</v>
+        <v>711</v>
       </c>
       <c r="D140" s="11" t="s">
         <v>461</v>
       </c>
       <c r="E140" s="22"/>
       <c r="F140" s="11" t="s">
-        <v>1061</v>
+        <v>1052</v>
       </c>
       <c r="G140" s="22"/>
     </row>
     <row r="141" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A141" s="137"/>
-      <c r="B141" s="140"/>
+      <c r="A141" s="140"/>
+      <c r="B141" s="144"/>
       <c r="C141" s="98" t="s">
-        <v>721</v>
+        <v>712</v>
       </c>
       <c r="D141" s="11" t="s">
         <v>462</v>
       </c>
       <c r="E141" s="22"/>
       <c r="F141" s="11" t="s">
-        <v>1062</v>
+        <v>1053</v>
       </c>
       <c r="G141" s="22"/>
     </row>
     <row r="142" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A142" s="137"/>
-      <c r="B142" s="140"/>
+      <c r="A142" s="140"/>
+      <c r="B142" s="144"/>
       <c r="C142" s="98" t="s">
-        <v>722</v>
+        <v>713</v>
       </c>
       <c r="D142" s="11" t="s">
         <v>463</v>
       </c>
       <c r="E142" s="22"/>
       <c r="F142" s="11" t="s">
-        <v>1063</v>
+        <v>1054</v>
       </c>
       <c r="G142" s="22"/>
     </row>
     <row r="143" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A143" s="137"/>
-      <c r="B143" s="140"/>
+      <c r="A143" s="140"/>
+      <c r="B143" s="144"/>
       <c r="C143" s="98" t="s">
-        <v>723</v>
+        <v>714</v>
       </c>
       <c r="D143" s="11" t="s">
         <v>464</v>
       </c>
       <c r="E143" s="22"/>
       <c r="F143" s="11" t="s">
-        <v>1064</v>
+        <v>1055</v>
       </c>
       <c r="G143" s="22"/>
     </row>
     <row r="144" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A144" s="137"/>
-      <c r="B144" s="140"/>
+      <c r="A144" s="140"/>
+      <c r="B144" s="144"/>
       <c r="C144" s="98" t="s">
-        <v>724</v>
+        <v>715</v>
       </c>
       <c r="D144" s="11" t="s">
         <v>465</v>
       </c>
       <c r="E144" s="22"/>
       <c r="F144" s="11" t="s">
-        <v>1065</v>
+        <v>1056</v>
       </c>
       <c r="G144" s="22"/>
     </row>
     <row r="145" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A145" s="137"/>
-      <c r="B145" s="140"/>
+      <c r="A145" s="140"/>
+      <c r="B145" s="144"/>
       <c r="C145" s="98" t="s">
-        <v>725</v>
+        <v>716</v>
       </c>
       <c r="D145" s="11" t="s">
         <v>466</v>
       </c>
       <c r="E145" s="22"/>
       <c r="F145" s="11" t="s">
-        <v>1066</v>
+        <v>1057</v>
       </c>
       <c r="G145" s="22"/>
     </row>
     <row r="146" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A146" s="137"/>
-      <c r="B146" s="140"/>
+      <c r="A146" s="140"/>
+      <c r="B146" s="144"/>
       <c r="C146" s="27" t="s">
-        <v>726</v>
+        <v>717</v>
       </c>
       <c r="D146" s="15" t="s">
         <v>467</v>
       </c>
       <c r="E146" s="22"/>
       <c r="F146" s="15" t="s">
-        <v>1067</v>
+        <v>1058</v>
       </c>
       <c r="G146" s="22"/>
     </row>
     <row r="147" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A147" s="137"/>
-      <c r="B147" s="125" t="s">
-        <v>727</v>
-      </c>
-      <c r="C147" s="125"/>
+      <c r="A147" s="140"/>
+      <c r="B147" s="142" t="s">
+        <v>718</v>
+      </c>
+      <c r="C147" s="142"/>
       <c r="D147" s="15" t="s">
-        <v>1068</v>
+        <v>1059</v>
       </c>
       <c r="E147" s="16" t="s">
-        <v>1069</v>
+        <v>1060</v>
       </c>
       <c r="F147" s="15" t="s">
-        <v>1070</v>
+        <v>1061</v>
       </c>
       <c r="G147" s="16" t="s">
-        <v>1071</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="148" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A148" s="137"/>
+      <c r="A148" s="140"/>
       <c r="B148" s="127" t="s">
-        <v>728</v>
+        <v>719</v>
       </c>
       <c r="C148" s="127"/>
       <c r="D148" s="18"/>
       <c r="E148" s="28" t="s">
-        <v>1072</v>
+        <v>1063</v>
       </c>
       <c r="F148" s="18"/>
       <c r="G148" s="28" t="s">
-        <v>1073</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="149" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A149" s="137"/>
-      <c r="B149" s="146" t="s">
-        <v>729</v>
-      </c>
-      <c r="C149" s="147"/>
+      <c r="A149" s="140"/>
+      <c r="B149" s="128" t="s">
+        <v>720</v>
+      </c>
+      <c r="C149" s="129"/>
       <c r="D149" s="11" t="s">
-        <v>1074</v>
+        <v>1065</v>
       </c>
       <c r="E149" s="19"/>
       <c r="F149" s="11" t="s">
-        <v>1075</v>
+        <v>1066</v>
       </c>
       <c r="G149" s="19"/>
     </row>
     <row r="150" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A150" s="138"/>
-      <c r="B150" s="146" t="s">
-        <v>730</v>
-      </c>
-      <c r="C150" s="147"/>
+      <c r="A150" s="141"/>
+      <c r="B150" s="128" t="s">
+        <v>721</v>
+      </c>
+      <c r="C150" s="129"/>
       <c r="D150" s="11" t="s">
-        <v>1076</v>
+        <v>1067</v>
       </c>
       <c r="E150" s="28" t="s">
-        <v>1077</v>
+        <v>1068</v>
       </c>
       <c r="F150" s="11" t="s">
-        <v>1078</v>
+        <v>1069</v>
       </c>
       <c r="G150" s="28" t="s">
-        <v>1079</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="151" spans="1:7" s="2" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A151" s="123" t="s">
+      <c r="A151" s="150" t="s">
         <v>468</v>
       </c>
-      <c r="B151" s="125" t="s">
+      <c r="B151" s="142" t="s">
         <v>469</v>
       </c>
-      <c r="C151" s="126"/>
+      <c r="C151" s="130"/>
       <c r="D151" s="9" t="s">
         <v>292</v>
       </c>
@@ -10074,7 +10083,7 @@
       </c>
     </row>
     <row r="152" spans="1:7" s="2" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A152" s="124"/>
+      <c r="A152" s="151"/>
       <c r="B152" s="127" t="s">
         <v>470</v>
       </c>
@@ -10088,14 +10097,14 @@
         <v>473</v>
       </c>
       <c r="F152" s="23" t="s">
-        <v>1080</v>
+        <v>1071</v>
       </c>
       <c r="G152" s="29" t="s">
-        <v>1081</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="153" spans="1:7" s="2" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A153" s="124"/>
+      <c r="A153" s="151"/>
       <c r="B153" s="127"/>
       <c r="C153" s="97" t="s">
         <v>474</v>
@@ -10107,14 +10116,14 @@
         <v>476</v>
       </c>
       <c r="F153" s="23" t="s">
-        <v>1082</v>
+        <v>1073</v>
       </c>
       <c r="G153" s="29" t="s">
-        <v>1083</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="154" spans="1:7" s="2" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A154" s="124"/>
+      <c r="A154" s="151"/>
       <c r="B154" s="127"/>
       <c r="C154" s="97" t="s">
         <v>477</v>
@@ -10126,18 +10135,18 @@
         <v>479</v>
       </c>
       <c r="F154" s="24" t="s">
-        <v>1084</v>
+        <v>1075</v>
       </c>
       <c r="G154" s="30" t="s">
-        <v>1085</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="155" spans="1:7" s="2" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A155" s="124"/>
+      <c r="A155" s="151"/>
       <c r="B155" s="127" t="s">
         <v>480</v>
       </c>
-      <c r="C155" s="126"/>
+      <c r="C155" s="130"/>
       <c r="D155" s="23" t="s">
         <v>481</v>
       </c>
@@ -10145,37 +10154,37 @@
         <v>482</v>
       </c>
       <c r="F155" s="23" t="s">
-        <v>1086</v>
+        <v>1077</v>
       </c>
       <c r="G155" s="29" t="s">
-        <v>1087</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="156" spans="1:7" s="2" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A156" s="124"/>
+      <c r="A156" s="151"/>
       <c r="B156" s="127" t="s">
-        <v>731</v>
-      </c>
-      <c r="C156" s="126"/>
+        <v>722</v>
+      </c>
+      <c r="C156" s="130"/>
       <c r="D156" s="23" t="s">
-        <v>1088</v>
+        <v>1079</v>
       </c>
       <c r="E156" s="29" t="s">
-        <v>1089</v>
+        <v>1080</v>
       </c>
       <c r="F156" s="23" t="s">
-        <v>1090</v>
+        <v>1081</v>
       </c>
       <c r="G156" s="29" t="s">
-        <v>1091</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="157" spans="1:7" s="2" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A157" s="124"/>
-      <c r="B157" s="125" t="s">
+      <c r="A157" s="151"/>
+      <c r="B157" s="142" t="s">
         <v>483</v>
       </c>
-      <c r="C157" s="156"/>
+      <c r="C157" s="160"/>
       <c r="D157" s="15" t="s">
         <v>484</v>
       </c>
@@ -10183,20 +10192,20 @@
         <v>485</v>
       </c>
       <c r="F157" s="15" t="s">
-        <v>1092</v>
+        <v>1083</v>
       </c>
       <c r="G157" s="31" t="s">
-        <v>1093</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="158" spans="1:7" s="2" customFormat="1" ht="23.25" customHeight="1">
-      <c r="A158" s="128" t="s">
+      <c r="A158" s="152" t="s">
         <v>486</v>
       </c>
-      <c r="B158" s="125" t="s">
+      <c r="B158" s="142" t="s">
         <v>487</v>
       </c>
-      <c r="C158" s="130"/>
+      <c r="C158" s="154"/>
       <c r="D158" s="9" t="s">
         <v>15</v>
       </c>
@@ -10207,71 +10216,71 @@
       <c r="G158" s="32"/>
     </row>
     <row r="159" spans="1:7" s="2" customFormat="1" ht="23.25" customHeight="1">
-      <c r="A159" s="128"/>
-      <c r="B159" s="131" t="s">
-        <v>732</v>
+      <c r="A159" s="152"/>
+      <c r="B159" s="155" t="s">
+        <v>723</v>
       </c>
       <c r="C159" s="34" t="s">
-        <v>733</v>
+        <v>724</v>
       </c>
       <c r="D159" s="23" t="s">
+        <v>1085</v>
+      </c>
+      <c r="E159" s="12" t="s">
+        <v>1086</v>
+      </c>
+      <c r="F159" s="23" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G159" s="12" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" s="2" customFormat="1" ht="23.25" customHeight="1">
+      <c r="A160" s="152"/>
+      <c r="B160" s="155"/>
+      <c r="C160" s="34" t="s">
+        <v>725</v>
+      </c>
+      <c r="D160" s="23" t="s">
+        <v>1089</v>
+      </c>
+      <c r="E160" s="12" t="s">
+        <v>1090</v>
+      </c>
+      <c r="F160" s="23" t="s">
+        <v>1091</v>
+      </c>
+      <c r="G160" s="12" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" s="2" customFormat="1" ht="23.25" customHeight="1">
+      <c r="A161" s="152"/>
+      <c r="B161" s="155"/>
+      <c r="C161" s="34" t="s">
+        <v>726</v>
+      </c>
+      <c r="D161" s="23" t="s">
+        <v>1093</v>
+      </c>
+      <c r="E161" s="12" t="s">
         <v>1094</v>
       </c>
-      <c r="E159" s="12" t="s">
+      <c r="F161" s="23" t="s">
         <v>1095</v>
       </c>
-      <c r="F159" s="23" t="s">
+      <c r="G161" s="12" t="s">
         <v>1096</v>
       </c>
-      <c r="G159" s="12" t="s">
-        <v>1097</v>
-      </c>
-    </row>
-    <row r="160" spans="1:7" s="2" customFormat="1" ht="23.25" customHeight="1">
-      <c r="A160" s="128"/>
-      <c r="B160" s="131"/>
-      <c r="C160" s="34" t="s">
-        <v>734</v>
-      </c>
-      <c r="D160" s="23" t="s">
-        <v>1098</v>
-      </c>
-      <c r="E160" s="12" t="s">
-        <v>1099</v>
-      </c>
-      <c r="F160" s="23" t="s">
-        <v>1100</v>
-      </c>
-      <c r="G160" s="12" t="s">
-        <v>1101</v>
-      </c>
-    </row>
-    <row r="161" spans="1:7" s="2" customFormat="1" ht="23.25" customHeight="1">
-      <c r="A161" s="128"/>
-      <c r="B161" s="131"/>
-      <c r="C161" s="34" t="s">
-        <v>735</v>
-      </c>
-      <c r="D161" s="23" t="s">
-        <v>1102</v>
-      </c>
-      <c r="E161" s="12" t="s">
-        <v>1103</v>
-      </c>
-      <c r="F161" s="23" t="s">
-        <v>1104</v>
-      </c>
-      <c r="G161" s="12" t="s">
-        <v>1105</v>
-      </c>
     </row>
     <row r="162" spans="1:7" s="2" customFormat="1" ht="23.25" customHeight="1">
-      <c r="A162" s="128"/>
-      <c r="B162" s="132" t="s">
-        <v>736</v>
+      <c r="A162" s="152"/>
+      <c r="B162" s="156" t="s">
+        <v>727</v>
       </c>
       <c r="C162" s="34" t="s">
-        <v>737</v>
+        <v>728</v>
       </c>
       <c r="D162" s="35"/>
       <c r="E162" s="12" t="s">
@@ -10279,14 +10288,14 @@
       </c>
       <c r="F162" s="35"/>
       <c r="G162" s="12" t="s">
-        <v>1106</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="163" spans="1:7" s="2" customFormat="1" ht="23.25" customHeight="1">
-      <c r="A163" s="128"/>
-      <c r="B163" s="133"/>
+      <c r="A163" s="152"/>
+      <c r="B163" s="157"/>
       <c r="C163" s="34" t="s">
-        <v>738</v>
+        <v>729</v>
       </c>
       <c r="D163" s="35"/>
       <c r="E163" s="12" t="s">
@@ -10294,14 +10303,14 @@
       </c>
       <c r="F163" s="35"/>
       <c r="G163" s="12" t="s">
-        <v>1107</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="164" spans="1:7" s="2" customFormat="1" ht="23.25" customHeight="1">
-      <c r="A164" s="128"/>
-      <c r="B164" s="133"/>
+      <c r="A164" s="152"/>
+      <c r="B164" s="157"/>
       <c r="C164" s="34" t="s">
-        <v>739</v>
+        <v>730</v>
       </c>
       <c r="D164" s="35"/>
       <c r="E164" s="12" t="s">
@@ -10309,14 +10318,14 @@
       </c>
       <c r="F164" s="35"/>
       <c r="G164" s="12" t="s">
-        <v>1108</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="165" spans="1:7" s="2" customFormat="1" ht="23.25" customHeight="1">
-      <c r="A165" s="128"/>
-      <c r="B165" s="133"/>
+      <c r="A165" s="152"/>
+      <c r="B165" s="157"/>
       <c r="C165" s="34" t="s">
-        <v>740</v>
+        <v>731</v>
       </c>
       <c r="D165" s="35"/>
       <c r="E165" s="12" t="s">
@@ -10324,14 +10333,14 @@
       </c>
       <c r="F165" s="35"/>
       <c r="G165" s="12" t="s">
-        <v>1109</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="166" spans="1:7" s="2" customFormat="1" ht="23.25" customHeight="1">
-      <c r="A166" s="128"/>
-      <c r="B166" s="133"/>
+      <c r="A166" s="152"/>
+      <c r="B166" s="157"/>
       <c r="C166" s="34" t="s">
-        <v>741</v>
+        <v>732</v>
       </c>
       <c r="D166" s="35"/>
       <c r="E166" s="12" t="s">
@@ -10339,14 +10348,14 @@
       </c>
       <c r="F166" s="35"/>
       <c r="G166" s="12" t="s">
-        <v>1110</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="167" spans="1:7" s="2" customFormat="1" ht="23.25" customHeight="1">
-      <c r="A167" s="128"/>
-      <c r="B167" s="134"/>
+      <c r="A167" s="152"/>
+      <c r="B167" s="158"/>
       <c r="C167" s="34" t="s">
-        <v>742</v>
+        <v>733</v>
       </c>
       <c r="D167" s="35"/>
       <c r="E167" s="12" t="s">
@@ -10354,15 +10363,15 @@
       </c>
       <c r="F167" s="35"/>
       <c r="G167" s="12" t="s">
-        <v>1111</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="168" spans="1:7" s="2" customFormat="1" ht="23.25" customHeight="1">
-      <c r="A168" s="128"/>
-      <c r="B168" s="125" t="s">
+      <c r="A168" s="152"/>
+      <c r="B168" s="142" t="s">
         <v>488</v>
       </c>
-      <c r="C168" s="130"/>
+      <c r="C168" s="154"/>
       <c r="D168" s="33"/>
       <c r="E168" s="10" t="s">
         <v>293</v>
@@ -10373,147 +10382,147 @@
       </c>
     </row>
     <row r="169" spans="1:7" s="2" customFormat="1" ht="23.25" customHeight="1">
-      <c r="A169" s="128"/>
-      <c r="B169" s="131" t="s">
-        <v>743</v>
+      <c r="A169" s="152"/>
+      <c r="B169" s="155" t="s">
+        <v>734</v>
       </c>
       <c r="C169" s="34" t="s">
-        <v>744</v>
+        <v>735</v>
       </c>
       <c r="D169" s="35"/>
       <c r="E169" s="12" t="s">
-        <v>1112</v>
+        <v>1103</v>
       </c>
       <c r="F169" s="35"/>
       <c r="G169" s="12" t="s">
-        <v>1113</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="170" spans="1:7" s="2" customFormat="1" ht="23.25" customHeight="1">
-      <c r="A170" s="128"/>
-      <c r="B170" s="131"/>
+      <c r="A170" s="152"/>
+      <c r="B170" s="155"/>
       <c r="C170" s="34" t="s">
-        <v>745</v>
+        <v>736</v>
       </c>
       <c r="D170" s="35"/>
       <c r="E170" s="12" t="s">
-        <v>1114</v>
+        <v>1105</v>
       </c>
       <c r="F170" s="35"/>
       <c r="G170" s="12" t="s">
-        <v>1115</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="171" spans="1:7" s="2" customFormat="1" ht="23.25" customHeight="1">
-      <c r="A171" s="128"/>
-      <c r="B171" s="131"/>
+      <c r="A171" s="152"/>
+      <c r="B171" s="155"/>
       <c r="C171" s="34" t="s">
-        <v>746</v>
+        <v>737</v>
       </c>
       <c r="D171" s="35"/>
       <c r="E171" s="12" t="s">
-        <v>1116</v>
+        <v>1107</v>
       </c>
       <c r="F171" s="35"/>
       <c r="G171" s="12" t="s">
-        <v>1117</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="172" spans="1:7" s="2" customFormat="1" ht="23.25" customHeight="1">
-      <c r="A172" s="128"/>
-      <c r="B172" s="131"/>
+      <c r="A172" s="152"/>
+      <c r="B172" s="155"/>
       <c r="C172" s="34" t="s">
-        <v>747</v>
+        <v>738</v>
       </c>
       <c r="D172" s="35"/>
       <c r="E172" s="12" t="s">
-        <v>1118</v>
+        <v>1109</v>
       </c>
       <c r="F172" s="35"/>
       <c r="G172" s="12" t="s">
-        <v>1119</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="173" spans="1:7" s="2" customFormat="1" ht="23.25" customHeight="1">
-      <c r="A173" s="128"/>
-      <c r="B173" s="131"/>
+      <c r="A173" s="152"/>
+      <c r="B173" s="155"/>
       <c r="C173" s="34" t="s">
-        <v>748</v>
+        <v>739</v>
       </c>
       <c r="D173" s="35"/>
       <c r="E173" s="12" t="s">
-        <v>1120</v>
+        <v>1111</v>
       </c>
       <c r="F173" s="35"/>
       <c r="G173" s="12" t="s">
-        <v>1121</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="174" spans="1:7" s="2" customFormat="1" ht="23.25" customHeight="1">
-      <c r="A174" s="128"/>
-      <c r="B174" s="131"/>
+      <c r="A174" s="152"/>
+      <c r="B174" s="155"/>
       <c r="C174" s="34" t="s">
-        <v>749</v>
+        <v>740</v>
       </c>
       <c r="D174" s="35"/>
       <c r="E174" s="12" t="s">
-        <v>1122</v>
+        <v>1113</v>
       </c>
       <c r="F174" s="35"/>
       <c r="G174" s="12" t="s">
-        <v>1123</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="175" spans="1:7" s="2" customFormat="1" ht="23.25" customHeight="1">
-      <c r="A175" s="128"/>
-      <c r="B175" s="131"/>
+      <c r="A175" s="152"/>
+      <c r="B175" s="155"/>
       <c r="C175" s="34" t="s">
-        <v>750</v>
+        <v>741</v>
       </c>
       <c r="D175" s="35"/>
       <c r="E175" s="12" t="s">
-        <v>1124</v>
+        <v>1115</v>
       </c>
       <c r="F175" s="35"/>
       <c r="G175" s="12" t="s">
-        <v>1125</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="176" spans="1:7" s="2" customFormat="1" ht="23.25" customHeight="1">
-      <c r="A176" s="128"/>
-      <c r="B176" s="131"/>
+      <c r="A176" s="152"/>
+      <c r="B176" s="155"/>
       <c r="C176" s="34" t="s">
-        <v>751</v>
+        <v>742</v>
       </c>
       <c r="D176" s="35"/>
       <c r="E176" s="12" t="s">
-        <v>1126</v>
+        <v>1117</v>
       </c>
       <c r="F176" s="35"/>
       <c r="G176" s="12" t="s">
-        <v>1127</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="177" spans="1:7" s="2" customFormat="1" ht="23.25" customHeight="1" thickBot="1">
-      <c r="A177" s="129"/>
-      <c r="B177" s="135"/>
+      <c r="A177" s="153"/>
+      <c r="B177" s="159"/>
       <c r="C177" s="36" t="s">
-        <v>752</v>
+        <v>743</v>
       </c>
       <c r="D177" s="37"/>
       <c r="E177" s="38" t="s">
-        <v>1128</v>
+        <v>1119</v>
       </c>
       <c r="F177" s="37"/>
       <c r="G177" s="38" t="s">
-        <v>1129</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="178" spans="1:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="A178" s="157" t="s">
+      <c r="A178" s="126" t="s">
         <v>282</v>
       </c>
-      <c r="B178" s="157"/>
+      <c r="B178" s="126"/>
       <c r="C178" s="40" t="s">
         <v>283</v>
       </c>
@@ -10557,7 +10566,7 @@
       <c r="F181" s="45"/>
       <c r="G181" s="45"/>
     </row>
-    <row r="182" spans="1:7" s="2" customFormat="1" ht="14.4">
+    <row r="182" spans="1:7" s="2" customFormat="1" ht="13.5">
       <c r="D182" s="52"/>
       <c r="E182" s="52"/>
       <c r="F182" s="52"/>
@@ -10583,6 +10592,30 @@
     </row>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="A158:A177"/>
+    <mergeCell ref="B158:C158"/>
+    <mergeCell ref="B159:B161"/>
+    <mergeCell ref="B162:B167"/>
+    <mergeCell ref="B168:C168"/>
+    <mergeCell ref="B169:B177"/>
+    <mergeCell ref="B119:B138"/>
+    <mergeCell ref="B139:B146"/>
+    <mergeCell ref="B147:C147"/>
+    <mergeCell ref="B150:C150"/>
+    <mergeCell ref="A151:A157"/>
+    <mergeCell ref="B151:C151"/>
+    <mergeCell ref="B152:B154"/>
+    <mergeCell ref="B157:C157"/>
+    <mergeCell ref="B70:B80"/>
+    <mergeCell ref="B81:B84"/>
+    <mergeCell ref="B85:B91"/>
+    <mergeCell ref="B92:B98"/>
+    <mergeCell ref="B99:B118"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B18:B35"/>
+    <mergeCell ref="B36:B56"/>
+    <mergeCell ref="B57:B61"/>
+    <mergeCell ref="B62:B69"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A178:B178"/>
@@ -10599,30 +10632,6 @@
     <mergeCell ref="A3:C4"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="A5:A150"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B18:B35"/>
-    <mergeCell ref="B36:B56"/>
-    <mergeCell ref="B57:B61"/>
-    <mergeCell ref="B62:B69"/>
-    <mergeCell ref="B70:B80"/>
-    <mergeCell ref="B81:B84"/>
-    <mergeCell ref="B85:B91"/>
-    <mergeCell ref="B92:B98"/>
-    <mergeCell ref="B99:B118"/>
-    <mergeCell ref="B119:B138"/>
-    <mergeCell ref="B139:B146"/>
-    <mergeCell ref="B147:C147"/>
-    <mergeCell ref="B150:C150"/>
-    <mergeCell ref="A151:A157"/>
-    <mergeCell ref="B151:C151"/>
-    <mergeCell ref="B152:B154"/>
-    <mergeCell ref="A158:A177"/>
-    <mergeCell ref="B158:C158"/>
-    <mergeCell ref="B159:B161"/>
-    <mergeCell ref="B162:B167"/>
-    <mergeCell ref="B168:C168"/>
-    <mergeCell ref="B169:B177"/>
-    <mergeCell ref="B157:C157"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <dataValidations count="2">
@@ -10643,7 +10652,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <sheetData/>
   <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
